--- a/docs/bus/lead/LEAD-PENDING-REGISTER.xlsx
+++ b/docs/bus/lead/LEAD-PENDING-REGISTER.xlsx
@@ -37,7 +37,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -66,11 +66,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E0E7FF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00E5E7EB"/>
       </patternFill>
     </fill>
@@ -92,10 +87,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -112,9 +107,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -502,7 +494,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>IH35-TMS · USMCA · LEAD PENDING REGISTER · updated 10-23-2026 5:30 PM CT · every item numbered · DONE only with live proof</t>
+          <t>IH35-TMS · USMCA · LEAD PENDING REGISTER · updated 10-23-2026 5:50 PM CT · every item numbered · DONE only with live proof</t>
         </is>
       </c>
     </row>
@@ -1356,14 +1348,14 @@
           <t>443.269-A</t>
         </is>
       </c>
-      <c r="J17" s="6" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
+      <c r="J17" s="5" t="inlineStr">
+        <is>
+          <t>MERGED-UNVERIFIED</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>c3167b77</t>
+          <t>#27364 d6e9d60b 5:07 PM</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
@@ -1464,14 +1456,14 @@
           <t>443.270</t>
         </is>
       </c>
-      <c r="J19" s="8" t="inlineStr">
-        <is>
-          <t>IN PROGRESS</t>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>DONE-LIVE</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>push270.log</t>
+          <t>#27365 ee5b7359</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
@@ -1572,7 +1564,7 @@
           <t>443.270-B</t>
         </is>
       </c>
-      <c r="J21" s="9" t="inlineStr">
+      <c r="J21" s="8" t="inlineStr">
         <is>
           <t>BLOCKED</t>
         </is>
@@ -1988,12 +1980,16 @@
           <t>443.247</t>
         </is>
       </c>
-      <c r="J29" s="7" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="K29" s="3" t="inlineStr"/>
+      <c r="J29" s="8" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t>CC-2 fork: purge cascade casts int child ids to uuid; accidents trigger refuses DELETE -&gt; CC-2 fixing (443.281-F)</t>
+        </is>
+      </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
           <t>10-24 02:00 UTC</t>
@@ -2151,7 +2147,7 @@
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>docs/design/baseline-2026-10-23/</t>
+          <t>#27369 9932b495</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr"/>
@@ -3060,12 +3056,16 @@
           <t>443.280</t>
         </is>
       </c>
-      <c r="J49" s="7" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="K49" s="3" t="inlineStr"/>
+      <c r="J49" s="5" t="inlineStr">
+        <is>
+          <t>MERGED-UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="K49" s="3" t="inlineStr">
+        <is>
+          <t>#27368 0c5f5376 Cursor 5:26 PM</t>
+        </is>
+      </c>
       <c r="L49" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve"> 10-24 02:00 UTC</t>
@@ -3116,12 +3116,16 @@
           <t>443.280</t>
         </is>
       </c>
-      <c r="J50" s="7" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="K50" s="3" t="inlineStr"/>
+      <c r="J50" s="5" t="inlineStr">
+        <is>
+          <t>MERGED-UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="K50" s="3" t="inlineStr">
+        <is>
+          <t>#27364 d6e9d60b 5:07 PM</t>
+        </is>
+      </c>
       <c r="L50" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve"> 10-24 02:00 UTC</t>
@@ -3229,7 +3233,11 @@
           <t>PARTIAL</t>
         </is>
       </c>
-      <c r="K52" s="3" t="inlineStr"/>
+      <c r="K52" s="3" t="inlineStr">
+        <is>
+          <t>#27354 e8a9f02b; duplicate rows still live</t>
+        </is>
+      </c>
       <c r="L52" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve"> 10-24 02:00 UTC</t>
@@ -3280,12 +3288,16 @@
           <t>443.280</t>
         </is>
       </c>
-      <c r="J53" s="7" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="K53" s="3" t="inlineStr"/>
+      <c r="J53" s="5" t="inlineStr">
+        <is>
+          <t>MERGED-UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="K53" s="3" t="inlineStr">
+        <is>
+          <t>#27355 / #27364; live 5:37 PM: by-type rows still "—" while total $470.00</t>
+        </is>
+      </c>
       <c r="L53" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve"> 10-24 02:00 UTC</t>
@@ -3336,12 +3348,16 @@
           <t>443.280</t>
         </is>
       </c>
-      <c r="J54" s="7" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="K54" s="3" t="inlineStr"/>
+      <c r="J54" s="5" t="inlineStr">
+        <is>
+          <t>MERGED-UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="K54" s="3" t="inlineStr">
+        <is>
+          <t>#27358 eb08254d; live 5:38 PM page stuck "Loading…"</t>
+        </is>
+      </c>
       <c r="L54" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve"> 10-24 02:00 UTC</t>
@@ -3612,12 +3628,16 @@
           <t>443.280</t>
         </is>
       </c>
-      <c r="J59" s="7" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="K59" s="3" t="inlineStr"/>
+      <c r="J59" s="4" t="inlineStr">
+        <is>
+          <t>DONE-LIVE</t>
+        </is>
+      </c>
+      <c r="K59" s="3" t="inlineStr">
+        <is>
+          <t>#27367 40daa907; live 5:37 PM board only</t>
+        </is>
+      </c>
       <c r="L59" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve"> 10-24 02:00 UTC</t>
@@ -3772,12 +3792,16 @@
           <t>443.280</t>
         </is>
       </c>
-      <c r="J62" s="7" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="K62" s="3" t="inlineStr"/>
+      <c r="J62" s="6" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="K62" s="3" t="inlineStr">
+        <is>
+          <t>#27357 80270997; live 5:38 PM same layout, ~15 s load, "No current truck assignment" while on T156</t>
+        </is>
+      </c>
       <c r="L62" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve"> 10-24 02:00 UTC</t>
@@ -3824,12 +3848,16 @@
           <t>443.280</t>
         </is>
       </c>
-      <c r="J63" s="6" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
-        </is>
-      </c>
-      <c r="K63" s="3" t="inlineStr"/>
+      <c r="J63" s="5" t="inlineStr">
+        <is>
+          <t>MERGED-UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="K63" s="3" t="inlineStr">
+        <is>
+          <t>4ff9f272 bars lane + $/mi; #27359</t>
+        </is>
+      </c>
       <c r="L63" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve"> 10-24 02:00 UTC</t>
@@ -3876,12 +3904,16 @@
           <t>443.280</t>
         </is>
       </c>
-      <c r="J64" s="6" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
-        </is>
-      </c>
-      <c r="K64" s="3" t="inlineStr"/>
+      <c r="J64" s="5" t="inlineStr">
+        <is>
+          <t>MERGED-UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="K64" s="3" t="inlineStr">
+        <is>
+          <t>4ff9f272 1260/760, Load # right</t>
+        </is>
+      </c>
       <c r="L64" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve"> 10-24 02:00 UTC</t>
@@ -4508,12 +4540,16 @@
           <t>443.279</t>
         </is>
       </c>
-      <c r="J76" s="7" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="K76" s="3" t="inlineStr"/>
+      <c r="J76" s="5" t="inlineStr">
+        <is>
+          <t>MERGED-UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="K76" s="3" t="inlineStr">
+        <is>
+          <t>#27360 528fd12c delivered only via final stop + history repair; 358b7c12</t>
+        </is>
+      </c>
       <c r="L76" s="3" t="inlineStr">
         <is>
           <t>10-24 02:00 UTC</t>
@@ -5293,7 +5329,11 @@
           <t>DONE-LIVE</t>
         </is>
       </c>
-      <c r="K90" s="3" t="inlineStr"/>
+      <c r="K90" s="3" t="inlineStr">
+        <is>
+          <t>#27346 + be076e3d fastify.inject</t>
+        </is>
+      </c>
       <c r="L90" s="3" t="inlineStr">
         <is>
           <t>10-24 02:00 UTC</t>
@@ -6128,12 +6168,16 @@
           <t>443.281</t>
         </is>
       </c>
-      <c r="J105" s="7" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="K105" s="3" t="inlineStr"/>
+      <c r="J105" s="6" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="K105" s="3" t="inlineStr">
+        <is>
+          <t>#27354 e8a9f02b; duplicate rows still live</t>
+        </is>
+      </c>
       <c r="L105" s="3" t="inlineStr">
         <is>
           <t>10-24 02:00 UTC</t>
@@ -6720,12 +6764,16 @@
           <t>443.278/280/281</t>
         </is>
       </c>
-      <c r="J116" s="7" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="K116" s="3" t="inlineStr"/>
+      <c r="J116" s="5" t="inlineStr">
+        <is>
+          <t>MERGED-UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="K116" s="3" t="inlineStr">
+        <is>
+          <t>#27356 6b9b2dc0</t>
+        </is>
+      </c>
       <c r="L116" s="3" t="inlineStr">
         <is>
           <t>10-24 02:00 UTC</t>
@@ -6764,12 +6812,16 @@
           <t>443.278/280/281</t>
         </is>
       </c>
-      <c r="J117" s="7" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="K117" s="3" t="inlineStr"/>
+      <c r="J117" s="5" t="inlineStr">
+        <is>
+          <t>MERGED-UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="K117" s="3" t="inlineStr">
+        <is>
+          <t>#27356 6b9b2dc0</t>
+        </is>
+      </c>
       <c r="L117" s="3" t="inlineStr">
         <is>
           <t>10-24 02:00 UTC</t>
@@ -11721,16 +11773,16 @@
         <v>30</v>
       </c>
       <c r="C2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G2" t="n">
         <v>2</v>
@@ -11746,16 +11798,16 @@
         <v>35</v>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F3" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -11799,13 +11851,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -11827,10 +11879,10 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -11849,13 +11901,13 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -11896,16 +11948,16 @@
         <v>197</v>
       </c>
       <c r="C9" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D9" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E9" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F9" t="n">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="G9" t="n">
         <v>3</v>

--- a/docs/bus/lead/LEAD-PENDING-REGISTER.xlsx
+++ b/docs/bus/lead/LEAD-PENDING-REGISTER.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Register'!$A$2:$L$199</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Register'!$A$2:$L$201</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -37,7 +37,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -71,6 +71,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00E0E7FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="0013233F"/>
       </patternFill>
     </fill>
@@ -87,10 +92,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -107,6 +112,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -474,7 +482,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L199"/>
+  <dimension ref="A1:L201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -494,7 +502,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>IH35-TMS · USMCA · LEAD PENDING REGISTER · updated 10-23-2026 5:50 PM CT · every item numbered · DONE only with live proof</t>
+          <t>IH35-TMS · USMCA · LEAD PENDING REGISTER · updated 10-23-2026 6:35 PM CT · every item numbered · DONE only with live proof</t>
         </is>
       </c>
     </row>
@@ -5272,12 +5280,16 @@
           <t>443.278</t>
         </is>
       </c>
-      <c r="J89" s="7" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="K89" s="3" t="inlineStr"/>
+      <c r="J89" s="9" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="K89" s="3" t="inlineStr">
+        <is>
+          <t>LEAD 443.282 758bd029: guard credits tables read through a read view (D074 cache); selftest lock</t>
+        </is>
+      </c>
       <c r="L89" s="3" t="inlineStr">
         <is>
           <t>10-24 02:00 UTC</t>
@@ -5384,12 +5396,16 @@
           <t>443.281</t>
         </is>
       </c>
-      <c r="J91" s="7" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="K91" s="3" t="inlineStr"/>
+      <c r="J91" s="9" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="K91" s="3" t="inlineStr">
+        <is>
+          <t>LEAD 443.283: one source; Manual opens from authoritative cash when no saved opening</t>
+        </is>
+      </c>
       <c r="L91" s="3" t="inlineStr">
         <is>
           <t>10-24 02:00 UTC</t>
@@ -5440,12 +5456,16 @@
           <t>443.281</t>
         </is>
       </c>
-      <c r="J92" s="7" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="K92" s="3" t="inlineStr"/>
+      <c r="J92" s="9" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="K92" s="3" t="inlineStr">
+        <is>
+          <t>LEAD 443.283 f03a33c4: /cash-flow/opening-cash = BofA $8,202.50 + Relay $17,330.87 = $25,533.37; tests 3/3; pushing</t>
+        </is>
+      </c>
       <c r="L92" s="3" t="inlineStr">
         <is>
           <t>10-24 02:00 UTC</t>
@@ -5496,12 +5516,16 @@
           <t>443.281</t>
         </is>
       </c>
-      <c r="J93" s="7" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="K93" s="3" t="inlineStr"/>
+      <c r="J93" s="9" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="K93" s="3" t="inlineStr">
+        <is>
+          <t>LEAD 443.282 cc74c41e/082a09a6: actuals from operating bank (Oct $208,031.56 in / $205,270.54 out posted); pushing</t>
+        </is>
+      </c>
       <c r="L93" s="3" t="inlineStr">
         <is>
           <t>10-24 02:00 UTC</t>
@@ -5552,12 +5576,16 @@
           <t>443.281</t>
         </is>
       </c>
-      <c r="J94" s="7" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="K94" s="3" t="inlineStr"/>
+      <c r="J94" s="9" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="K94" s="3" t="inlineStr">
+        <is>
+          <t>LEAD 443.282: pointer matched_advance_id -&gt; matched_factoring_advance_id (25 advances $202,044.98); pushing</t>
+        </is>
+      </c>
       <c r="L94" s="3" t="inlineStr">
         <is>
           <t>10-24 02:00 UTC</t>
@@ -6694,30 +6722,42 @@
       </c>
       <c r="B115" s="3" t="inlineStr">
         <is>
-          <t>G · Main reds / guards</t>
+          <t>E · Data / engine root causes</t>
         </is>
       </c>
       <c r="C115" s="3" t="inlineStr">
         <is>
-          <t>Guards</t>
+          <t>Banking</t>
         </is>
       </c>
       <c r="D115" s="3" t="inlineStr">
         <is>
-          <t>verify-stops-are-geocoded red (13699) — live-data exception for CC-2 migration</t>
-        </is>
-      </c>
-      <c r="E115" s="3" t="inlineStr"/>
-      <c r="F115" s="3" t="inlineStr"/>
-      <c r="G115" s="3" t="inlineStr"/>
+          <t>43 Plaid PENDING lines in October never replaced by their posted lines (e.g. SOUTH TX TRUCK CENTERS -460.01 pending 10-03 + posted 10-05) -&gt; Banking Money in/out ($216,532.56 / $239,059.03) and Unexpected "possible duplicates" count them twice</t>
+        </is>
+      </c>
+      <c r="E115" s="3" t="inlineStr">
+        <is>
+          <t>prod 10-23 6:00 PM</t>
+        </is>
+      </c>
+      <c r="F115" s="3" t="inlineStr">
+        <is>
+          <t>ingest keeps pending rows after the posted row arrives (pending_transaction_id not reconciled)</t>
+        </is>
+      </c>
+      <c r="G115" s="3" t="inlineStr">
+        <is>
+          <t>on posted arrival, retire the pending row (merged_into or void with reason); backfill; guard: no pending row older than 10 days with a posted twin</t>
+        </is>
+      </c>
       <c r="H115" s="3" t="inlineStr">
         <is>
-          <t>CC-2/CC-3</t>
+          <t>CC-2</t>
         </is>
       </c>
       <c r="I115" s="3" t="inlineStr">
         <is>
-          <t>443.278/280/281</t>
+          <t>443.282</t>
         </is>
       </c>
       <c r="J115" s="7" t="inlineStr">
@@ -6738,42 +6778,42 @@
       </c>
       <c r="B116" s="3" t="inlineStr">
         <is>
-          <t>G · Main reds / guards</t>
+          <t>A · Owner requests (last 24 h)</t>
         </is>
       </c>
       <c r="C116" s="3" t="inlineStr">
         <is>
-          <t>Guards</t>
+          <t>Process</t>
         </is>
       </c>
       <c r="D116" s="3" t="inlineStr">
         <is>
-          <t>verify-resettlement-origin-load-dates — guard retarget to board labels</t>
-        </is>
-      </c>
-      <c r="E116" s="3" t="inlineStr"/>
+          <t>Cursor confirmation of 443.282 (owner-authorized build exactly as specified)</t>
+        </is>
+      </c>
+      <c r="E116" s="3" t="inlineStr">
+        <is>
+          <t>box posted 5:45 PM</t>
+        </is>
+      </c>
       <c r="F116" s="3" t="inlineStr"/>
       <c r="G116" s="3" t="inlineStr"/>
       <c r="H116" s="3" t="inlineStr">
         <is>
-          <t>CC-3</t>
+          <t>CURSOR</t>
         </is>
       </c>
       <c r="I116" s="3" t="inlineStr">
         <is>
-          <t>443.278/280/281</t>
-        </is>
-      </c>
-      <c r="J116" s="5" t="inlineStr">
-        <is>
-          <t>MERGED-UNVERIFIED</t>
-        </is>
-      </c>
-      <c r="K116" s="3" t="inlineStr">
-        <is>
-          <t>#27356 6b9b2dc0</t>
-        </is>
-      </c>
+          <t>443.282</t>
+        </is>
+      </c>
+      <c r="J116" s="7" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="K116" s="3" t="inlineStr"/>
       <c r="L116" s="3" t="inlineStr">
         <is>
           <t>10-24 02:00 UTC</t>
@@ -6796,7 +6836,7 @@
       </c>
       <c r="D117" s="3" t="inlineStr">
         <is>
-          <t>verify-entity-label-rejects-uuid-shaped-name — restore protection in accounting hub</t>
+          <t>verify-stops-are-geocoded red (13699) — live-data exception for CC-2 migration</t>
         </is>
       </c>
       <c r="E117" s="3" t="inlineStr"/>
@@ -6804,7 +6844,7 @@
       <c r="G117" s="3" t="inlineStr"/>
       <c r="H117" s="3" t="inlineStr">
         <is>
-          <t>CC-3</t>
+          <t>CC-2/CC-3</t>
         </is>
       </c>
       <c r="I117" s="3" t="inlineStr">
@@ -6812,16 +6852,12 @@
           <t>443.278/280/281</t>
         </is>
       </c>
-      <c r="J117" s="5" t="inlineStr">
-        <is>
-          <t>MERGED-UNVERIFIED</t>
-        </is>
-      </c>
-      <c r="K117" s="3" t="inlineStr">
-        <is>
-          <t>#27356 6b9b2dc0</t>
-        </is>
-      </c>
+      <c r="J117" s="7" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="K117" s="3" t="inlineStr"/>
       <c r="L117" s="3" t="inlineStr">
         <is>
           <t>10-24 02:00 UTC</t>
@@ -6844,7 +6880,7 @@
       </c>
       <c r="D118" s="3" t="inlineStr">
         <is>
-          <t>verify-board-page-no-legacy-sections (new) — stops layering</t>
+          <t>verify-resettlement-origin-load-dates — guard retarget to board labels</t>
         </is>
       </c>
       <c r="E118" s="3" t="inlineStr"/>
@@ -6852,7 +6888,7 @@
       <c r="G118" s="3" t="inlineStr"/>
       <c r="H118" s="3" t="inlineStr">
         <is>
-          <t>CODEX</t>
+          <t>CC-3</t>
         </is>
       </c>
       <c r="I118" s="3" t="inlineStr">
@@ -6860,12 +6896,16 @@
           <t>443.278/280/281</t>
         </is>
       </c>
-      <c r="J118" s="7" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="K118" s="3" t="inlineStr"/>
+      <c r="J118" s="5" t="inlineStr">
+        <is>
+          <t>MERGED-UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="K118" s="3" t="inlineStr">
+        <is>
+          <t>#27356 6b9b2dc0</t>
+        </is>
+      </c>
       <c r="L118" s="3" t="inlineStr">
         <is>
           <t>10-24 02:00 UTC</t>
@@ -6888,7 +6928,7 @@
       </c>
       <c r="D119" s="3" t="inlineStr">
         <is>
-          <t>verify-entity-filters-multi-select (new) — fails on single-select entity filters</t>
+          <t>verify-entity-label-rejects-uuid-shaped-name — restore protection in accounting hub</t>
         </is>
       </c>
       <c r="E119" s="3" t="inlineStr"/>
@@ -6896,7 +6936,7 @@
       <c r="G119" s="3" t="inlineStr"/>
       <c r="H119" s="3" t="inlineStr">
         <is>
-          <t>CODEX</t>
+          <t>CC-3</t>
         </is>
       </c>
       <c r="I119" s="3" t="inlineStr">
@@ -6904,12 +6944,16 @@
           <t>443.278/280/281</t>
         </is>
       </c>
-      <c r="J119" s="7" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="K119" s="3" t="inlineStr"/>
+      <c r="J119" s="5" t="inlineStr">
+        <is>
+          <t>MERGED-UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="K119" s="3" t="inlineStr">
+        <is>
+          <t>#27356 6b9b2dc0</t>
+        </is>
+      </c>
       <c r="L119" s="3" t="inlineStr">
         <is>
           <t>10-24 02:00 UTC</t>
@@ -6922,54 +6966,38 @@
       </c>
       <c r="B120" s="3" t="inlineStr">
         <is>
-          <t>H · Codex live Chrome audit D001-D079 (docs/bus/AUDIT-443.257-REGISTER.md)</t>
+          <t>G · Main reds / guards</t>
         </is>
       </c>
       <c r="C120" s="3" t="inlineStr">
         <is>
-          <t>Fuel › Questions › Review</t>
+          <t>Guards</t>
         </is>
       </c>
       <c r="D120" s="3" t="inlineStr">
         <is>
-          <t>D001: Clicking Review throws undefined `load_number` in FuelAssignmentPopup; whole-app crash</t>
-        </is>
-      </c>
-      <c r="E120" s="3" t="inlineStr">
-        <is>
-          <t>inline: Fuel Questions crash</t>
-        </is>
-      </c>
-      <c r="F120" s="3" t="inlineStr">
-        <is>
-          <t>class E</t>
-        </is>
-      </c>
-      <c r="G120" s="3" t="inlineStr">
-        <is>
-          <t>Review opens a usable panel; missing data handled without crashing</t>
-        </is>
-      </c>
+          <t>verify-board-page-no-legacy-sections (new) — stops layering</t>
+        </is>
+      </c>
+      <c r="E120" s="3" t="inlineStr"/>
+      <c r="F120" s="3" t="inlineStr"/>
+      <c r="G120" s="3" t="inlineStr"/>
       <c r="H120" s="3" t="inlineStr">
         <is>
-          <t>CC-2</t>
+          <t>CODEX</t>
         </is>
       </c>
       <c r="I120" s="3" t="inlineStr">
         <is>
-          <t>443.257-D</t>
-        </is>
-      </c>
-      <c r="J120" s="5" t="inlineStr">
-        <is>
-          <t>MERGED-UNVERIFIED</t>
-        </is>
-      </c>
-      <c r="K120" s="3" t="inlineStr">
-        <is>
-          <t>bf7dadd3</t>
-        </is>
-      </c>
+          <t>443.278/280/281</t>
+        </is>
+      </c>
+      <c r="J120" s="7" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="K120" s="3" t="inlineStr"/>
       <c r="L120" s="3" t="inlineStr">
         <is>
           <t>10-24 02:00 UTC</t>
@@ -6982,42 +7010,30 @@
       </c>
       <c r="B121" s="3" t="inlineStr">
         <is>
-          <t>H · Codex live Chrome audit D001-D079 (docs/bus/AUDIT-443.257-REGISTER.md)</t>
+          <t>G · Main reds / guards</t>
         </is>
       </c>
       <c r="C121" s="3" t="inlineStr">
         <is>
-          <t>Home › Overview › Money tiles</t>
+          <t>Guards</t>
         </is>
       </c>
       <c r="D121" s="3" t="inlineStr">
         <is>
-          <t>D002: Currency values omit cents</t>
-        </is>
-      </c>
-      <c r="E121" s="3" t="inlineStr">
-        <is>
-          <t>inline: Home</t>
-        </is>
-      </c>
-      <c r="F121" s="3" t="inlineStr">
-        <is>
-          <t>class M</t>
-        </is>
-      </c>
-      <c r="G121" s="3" t="inlineStr">
-        <is>
-          <t>Currency always two decimal places</t>
-        </is>
-      </c>
+          <t>verify-entity-filters-multi-select (new) — fails on single-select entity filters</t>
+        </is>
+      </c>
+      <c r="E121" s="3" t="inlineStr"/>
+      <c r="F121" s="3" t="inlineStr"/>
+      <c r="G121" s="3" t="inlineStr"/>
       <c r="H121" s="3" t="inlineStr">
         <is>
-          <t>Cursor</t>
+          <t>CODEX</t>
         </is>
       </c>
       <c r="I121" s="3" t="inlineStr">
         <is>
-          <t>443.257-D</t>
+          <t>443.278/280/281</t>
         </is>
       </c>
       <c r="J121" s="7" t="inlineStr">
@@ -7025,11 +7041,7 @@
           <t>OPEN</t>
         </is>
       </c>
-      <c r="K121" s="3" t="inlineStr">
-        <is>
-          <t>not re-verified since audit</t>
-        </is>
-      </c>
+      <c r="K121" s="3" t="inlineStr"/>
       <c r="L121" s="3" t="inlineStr">
         <is>
           <t>10-24 02:00 UTC</t>
@@ -7047,32 +7059,32 @@
       </c>
       <c r="C122" s="3" t="inlineStr">
         <is>
-          <t>Home › Overview › Driver day summary</t>
+          <t>Fuel › Questions › Review</t>
         </is>
       </c>
       <c r="D122" s="3" t="inlineStr">
         <is>
-          <t>D003: Names render all-uppercase</t>
+          <t>D001: Clicking Review throws undefined `load_number` in FuelAssignmentPopup; whole-app crash</t>
         </is>
       </c>
       <c r="E122" s="3" t="inlineStr">
         <is>
-          <t>inline: Home</t>
+          <t>inline: Fuel Questions crash</t>
         </is>
       </c>
       <c r="F122" s="3" t="inlineStr">
         <is>
-          <t>class N</t>
+          <t>class E</t>
         </is>
       </c>
       <c r="G122" s="3" t="inlineStr">
         <is>
-          <t>Full proper-case names, honoring exceptions</t>
+          <t>Review opens a usable panel; missing data handled without crashing</t>
         </is>
       </c>
       <c r="H122" s="3" t="inlineStr">
         <is>
-          <t>CC-1 / Cursor</t>
+          <t>CC-2</t>
         </is>
       </c>
       <c r="I122" s="3" t="inlineStr">
@@ -7080,14 +7092,14 @@
           <t>443.257-D</t>
         </is>
       </c>
-      <c r="J122" s="7" t="inlineStr">
-        <is>
-          <t>OPEN</t>
+      <c r="J122" s="5" t="inlineStr">
+        <is>
+          <t>MERGED-UNVERIFIED</t>
         </is>
       </c>
       <c r="K122" s="3" t="inlineStr">
         <is>
-          <t>not re-verified since audit</t>
+          <t>bf7dadd3</t>
         </is>
       </c>
       <c r="L122" s="3" t="inlineStr">
@@ -7107,12 +7119,12 @@
       </c>
       <c r="C123" s="3" t="inlineStr">
         <is>
-          <t>Home › Overview › Weekly revenue</t>
+          <t>Home › Overview › Money tiles</t>
         </is>
       </c>
       <c r="D123" s="3" t="inlineStr">
         <is>
-          <t>D004: Axis dates use DD/MM without year</t>
+          <t>D002: Currency values omit cents</t>
         </is>
       </c>
       <c r="E123" s="3" t="inlineStr">
@@ -7122,12 +7134,12 @@
       </c>
       <c r="F123" s="3" t="inlineStr">
         <is>
-          <t>class D</t>
+          <t>class M</t>
         </is>
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
-          <t>MM/DD/YYYY under this round's explicit rule</t>
+          <t>Currency always two decimal places</t>
         </is>
       </c>
       <c r="H123" s="3" t="inlineStr">
@@ -7167,32 +7179,32 @@
       </c>
       <c r="C124" s="3" t="inlineStr">
         <is>
-          <t>Home › Overview › Driver summary request</t>
+          <t>Home › Overview › Driver day summary</t>
         </is>
       </c>
       <c r="D124" s="3" t="inlineStr">
         <is>
-          <t>D005: `/api/v1/telematics/driver-day-summary` 5,071 ms</t>
+          <t>D003: Names render all-uppercase</t>
         </is>
       </c>
       <c r="E124" s="3" t="inlineStr">
         <is>
-          <t>pending: resource timing</t>
+          <t>inline: Home</t>
         </is>
       </c>
       <c r="F124" s="3" t="inlineStr">
         <is>
-          <t>class P</t>
+          <t>class N</t>
         </is>
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>API at most 2,000 ms</t>
+          <t>Full proper-case names, honoring exceptions</t>
         </is>
       </c>
       <c r="H124" s="3" t="inlineStr">
         <is>
-          <t>CC-2</t>
+          <t>CC-1 / Cursor</t>
         </is>
       </c>
       <c r="I124" s="3" t="inlineStr">
@@ -7227,27 +7239,27 @@
       </c>
       <c r="C125" s="3" t="inlineStr">
         <is>
-          <t>Settlements › Navigation › Drivers</t>
+          <t>Home › Overview › Weekly revenue</t>
         </is>
       </c>
       <c r="D125" s="3" t="inlineStr">
         <is>
-          <t>D006: Link targets `/drivers` outside module</t>
+          <t>D004: Axis dates use DD/MM without year</t>
         </is>
       </c>
       <c r="E125" s="3" t="inlineStr">
         <is>
-          <t>pending: DOM</t>
+          <t>inline: Home</t>
         </is>
       </c>
       <c r="F125" s="3" t="inlineStr">
         <is>
-          <t>class B</t>
+          <t>class D</t>
         </is>
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
-          <t>Keep Settlements context</t>
+          <t>MM/DD/YYYY under this round's explicit rule</t>
         </is>
       </c>
       <c r="H125" s="3" t="inlineStr">
@@ -7287,32 +7299,32 @@
       </c>
       <c r="C126" s="3" t="inlineStr">
         <is>
-          <t>Settlements › Navigation › Profiles</t>
+          <t>Home › Overview › Driver summary request</t>
         </is>
       </c>
       <c r="D126" s="3" t="inlineStr">
         <is>
-          <t>D007: Link targets `/drivers/profiles`</t>
+          <t>D005: `/api/v1/telematics/driver-day-summary` 5,071 ms</t>
         </is>
       </c>
       <c r="E126" s="3" t="inlineStr">
         <is>
-          <t>pending: DOM</t>
+          <t>pending: resource timing</t>
         </is>
       </c>
       <c r="F126" s="3" t="inlineStr">
         <is>
-          <t>class B</t>
+          <t>class P</t>
         </is>
       </c>
       <c r="G126" s="3" t="inlineStr">
         <is>
-          <t>Keep Settlements context</t>
+          <t>API at most 2,000 ms</t>
         </is>
       </c>
       <c r="H126" s="3" t="inlineStr">
         <is>
-          <t>Cursor</t>
+          <t>CC-2</t>
         </is>
       </c>
       <c r="I126" s="3" t="inlineStr">
@@ -7347,12 +7359,12 @@
       </c>
       <c r="C127" s="3" t="inlineStr">
         <is>
-          <t>Settlements › Navigation › Pre-Settlements</t>
+          <t>Settlements › Navigation › Drivers</t>
         </is>
       </c>
       <c r="D127" s="3" t="inlineStr">
         <is>
-          <t>D008: Link targets `/drivers/pre-settlements`</t>
+          <t>D006: Link targets `/drivers` outside module</t>
         </is>
       </c>
       <c r="E127" s="3" t="inlineStr">
@@ -7407,12 +7419,12 @@
       </c>
       <c r="C128" s="3" t="inlineStr">
         <is>
-          <t>Settlements › Navigation › Feed Gate</t>
+          <t>Settlements › Navigation › Profiles</t>
         </is>
       </c>
       <c r="D128" s="3" t="inlineStr">
         <is>
-          <t>D009: Link targets `/feed-gate`</t>
+          <t>D007: Link targets `/drivers/profiles`</t>
         </is>
       </c>
       <c r="E128" s="3" t="inlineStr">
@@ -7467,12 +7479,12 @@
       </c>
       <c r="C129" s="3" t="inlineStr">
         <is>
-          <t>Settlements › Navigation › Cash Advances</t>
+          <t>Settlements › Navigation › Pre-Settlements</t>
         </is>
       </c>
       <c r="D129" s="3" t="inlineStr">
         <is>
-          <t>D010: Link targets `/cash-advances`</t>
+          <t>D008: Link targets `/drivers/pre-settlements`</t>
         </is>
       </c>
       <c r="E129" s="3" t="inlineStr">
@@ -7527,12 +7539,12 @@
       </c>
       <c r="C130" s="3" t="inlineStr">
         <is>
-          <t>Settlements › Navigation › Liabilities</t>
+          <t>Settlements › Navigation › Feed Gate</t>
         </is>
       </c>
       <c r="D130" s="3" t="inlineStr">
         <is>
-          <t>D011: Link targets `/liabilities`</t>
+          <t>D009: Link targets `/feed-gate`</t>
         </is>
       </c>
       <c r="E130" s="3" t="inlineStr">
@@ -7587,12 +7599,12 @@
       </c>
       <c r="C131" s="3" t="inlineStr">
         <is>
-          <t>Settlements › Navigation › Escrow</t>
+          <t>Settlements › Navigation › Cash Advances</t>
         </is>
       </c>
       <c r="D131" s="3" t="inlineStr">
         <is>
-          <t>D012: Link targets `/accounting/escrow`</t>
+          <t>D010: Link targets `/cash-advances`</t>
         </is>
       </c>
       <c r="E131" s="3" t="inlineStr">
@@ -7647,12 +7659,12 @@
       </c>
       <c r="C132" s="3" t="inlineStr">
         <is>
-          <t>Settlements › Navigation › Pay Rate Templates</t>
+          <t>Settlements › Navigation › Liabilities</t>
         </is>
       </c>
       <c r="D132" s="3" t="inlineStr">
         <is>
-          <t>D013: Link targets `/drivers/pay-rate-templates`</t>
+          <t>D011: Link targets `/liabilities`</t>
         </is>
       </c>
       <c r="E132" s="3" t="inlineStr">
@@ -7707,12 +7719,12 @@
       </c>
       <c r="C133" s="3" t="inlineStr">
         <is>
-          <t>Settlements › Navigation › Deductions</t>
+          <t>Settlements › Navigation › Escrow</t>
         </is>
       </c>
       <c r="D133" s="3" t="inlineStr">
         <is>
-          <t>D014: Link targets `/drivers/deductions`</t>
+          <t>D012: Link targets `/accounting/escrow`</t>
         </is>
       </c>
       <c r="E133" s="3" t="inlineStr">
@@ -7767,12 +7779,12 @@
       </c>
       <c r="C134" s="3" t="inlineStr">
         <is>
-          <t>Settlements › List › Driver names</t>
+          <t>Settlements › Navigation › Pay Rate Templates</t>
         </is>
       </c>
       <c r="D134" s="3" t="inlineStr">
         <is>
-          <t>D015: All-uppercase names displayed</t>
+          <t>D013: Link targets `/drivers/pay-rate-templates`</t>
         </is>
       </c>
       <c r="E134" s="3" t="inlineStr">
@@ -7782,17 +7794,17 @@
       </c>
       <c r="F134" s="3" t="inlineStr">
         <is>
-          <t>class N</t>
+          <t>class B</t>
         </is>
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>Full proper-case names</t>
+          <t>Keep Settlements context</t>
         </is>
       </c>
       <c r="H134" s="3" t="inlineStr">
         <is>
-          <t>CC-1 / Cursor</t>
+          <t>Cursor</t>
         </is>
       </c>
       <c r="I134" s="3" t="inlineStr">
@@ -7800,14 +7812,14 @@
           <t>443.257-D</t>
         </is>
       </c>
-      <c r="J134" s="4" t="inlineStr">
-        <is>
-          <t>DONE-LIVE</t>
+      <c r="J134" s="7" t="inlineStr">
+        <is>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="K134" s="3" t="inlineStr">
         <is>
-          <t>settlements home proper case 10-23 5:12 PM</t>
+          <t>not re-verified since audit</t>
         </is>
       </c>
       <c r="L134" s="3" t="inlineStr">
@@ -7827,12 +7839,12 @@
       </c>
       <c r="C135" s="3" t="inlineStr">
         <is>
-          <t>Fuel › Questions › Table</t>
+          <t>Settlements › Navigation › Deductions</t>
         </is>
       </c>
       <c r="D135" s="3" t="inlineStr">
         <is>
-          <t>D016: No column chooser in rendered DOM</t>
+          <t>D014: Link targets `/drivers/deductions`</t>
         </is>
       </c>
       <c r="E135" s="3" t="inlineStr">
@@ -7842,12 +7854,12 @@
       </c>
       <c r="F135" s="3" t="inlineStr">
         <is>
-          <t>class T</t>
+          <t>class B</t>
         </is>
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
-          <t>Gear column chooser</t>
+          <t>Keep Settlements context</t>
         </is>
       </c>
       <c r="H135" s="3" t="inlineStr">
@@ -7860,14 +7872,14 @@
           <t>443.257-D</t>
         </is>
       </c>
-      <c r="J135" s="5" t="inlineStr">
-        <is>
-          <t>MERGED-UNVERIFIED</t>
+      <c r="J135" s="7" t="inlineStr">
+        <is>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="K135" s="3" t="inlineStr">
         <is>
-          <t>0512ef14</t>
+          <t>not re-verified since audit</t>
         </is>
       </c>
       <c r="L135" s="3" t="inlineStr">
@@ -7887,12 +7899,12 @@
       </c>
       <c r="C136" s="3" t="inlineStr">
         <is>
-          <t>Fuel › Questions › Table headers</t>
+          <t>Settlements › List › Driver names</t>
         </is>
       </c>
       <c r="D136" s="3" t="inlineStr">
         <is>
-          <t>D017: Headers have no sorting controls</t>
+          <t>D015: All-uppercase names displayed</t>
         </is>
       </c>
       <c r="E136" s="3" t="inlineStr">
@@ -7902,17 +7914,17 @@
       </c>
       <c r="F136" s="3" t="inlineStr">
         <is>
-          <t>class T</t>
+          <t>class N</t>
         </is>
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>Sortable columns</t>
+          <t>Full proper-case names</t>
         </is>
       </c>
       <c r="H136" s="3" t="inlineStr">
         <is>
-          <t>Cursor</t>
+          <t>CC-1 / Cursor</t>
         </is>
       </c>
       <c r="I136" s="3" t="inlineStr">
@@ -7920,14 +7932,14 @@
           <t>443.257-D</t>
         </is>
       </c>
-      <c r="J136" s="5" t="inlineStr">
-        <is>
-          <t>MERGED-UNVERIFIED</t>
+      <c r="J136" s="4" t="inlineStr">
+        <is>
+          <t>DONE-LIVE</t>
         </is>
       </c>
       <c r="K136" s="3" t="inlineStr">
         <is>
-          <t>0512ef14</t>
+          <t>settlements home proper case 10-23 5:12 PM</t>
         </is>
       </c>
       <c r="L136" s="3" t="inlineStr">
@@ -7947,27 +7959,27 @@
       </c>
       <c r="C137" s="3" t="inlineStr">
         <is>
-          <t>Fuel › Cards › Assign card drawer</t>
+          <t>Fuel › Questions › Table</t>
         </is>
       </c>
       <c r="D137" s="3" t="inlineStr">
         <is>
-          <t>D018: Six input controls measured 38px high</t>
+          <t>D016: No column chooser in rendered DOM</t>
         </is>
       </c>
       <c r="E137" s="3" t="inlineStr">
         <is>
-          <t>inline: Assign fuel card</t>
+          <t>pending: DOM</t>
         </is>
       </c>
       <c r="F137" s="3" t="inlineStr">
         <is>
-          <t>class I</t>
+          <t>class T</t>
         </is>
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
-          <t>Inputs 32px</t>
+          <t>Gear column chooser</t>
         </is>
       </c>
       <c r="H137" s="3" t="inlineStr">
@@ -7980,14 +7992,14 @@
           <t>443.257-D</t>
         </is>
       </c>
-      <c r="J137" s="7" t="inlineStr">
-        <is>
-          <t>OPEN</t>
+      <c r="J137" s="5" t="inlineStr">
+        <is>
+          <t>MERGED-UNVERIFIED</t>
         </is>
       </c>
       <c r="K137" s="3" t="inlineStr">
         <is>
-          <t>not re-verified since audit</t>
+          <t>0512ef14</t>
         </is>
       </c>
       <c r="L137" s="3" t="inlineStr">
@@ -8007,32 +8019,32 @@
       </c>
       <c r="C138" s="3" t="inlineStr">
         <is>
-          <t>Fuel › Cards › Driver options request</t>
+          <t>Fuel › Questions › Table headers</t>
         </is>
       </c>
       <c r="D138" s="3" t="inlineStr">
         <is>
-          <t>D019: `/api/v1/mdata/drivers` 4,522 ms in audit session</t>
+          <t>D017: Headers have no sorting controls</t>
         </is>
       </c>
       <c r="E138" s="3" t="inlineStr">
         <is>
-          <t>pending: resource timing</t>
+          <t>pending: DOM</t>
         </is>
       </c>
       <c r="F138" s="3" t="inlineStr">
         <is>
-          <t>class P</t>
+          <t>class T</t>
         </is>
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>API at most 2,000 ms</t>
+          <t>Sortable columns</t>
         </is>
       </c>
       <c r="H138" s="3" t="inlineStr">
         <is>
-          <t>CC-2</t>
+          <t>Cursor</t>
         </is>
       </c>
       <c r="I138" s="3" t="inlineStr">
@@ -8040,14 +8052,14 @@
           <t>443.257-D</t>
         </is>
       </c>
-      <c r="J138" s="7" t="inlineStr">
-        <is>
-          <t>OPEN</t>
+      <c r="J138" s="5" t="inlineStr">
+        <is>
+          <t>MERGED-UNVERIFIED</t>
         </is>
       </c>
       <c r="K138" s="3" t="inlineStr">
         <is>
-          <t>not re-verified since audit</t>
+          <t>0512ef14</t>
         </is>
       </c>
       <c r="L138" s="3" t="inlineStr">
@@ -8067,32 +8079,32 @@
       </c>
       <c r="C139" s="3" t="inlineStr">
         <is>
-          <t>Fuel › Expense mapping › Mapping request</t>
+          <t>Fuel › Cards › Assign card drawer</t>
         </is>
       </c>
       <c r="D139" s="3" t="inlineStr">
         <is>
-          <t>D020: `/api/v1/accounting/expense-category-map` 8,831 ms</t>
+          <t>D018: Six input controls measured 38px high</t>
         </is>
       </c>
       <c r="E139" s="3" t="inlineStr">
         <is>
-          <t>pending: resource timing</t>
+          <t>inline: Assign fuel card</t>
         </is>
       </c>
       <c r="F139" s="3" t="inlineStr">
         <is>
-          <t>class P</t>
+          <t>class I</t>
         </is>
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
-          <t>API at most 2,000 ms</t>
+          <t>Inputs 32px</t>
         </is>
       </c>
       <c r="H139" s="3" t="inlineStr">
         <is>
-          <t>CC-1</t>
+          <t>Cursor</t>
         </is>
       </c>
       <c r="I139" s="3" t="inlineStr">
@@ -8127,32 +8139,32 @@
       </c>
       <c r="C140" s="3" t="inlineStr">
         <is>
-          <t>Dispatch › Home › Round-trip exposure</t>
+          <t>Fuel › Cards › Driver options request</t>
         </is>
       </c>
       <c r="D140" s="3" t="inlineStr">
         <is>
-          <t>D021: Driver names abbreviated to initials</t>
+          <t>D019: `/api/v1/mdata/drivers` 4,522 ms in audit session</t>
         </is>
       </c>
       <c r="E140" s="3" t="inlineStr">
         <is>
-          <t>pending: DOM</t>
+          <t>pending: resource timing</t>
         </is>
       </c>
       <c r="F140" s="3" t="inlineStr">
         <is>
-          <t>class N</t>
+          <t>class P</t>
         </is>
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>Full proper-case names</t>
+          <t>API at most 2,000 ms</t>
         </is>
       </c>
       <c r="H140" s="3" t="inlineStr">
         <is>
-          <t>Cursor</t>
+          <t>CC-2</t>
         </is>
       </c>
       <c r="I140" s="3" t="inlineStr">
@@ -8160,14 +8172,14 @@
           <t>443.257-D</t>
         </is>
       </c>
-      <c r="J140" s="6" t="inlineStr">
-        <is>
-          <t>RE-VERIFY</t>
+      <c r="J140" s="7" t="inlineStr">
+        <is>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="K140" s="3" t="inlineStr">
         <is>
-          <t>loads list shows full names 10-23</t>
+          <t>not re-verified since audit</t>
         </is>
       </c>
       <c r="L140" s="3" t="inlineStr">
@@ -8187,32 +8199,32 @@
       </c>
       <c r="C141" s="3" t="inlineStr">
         <is>
-          <t>Dispatch › Home › Return / idle / missing-bill tables</t>
+          <t>Fuel › Expense mapping › Mapping request</t>
         </is>
       </c>
       <c r="D141" s="3" t="inlineStr">
         <is>
-          <t>D022: Driver names all-uppercase</t>
+          <t>D020: `/api/v1/accounting/expense-category-map` 8,831 ms</t>
         </is>
       </c>
       <c r="E141" s="3" t="inlineStr">
         <is>
-          <t>pending: DOM</t>
+          <t>pending: resource timing</t>
         </is>
       </c>
       <c r="F141" s="3" t="inlineStr">
         <is>
-          <t>class N</t>
+          <t>class P</t>
         </is>
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
-          <t>Full proper-case names</t>
+          <t>API at most 2,000 ms</t>
         </is>
       </c>
       <c r="H141" s="3" t="inlineStr">
         <is>
-          <t>CC-1 / Cursor</t>
+          <t>CC-1</t>
         </is>
       </c>
       <c r="I141" s="3" t="inlineStr">
@@ -8247,32 +8259,32 @@
       </c>
       <c r="C142" s="3" t="inlineStr">
         <is>
-          <t>Dispatch › Book Load › Stop fields</t>
+          <t>Dispatch › Home › Round-trip exposure</t>
         </is>
       </c>
       <c r="D142" s="3" t="inlineStr">
         <is>
-          <t>D023: Both ZIP controls measured 28px high × 381.33px wide</t>
+          <t>D021: Driver names abbreviated to initials</t>
         </is>
       </c>
       <c r="E142" s="3" t="inlineStr">
         <is>
-          <t>inline: Book Load</t>
+          <t>pending: DOM</t>
         </is>
       </c>
       <c r="F142" s="3" t="inlineStr">
         <is>
-          <t>class I</t>
+          <t>class N</t>
         </is>
       </c>
       <c r="G142" s="3" t="inlineStr">
         <is>
-          <t>ZIP 32px high × 88px wide</t>
+          <t>Full proper-case names</t>
         </is>
       </c>
       <c r="H142" s="3" t="inlineStr">
         <is>
-          <t>Cursor / CC-3</t>
+          <t>Cursor</t>
         </is>
       </c>
       <c r="I142" s="3" t="inlineStr">
@@ -8280,14 +8292,14 @@
           <t>443.257-D</t>
         </is>
       </c>
-      <c r="J142" s="4" t="inlineStr">
-        <is>
-          <t>DONE-LIVE</t>
+      <c r="J142" s="6" t="inlineStr">
+        <is>
+          <t>RE-VERIFY</t>
         </is>
       </c>
       <c r="K142" s="3" t="inlineStr">
         <is>
-          <t>#27294 ZIP 88px</t>
+          <t>loads list shows full names 10-23</t>
         </is>
       </c>
       <c r="L142" s="3" t="inlineStr">
@@ -8307,32 +8319,32 @@
       </c>
       <c r="C143" s="3" t="inlineStr">
         <is>
-          <t>Dispatch › Book Load › Presentation</t>
+          <t>Dispatch › Home › Return / idle / missing-bill tables</t>
         </is>
       </c>
       <c r="D143" s="3" t="inlineStr">
         <is>
-          <t>D024: Long A–E form; no Side panel / Center toggle or five-step flow present</t>
+          <t>D022: Driver names all-uppercase</t>
         </is>
       </c>
       <c r="E143" s="3" t="inlineStr">
         <is>
-          <t>inline: Book Load</t>
+          <t>pending: DOM</t>
         </is>
       </c>
       <c r="F143" s="3" t="inlineStr">
         <is>
-          <t>class V</t>
+          <t>class N</t>
         </is>
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
-          <t>Same component with side/center toggle and specified five-step layout</t>
+          <t>Full proper-case names</t>
         </is>
       </c>
       <c r="H143" s="3" t="inlineStr">
         <is>
-          <t>Cursor / CC-3</t>
+          <t>CC-1 / Cursor</t>
         </is>
       </c>
       <c r="I143" s="3" t="inlineStr">
@@ -8340,14 +8352,14 @@
           <t>443.257-D</t>
         </is>
       </c>
-      <c r="J143" s="4" t="inlineStr">
-        <is>
-          <t>DONE-LIVE</t>
+      <c r="J143" s="7" t="inlineStr">
+        <is>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="K143" s="3" t="inlineStr">
         <is>
-          <t>Side panel | Center toggle live 10-23 5:19 PM</t>
+          <t>not re-verified since audit</t>
         </is>
       </c>
       <c r="L143" s="3" t="inlineStr">
@@ -8367,32 +8379,32 @@
       </c>
       <c r="C144" s="3" t="inlineStr">
         <is>
-          <t>Dispatch › Load Costs › Pickup / delivery cells</t>
+          <t>Dispatch › Book Load › Stop fields</t>
         </is>
       </c>
       <c r="D144" s="3" t="inlineStr">
         <is>
-          <t>D025: Dates display M/D/YY</t>
+          <t>D023: Both ZIP controls measured 28px high × 381.33px wide</t>
         </is>
       </c>
       <c r="E144" s="3" t="inlineStr">
         <is>
-          <t>inline: Load Costs</t>
+          <t>inline: Book Load</t>
         </is>
       </c>
       <c r="F144" s="3" t="inlineStr">
         <is>
-          <t>class D</t>
+          <t>class I</t>
         </is>
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t>MM/DD/YYYY</t>
+          <t>ZIP 32px high × 88px wide</t>
         </is>
       </c>
       <c r="H144" s="3" t="inlineStr">
         <is>
-          <t>Cursor</t>
+          <t>Cursor / CC-3</t>
         </is>
       </c>
       <c r="I144" s="3" t="inlineStr">
@@ -8400,14 +8412,14 @@
           <t>443.257-D</t>
         </is>
       </c>
-      <c r="J144" s="7" t="inlineStr">
-        <is>
-          <t>OPEN</t>
+      <c r="J144" s="4" t="inlineStr">
+        <is>
+          <t>DONE-LIVE</t>
         </is>
       </c>
       <c r="K144" s="3" t="inlineStr">
         <is>
-          <t>not re-verified since audit</t>
+          <t>#27294 ZIP 88px</t>
         </is>
       </c>
       <c r="L144" s="3" t="inlineStr">
@@ -8427,32 +8439,32 @@
       </c>
       <c r="C145" s="3" t="inlineStr">
         <is>
-          <t>Dispatch › Load Costs › Driver names</t>
+          <t>Dispatch › Book Load › Presentation</t>
         </is>
       </c>
       <c r="D145" s="3" t="inlineStr">
         <is>
-          <t>D026: All-uppercase names</t>
+          <t>D024: Long A–E form; no Side panel / Center toggle or five-step flow present</t>
         </is>
       </c>
       <c r="E145" s="3" t="inlineStr">
         <is>
-          <t>inline: Load Costs</t>
+          <t>inline: Book Load</t>
         </is>
       </c>
       <c r="F145" s="3" t="inlineStr">
         <is>
-          <t>class N</t>
+          <t>class V</t>
         </is>
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
-          <t>Full proper-case names</t>
+          <t>Same component with side/center toggle and specified five-step layout</t>
         </is>
       </c>
       <c r="H145" s="3" t="inlineStr">
         <is>
-          <t>CC-1 / Cursor</t>
+          <t>Cursor / CC-3</t>
         </is>
       </c>
       <c r="I145" s="3" t="inlineStr">
@@ -8460,14 +8472,14 @@
           <t>443.257-D</t>
         </is>
       </c>
-      <c r="J145" s="7" t="inlineStr">
-        <is>
-          <t>OPEN</t>
+      <c r="J145" s="4" t="inlineStr">
+        <is>
+          <t>DONE-LIVE</t>
         </is>
       </c>
       <c r="K145" s="3" t="inlineStr">
         <is>
-          <t>not re-verified since audit</t>
+          <t>Side panel | Center toggle live 10-23 5:19 PM</t>
         </is>
       </c>
       <c r="L145" s="3" t="inlineStr">
@@ -8487,12 +8499,12 @@
       </c>
       <c r="C146" s="3" t="inlineStr">
         <is>
-          <t>Dispatch › Load Costs › Settlement/Tour link</t>
+          <t>Dispatch › Load Costs › Pickup / delivery cells</t>
         </is>
       </c>
       <c r="D146" s="3" t="inlineStr">
         <is>
-          <t>D027: Several links have only an em dash as label despite a settlement destination</t>
+          <t>D025: Dates display M/D/YY</t>
         </is>
       </c>
       <c r="E146" s="3" t="inlineStr">
@@ -8502,17 +8514,17 @@
       </c>
       <c r="F146" s="3" t="inlineStr">
         <is>
-          <t>class N</t>
+          <t>class D</t>
         </is>
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>Resolve human-readable settlement/tour display identifier</t>
+          <t>MM/DD/YYYY</t>
         </is>
       </c>
       <c r="H146" s="3" t="inlineStr">
         <is>
-          <t>CC-1 / Cursor</t>
+          <t>Cursor</t>
         </is>
       </c>
       <c r="I146" s="3" t="inlineStr">
@@ -8547,32 +8559,32 @@
       </c>
       <c r="C147" s="3" t="inlineStr">
         <is>
-          <t>Tasks › Create Task › Inputs</t>
+          <t>Dispatch › Load Costs › Driver names</t>
         </is>
       </c>
       <c r="D147" s="3" t="inlineStr">
         <is>
-          <t>D028: Eleven single-line inputs measured 38px high; textarea excluded</t>
+          <t>D026: All-uppercase names</t>
         </is>
       </c>
       <c r="E147" s="3" t="inlineStr">
         <is>
-          <t>inline: Create Task</t>
+          <t>inline: Load Costs</t>
         </is>
       </c>
       <c r="F147" s="3" t="inlineStr">
         <is>
-          <t>class I</t>
+          <t>class N</t>
         </is>
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
-          <t>Single-line inputs 32px</t>
+          <t>Full proper-case names</t>
         </is>
       </c>
       <c r="H147" s="3" t="inlineStr">
         <is>
-          <t>Cursor</t>
+          <t>CC-1 / Cursor</t>
         </is>
       </c>
       <c r="I147" s="3" t="inlineStr">
@@ -8607,32 +8619,32 @@
       </c>
       <c r="C148" s="3" t="inlineStr">
         <is>
-          <t>Tasks › Exceptions › Since column</t>
+          <t>Dispatch › Load Costs › Settlement/Tour link</t>
         </is>
       </c>
       <c r="D148" s="3" t="inlineStr">
         <is>
-          <t>D029: ISO YYYY-MM-DD rendered</t>
+          <t>D027: Several links have only an em dash as label despite a settlement destination</t>
         </is>
       </c>
       <c r="E148" s="3" t="inlineStr">
         <is>
-          <t>pending: DOM</t>
+          <t>inline: Load Costs</t>
         </is>
       </c>
       <c r="F148" s="3" t="inlineStr">
         <is>
-          <t>class D</t>
+          <t>class N</t>
         </is>
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>MM/DD/YYYY</t>
+          <t>Resolve human-readable settlement/tour display identifier</t>
         </is>
       </c>
       <c r="H148" s="3" t="inlineStr">
         <is>
-          <t>Cursor</t>
+          <t>CC-1 / Cursor</t>
         </is>
       </c>
       <c r="I148" s="3" t="inlineStr">
@@ -8667,27 +8679,27 @@
       </c>
       <c r="C149" s="3" t="inlineStr">
         <is>
-          <t>Driver Hub › Driver Scheduler › Date range</t>
+          <t>Tasks › Create Task › Inputs</t>
         </is>
       </c>
       <c r="D149" s="3" t="inlineStr">
         <is>
-          <t>D030: Subtitle uses YYYY-MM-DD; grid uses MON-DD</t>
+          <t>D028: Eleven single-line inputs measured 38px high; textarea excluded</t>
         </is>
       </c>
       <c r="E149" s="3" t="inlineStr">
         <is>
-          <t>pending: DOM</t>
+          <t>inline: Create Task</t>
         </is>
       </c>
       <c r="F149" s="3" t="inlineStr">
         <is>
-          <t>class D</t>
+          <t>class I</t>
         </is>
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
-          <t>MM/DD/YYYY under explicit round requirement</t>
+          <t>Single-line inputs 32px</t>
         </is>
       </c>
       <c r="H149" s="3" t="inlineStr">
@@ -8727,12 +8739,12 @@
       </c>
       <c r="C150" s="3" t="inlineStr">
         <is>
-          <t>Driver Hub › Driver Scheduler › Driver cells</t>
+          <t>Tasks › Exceptions › Since column</t>
         </is>
       </c>
       <c r="D150" s="3" t="inlineStr">
         <is>
-          <t>D031: All-uppercase and inconsistent surname casing</t>
+          <t>D029: ISO YYYY-MM-DD rendered</t>
         </is>
       </c>
       <c r="E150" s="3" t="inlineStr">
@@ -8742,17 +8754,17 @@
       </c>
       <c r="F150" s="3" t="inlineStr">
         <is>
-          <t>class N</t>
+          <t>class D</t>
         </is>
       </c>
       <c r="G150" s="3" t="inlineStr">
         <is>
-          <t>Full proper-case names</t>
+          <t>MM/DD/YYYY</t>
         </is>
       </c>
       <c r="H150" s="3" t="inlineStr">
         <is>
-          <t>CC-1 / Cursor</t>
+          <t>Cursor</t>
         </is>
       </c>
       <c r="I150" s="3" t="inlineStr">
@@ -8787,27 +8799,27 @@
       </c>
       <c r="C151" s="3" t="inlineStr">
         <is>
-          <t>Driver Hub › Driver Scheduler › Assign Temp Cover</t>
+          <t>Driver Hub › Driver Scheduler › Date range</t>
         </is>
       </c>
       <c r="D151" s="3" t="inlineStr">
         <is>
-          <t>D032: Five single-line inputs measured 38px high; pickers about 2,477px wide and dates about 1,203px</t>
+          <t>D030: Subtitle uses YYYY-MM-DD; grid uses MON-DD</t>
         </is>
       </c>
       <c r="E151" s="3" t="inlineStr">
         <is>
-          <t>pending: screenshot timed out</t>
+          <t>pending: DOM</t>
         </is>
       </c>
       <c r="F151" s="3" t="inlineStr">
         <is>
-          <t>class I</t>
+          <t>class D</t>
         </is>
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
-          <t>32px inputs and content-appropriate form widths</t>
+          <t>MM/DD/YYYY under explicit round requirement</t>
         </is>
       </c>
       <c r="H151" s="3" t="inlineStr">
@@ -8847,32 +8859,32 @@
       </c>
       <c r="C152" s="3" t="inlineStr">
         <is>
-          <t>Maintenance › Home / Fleet Table › Money tiles</t>
+          <t>Driver Hub › Driver Scheduler › Driver cells</t>
         </is>
       </c>
       <c r="D152" s="3" t="inlineStr">
         <is>
-          <t>D033: MTD Cost, Open $ and severe-repair total omit cents</t>
+          <t>D031: All-uppercase and inconsistent surname casing</t>
         </is>
       </c>
       <c r="E152" s="3" t="inlineStr">
         <is>
-          <t>inline: Maintenance Home</t>
+          <t>pending: DOM</t>
         </is>
       </c>
       <c r="F152" s="3" t="inlineStr">
         <is>
-          <t>class M</t>
+          <t>class N</t>
         </is>
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>Currency always two decimal places</t>
+          <t>Full proper-case names</t>
         </is>
       </c>
       <c r="H152" s="3" t="inlineStr">
         <is>
-          <t>Cursor</t>
+          <t>CC-1 / Cursor</t>
         </is>
       </c>
       <c r="I152" s="3" t="inlineStr">
@@ -8907,17 +8919,17 @@
       </c>
       <c r="C153" s="3" t="inlineStr">
         <is>
-          <t>Maintenance › Create Work Order › Drawer inputs</t>
+          <t>Driver Hub › Driver Scheduler › Assign Temp Cover</t>
         </is>
       </c>
       <c r="D153" s="3" t="inlineStr">
         <is>
-          <t>D034: Visible single-line inputs measured 38px; customer picker about 2,408px wide, open-date input about 766px</t>
+          <t>D032: Five single-line inputs measured 38px high; pickers about 2,477px wide and dates about 1,203px</t>
         </is>
       </c>
       <c r="E153" s="3" t="inlineStr">
         <is>
-          <t>pending: measured DOM</t>
+          <t>pending: screenshot timed out</t>
         </is>
       </c>
       <c r="F153" s="3" t="inlineStr">
@@ -8927,7 +8939,7 @@
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
-          <t>32px inputs; dates 150px; content-appropriate widths</t>
+          <t>32px inputs and content-appropriate form widths</t>
         </is>
       </c>
       <c r="H153" s="3" t="inlineStr">
@@ -8967,27 +8979,27 @@
       </c>
       <c r="C154" s="3" t="inlineStr">
         <is>
-          <t>Maintenance › Active WOs › Table headers</t>
+          <t>Maintenance › Home / Fleet Table › Money tiles</t>
         </is>
       </c>
       <c r="D154" s="3" t="inlineStr">
         <is>
-          <t>D035: Load, Driver, Vendor, Bill, JE and Timing headers have no sorting button, unlike adjacent headers</t>
+          <t>D033: MTD Cost, Open $ and severe-repair total omit cents</t>
         </is>
       </c>
       <c r="E154" s="3" t="inlineStr">
         <is>
-          <t>pending: DOM</t>
+          <t>inline: Maintenance Home</t>
         </is>
       </c>
       <c r="F154" s="3" t="inlineStr">
         <is>
-          <t>class T</t>
+          <t>class M</t>
         </is>
       </c>
       <c r="G154" s="3" t="inlineStr">
         <is>
-          <t>Sortable data columns</t>
+          <t>Currency always two decimal places</t>
         </is>
       </c>
       <c r="H154" s="3" t="inlineStr">
@@ -9027,32 +9039,32 @@
       </c>
       <c r="C155" s="3" t="inlineStr">
         <is>
-          <t>Safety › Hours &amp; Fatigue › Driver roster</t>
+          <t>Maintenance › Create Work Order › Drawer inputs</t>
         </is>
       </c>
       <c r="D155" s="3" t="inlineStr">
         <is>
-          <t>D036: Mixed proper-case and all-uppercase driver names</t>
+          <t>D034: Visible single-line inputs measured 38px; customer picker about 2,408px wide, open-date input about 766px</t>
         </is>
       </c>
       <c r="E155" s="3" t="inlineStr">
         <is>
-          <t>pending: DOM</t>
+          <t>pending: measured DOM</t>
         </is>
       </c>
       <c r="F155" s="3" t="inlineStr">
         <is>
-          <t>class N</t>
+          <t>class I</t>
         </is>
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
-          <t>Full proper-case display with exceptions</t>
+          <t>32px inputs; dates 150px; content-appropriate widths</t>
         </is>
       </c>
       <c r="H155" s="3" t="inlineStr">
         <is>
-          <t>CC-1 / Cursor</t>
+          <t>Cursor</t>
         </is>
       </c>
       <c r="I155" s="3" t="inlineStr">
@@ -9087,27 +9099,27 @@
       </c>
       <c r="C156" s="3" t="inlineStr">
         <is>
-          <t>Safety › Hours &amp; Fatigue › Create HOS Violation</t>
+          <t>Maintenance › Active WOs › Table headers</t>
         </is>
       </c>
       <c r="D156" s="3" t="inlineStr">
         <is>
-          <t>D037: Seven visible inputs measured 38px high</t>
+          <t>D035: Load, Driver, Vendor, Bill, JE and Timing headers have no sorting button, unlike adjacent headers</t>
         </is>
       </c>
       <c r="E156" s="3" t="inlineStr">
         <is>
-          <t>pending: measured DOM</t>
+          <t>pending: DOM</t>
         </is>
       </c>
       <c r="F156" s="3" t="inlineStr">
         <is>
-          <t>class I</t>
+          <t>class T</t>
         </is>
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
-          <t>32px single-line inputs</t>
+          <t>Sortable data columns</t>
         </is>
       </c>
       <c r="H156" s="3" t="inlineStr">
@@ -9147,12 +9159,12 @@
       </c>
       <c r="C157" s="3" t="inlineStr">
         <is>
-          <t>Compliance › Filings / Overview › Driver labels</t>
+          <t>Safety › Hours &amp; Fatigue › Driver roster</t>
         </is>
       </c>
       <c r="D157" s="3" t="inlineStr">
         <is>
-          <t>D038: Mixed proper-case and uppercase driver labels in populated tables</t>
+          <t>D036: Mixed proper-case and all-uppercase driver names</t>
         </is>
       </c>
       <c r="E157" s="3" t="inlineStr">
@@ -9207,12 +9219,12 @@
       </c>
       <c r="C158" s="3" t="inlineStr">
         <is>
-          <t>Driver Profile › Create Driver › Identity step</t>
+          <t>Safety › Hours &amp; Fatigue › Create HOS Violation</t>
         </is>
       </c>
       <c r="D158" s="3" t="inlineStr">
         <is>
-          <t>D039: Fifteen visible inputs measured 38px; CDL state about 199px wide</t>
+          <t>D037: Seven visible inputs measured 38px high</t>
         </is>
       </c>
       <c r="E158" s="3" t="inlineStr">
@@ -9227,7 +9239,7 @@
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
-          <t>Inputs 32px; state 64px</t>
+          <t>32px single-line inputs</t>
         </is>
       </c>
       <c r="H158" s="3" t="inlineStr">
@@ -9267,32 +9279,32 @@
       </c>
       <c r="C159" s="3" t="inlineStr">
         <is>
-          <t>Fleet › Create Trailer › Identity drawer</t>
+          <t>Compliance › Filings / Overview › Driver labels</t>
         </is>
       </c>
       <c r="D159" s="3" t="inlineStr">
         <is>
-          <t>D040: Seven visible inputs measured 38px high</t>
+          <t>D038: Mixed proper-case and uppercase driver labels in populated tables</t>
         </is>
       </c>
       <c r="E159" s="3" t="inlineStr">
         <is>
-          <t>pending: measured DOM</t>
+          <t>pending: DOM</t>
         </is>
       </c>
       <c r="F159" s="3" t="inlineStr">
         <is>
-          <t>class I</t>
+          <t>class N</t>
         </is>
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
-          <t>Inputs 32px</t>
+          <t>Full proper-case display with exceptions</t>
         </is>
       </c>
       <c r="H159" s="3" t="inlineStr">
         <is>
-          <t>Cursor</t>
+          <t>CC-1 / Cursor</t>
         </is>
       </c>
       <c r="I159" s="3" t="inlineStr">
@@ -9327,12 +9339,12 @@
       </c>
       <c r="C160" s="3" t="inlineStr">
         <is>
-          <t>Insurance › Policies › Create policy step 1</t>
+          <t>Driver Profile › Create Driver › Identity step</t>
         </is>
       </c>
       <c r="D160" s="3" t="inlineStr">
         <is>
-          <t>D041: Eight visible inputs measured 38px high</t>
+          <t>D039: Fifteen visible inputs measured 38px; CDL state about 199px wide</t>
         </is>
       </c>
       <c r="E160" s="3" t="inlineStr">
@@ -9347,7 +9359,7 @@
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t>Inputs 32px</t>
+          <t>Inputs 32px; state 64px</t>
         </is>
       </c>
       <c r="H160" s="3" t="inlineStr">
@@ -9387,27 +9399,27 @@
       </c>
       <c r="C161" s="3" t="inlineStr">
         <is>
-          <t>Cash Flow › Projected Auto › Seven-day outlook</t>
+          <t>Fleet › Create Trailer › Identity drawer</t>
         </is>
       </c>
       <c r="D161" s="3" t="inlineStr">
         <is>
-          <t>D042: Currency abbreviated with k suffix and zero shown without cents</t>
+          <t>D040: Seven visible inputs measured 38px high</t>
         </is>
       </c>
       <c r="E161" s="3" t="inlineStr">
         <is>
-          <t>pending: DOM</t>
+          <t>pending: measured DOM</t>
         </is>
       </c>
       <c r="F161" s="3" t="inlineStr">
         <is>
-          <t>class M</t>
+          <t>class I</t>
         </is>
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
-          <t>Full currency with two decimals</t>
+          <t>Inputs 32px</t>
         </is>
       </c>
       <c r="H161" s="3" t="inlineStr">
@@ -9427,7 +9439,7 @@
       </c>
       <c r="K161" s="3" t="inlineStr">
         <is>
-          <t>still +15,386 no cents 10-23 5:10 PM</t>
+          <t>not re-verified since audit</t>
         </is>
       </c>
       <c r="L161" s="3" t="inlineStr">
@@ -9447,27 +9459,27 @@
       </c>
       <c r="C162" s="3" t="inlineStr">
         <is>
-          <t>Cash Flow › Projected / Rolling / Manual › Date labels and cells</t>
+          <t>Insurance › Policies › Create policy step 1</t>
         </is>
       </c>
       <c r="D162" s="3" t="inlineStr">
         <is>
-          <t>D043: Day labels and invoice/due cells omit year and use month names</t>
+          <t>D041: Eight visible inputs measured 38px high</t>
         </is>
       </c>
       <c r="E162" s="3" t="inlineStr">
         <is>
-          <t>pending: DOM</t>
+          <t>pending: measured DOM</t>
         </is>
       </c>
       <c r="F162" s="3" t="inlineStr">
         <is>
-          <t>class D</t>
+          <t>class I</t>
         </is>
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t>MM/DD/YYYY for business dates</t>
+          <t>Inputs 32px</t>
         </is>
       </c>
       <c r="H162" s="3" t="inlineStr">
@@ -9507,12 +9519,12 @@
       </c>
       <c r="C163" s="3" t="inlineStr">
         <is>
-          <t>Accounting › Home › Settlement / transaction links</t>
+          <t>Cash Flow › Projected Auto › Seven-day outlook</t>
         </is>
       </c>
       <c r="D163" s="3" t="inlineStr">
         <is>
-          <t>D044: Driver/vendor names still all-uppercase</t>
+          <t>D042: Currency abbreviated with k suffix and zero shown without cents</t>
         </is>
       </c>
       <c r="E163" s="3" t="inlineStr">
@@ -9522,17 +9534,17 @@
       </c>
       <c r="F163" s="3" t="inlineStr">
         <is>
-          <t>class N</t>
+          <t>class M</t>
         </is>
       </c>
       <c r="G163" s="3" t="inlineStr">
         <is>
-          <t>Proper-case full names with exceptions</t>
+          <t>Full currency with two decimals</t>
         </is>
       </c>
       <c r="H163" s="3" t="inlineStr">
         <is>
-          <t>CC-1 / Cursor</t>
+          <t>Cursor</t>
         </is>
       </c>
       <c r="I163" s="3" t="inlineStr">
@@ -9547,7 +9559,7 @@
       </c>
       <c r="K163" s="3" t="inlineStr">
         <is>
-          <t>not re-verified since audit</t>
+          <t>still +15,386 no cents 10-23 5:10 PM</t>
         </is>
       </c>
       <c r="L163" s="3" t="inlineStr">
@@ -9567,12 +9579,12 @@
       </c>
       <c r="C164" s="3" t="inlineStr">
         <is>
-          <t>Banking › Home › Drift alert as-of</t>
+          <t>Cash Flow › Projected / Rolling / Manual › Date labels and cells</t>
         </is>
       </c>
       <c r="D164" s="3" t="inlineStr">
         <is>
-          <t>D045: Raw ISO timestamp rendered, including T and Z</t>
+          <t>D043: Day labels and invoice/due cells omit year and use month names</t>
         </is>
       </c>
       <c r="E164" s="3" t="inlineStr">
@@ -9587,7 +9599,7 @@
       </c>
       <c r="G164" s="3" t="inlineStr">
         <is>
-          <t>Local business date MM/DD/YYYY; readable time if needed</t>
+          <t>MM/DD/YYYY for business dates</t>
         </is>
       </c>
       <c r="H164" s="3" t="inlineStr">
@@ -9627,12 +9639,12 @@
       </c>
       <c r="C165" s="3" t="inlineStr">
         <is>
-          <t>Banking › Home › Drift account label</t>
+          <t>Accounting › Home › Settlement / transaction links</t>
         </is>
       </c>
       <c r="D165" s="3" t="inlineStr">
         <is>
-          <t>D046: Several alerts show only generic Account rather than the account display name</t>
+          <t>D044: Driver/vendor names still all-uppercase</t>
         </is>
       </c>
       <c r="E165" s="3" t="inlineStr">
@@ -9647,7 +9659,7 @@
       </c>
       <c r="G165" s="3" t="inlineStr">
         <is>
-          <t>Resolve full account display name</t>
+          <t>Proper-case full names with exceptions</t>
         </is>
       </c>
       <c r="H165" s="3" t="inlineStr">
@@ -9687,12 +9699,12 @@
       </c>
       <c r="C166" s="3" t="inlineStr">
         <is>
-          <t>Factoring › Home › Ready-to-factor customers</t>
+          <t>Banking › Home › Drift alert as-of</t>
         </is>
       </c>
       <c r="D166" s="3" t="inlineStr">
         <is>
-          <t>D047: All-uppercase customer names displayed</t>
+          <t>D045: Raw ISO timestamp rendered, including T and Z</t>
         </is>
       </c>
       <c r="E166" s="3" t="inlineStr">
@@ -9702,17 +9714,17 @@
       </c>
       <c r="F166" s="3" t="inlineStr">
         <is>
-          <t>class N</t>
+          <t>class D</t>
         </is>
       </c>
       <c r="G166" s="3" t="inlineStr">
         <is>
-          <t>Proper-case names honoring acronym exceptions</t>
+          <t>Local business date MM/DD/YYYY; readable time if needed</t>
         </is>
       </c>
       <c r="H166" s="3" t="inlineStr">
         <is>
-          <t>CC-1 / Cursor</t>
+          <t>Cursor</t>
         </is>
       </c>
       <c r="I166" s="3" t="inlineStr">
@@ -9747,32 +9759,32 @@
       </c>
       <c r="C167" s="3" t="inlineStr">
         <is>
-          <t>Customers › Create Customer › Billing address</t>
+          <t>Banking › Home › Drift account label</t>
         </is>
       </c>
       <c r="D167" s="3" t="inlineStr">
         <is>
-          <t>D048: State and ZIP each measure 38px high and 209.33px wide</t>
+          <t>D046: Several alerts show only generic Account rather than the account display name</t>
         </is>
       </c>
       <c r="E167" s="3" t="inlineStr">
         <is>
-          <t>pending: measured DOM</t>
+          <t>pending: DOM</t>
         </is>
       </c>
       <c r="F167" s="3" t="inlineStr">
         <is>
-          <t>class I</t>
+          <t>class N</t>
         </is>
       </c>
       <c r="G167" s="3" t="inlineStr">
         <is>
-          <t>32px high; state 64px and ZIP 88px wide</t>
+          <t>Resolve full account display name</t>
         </is>
       </c>
       <c r="H167" s="3" t="inlineStr">
         <is>
-          <t>Cursor</t>
+          <t>CC-1 / Cursor</t>
         </is>
       </c>
       <c r="I167" s="3" t="inlineStr">
@@ -9807,12 +9819,12 @@
       </c>
       <c r="C168" s="3" t="inlineStr">
         <is>
-          <t>Customers › Directory › Customer display names</t>
+          <t>Factoring › Home › Ready-to-factor customers</t>
         </is>
       </c>
       <c r="D168" s="3" t="inlineStr">
         <is>
-          <t>D049: Mixed uppercase and proper-case customer labels</t>
+          <t>D047: All-uppercase customer names displayed</t>
         </is>
       </c>
       <c r="E168" s="3" t="inlineStr">
@@ -9827,7 +9839,7 @@
       </c>
       <c r="G168" s="3" t="inlineStr">
         <is>
-          <t>Proper-case display honoring acronym exceptions</t>
+          <t>Proper-case names honoring acronym exceptions</t>
         </is>
       </c>
       <c r="H168" s="3" t="inlineStr">
@@ -9867,12 +9879,12 @@
       </c>
       <c r="C169" s="3" t="inlineStr">
         <is>
-          <t>Inventory › Create part › Unit cost</t>
+          <t>Customers › Create Customer › Billing address</t>
         </is>
       </c>
       <c r="D169" s="3" t="inlineStr">
         <is>
-          <t>D050: Money input measures 28px high</t>
+          <t>D048: State and ZIP each measure 38px high and 209.33px wide</t>
         </is>
       </c>
       <c r="E169" s="3" t="inlineStr">
@@ -9887,7 +9899,7 @@
       </c>
       <c r="G169" s="3" t="inlineStr">
         <is>
-          <t>Single-line input 32px high</t>
+          <t>32px high; state 64px and ZIP 88px wide</t>
         </is>
       </c>
       <c r="H169" s="3" t="inlineStr">
@@ -9927,32 +9939,32 @@
       </c>
       <c r="C170" s="3" t="inlineStr">
         <is>
-          <t>425C › Profiles &amp; Defaults › Company Name</t>
+          <t>Customers › Directory › Customer display names</t>
         </is>
       </c>
       <c r="D170" s="3" t="inlineStr">
         <is>
-          <t>D051: Input measures 30.67px high</t>
+          <t>D049: Mixed uppercase and proper-case customer labels</t>
         </is>
       </c>
       <c r="E170" s="3" t="inlineStr">
         <is>
-          <t>pending: measured DOM</t>
+          <t>pending: DOM</t>
         </is>
       </c>
       <c r="F170" s="3" t="inlineStr">
         <is>
-          <t>class I</t>
+          <t>class N</t>
         </is>
       </c>
       <c r="G170" s="3" t="inlineStr">
         <is>
-          <t>Single-line input 32px</t>
+          <t>Proper-case display honoring acronym exceptions</t>
         </is>
       </c>
       <c r="H170" s="3" t="inlineStr">
         <is>
-          <t>Cursor</t>
+          <t>CC-1 / Cursor</t>
         </is>
       </c>
       <c r="I170" s="3" t="inlineStr">
@@ -9987,27 +9999,27 @@
       </c>
       <c r="C171" s="3" t="inlineStr">
         <is>
-          <t>425C › History › Filed timestamp</t>
+          <t>Inventory › Create part › Unit cost</t>
         </is>
       </c>
       <c r="D171" s="3" t="inlineStr">
         <is>
-          <t>D052: Month/day rendered without zero padding</t>
+          <t>D050: Money input measures 28px high</t>
         </is>
       </c>
       <c r="E171" s="3" t="inlineStr">
         <is>
-          <t>pending: DOM</t>
+          <t>pending: measured DOM</t>
         </is>
       </c>
       <c r="F171" s="3" t="inlineStr">
         <is>
-          <t>class D</t>
+          <t>class I</t>
         </is>
       </c>
       <c r="G171" s="3" t="inlineStr">
         <is>
-          <t>MM/DD/YYYY plus readable local time</t>
+          <t>Single-line input 32px high</t>
         </is>
       </c>
       <c r="H171" s="3" t="inlineStr">
@@ -10047,32 +10059,32 @@
       </c>
       <c r="C172" s="3" t="inlineStr">
         <is>
-          <t>Lists › Names Master › Name column</t>
+          <t>425C › Profiles &amp; Defaults › Company Name</t>
         </is>
       </c>
       <c r="D172" s="3" t="inlineStr">
         <is>
-          <t>D053: Mixed uppercase and proper-case customer names</t>
+          <t>D051: Input measures 30.67px high</t>
         </is>
       </c>
       <c r="E172" s="3" t="inlineStr">
         <is>
-          <t>pending: DOM</t>
+          <t>pending: measured DOM</t>
         </is>
       </c>
       <c r="F172" s="3" t="inlineStr">
         <is>
-          <t>class N</t>
+          <t>class I</t>
         </is>
       </c>
       <c r="G172" s="3" t="inlineStr">
         <is>
-          <t>Proper-case display honoring exceptions</t>
+          <t>Single-line input 32px</t>
         </is>
       </c>
       <c r="H172" s="3" t="inlineStr">
         <is>
-          <t>CC-1 / Cursor</t>
+          <t>Cursor</t>
         </is>
       </c>
       <c r="I172" s="3" t="inlineStr">
@@ -10107,27 +10119,27 @@
       </c>
       <c r="C173" s="3" t="inlineStr">
         <is>
-          <t>Reports › Custom report builder › Report name</t>
+          <t>425C › History › Filed timestamp</t>
         </is>
       </c>
       <c r="D173" s="3" t="inlineStr">
         <is>
-          <t>D054: Input measures 26.67px high and 1156.38px wide</t>
+          <t>D052: Month/day rendered without zero padding</t>
         </is>
       </c>
       <c r="E173" s="3" t="inlineStr">
         <is>
-          <t>pending: measured DOM</t>
+          <t>pending: DOM</t>
         </is>
       </c>
       <c r="F173" s="3" t="inlineStr">
         <is>
-          <t>class I</t>
+          <t>class D</t>
         </is>
       </c>
       <c r="G173" s="3" t="inlineStr">
         <is>
-          <t>Single-line input 32px; content-appropriate width</t>
+          <t>MM/DD/YYYY plus readable local time</t>
         </is>
       </c>
       <c r="H173" s="3" t="inlineStr">
@@ -10167,12 +10179,12 @@
       </c>
       <c r="C174" s="3" t="inlineStr">
         <is>
-          <t>Docs › All Entities › Entity names</t>
+          <t>Lists › Names Master › Name column</t>
         </is>
       </c>
       <c r="D174" s="3" t="inlineStr">
         <is>
-          <t>D055: Mixed uppercase and proper-case driver names</t>
+          <t>D053: Mixed uppercase and proper-case customer names</t>
         </is>
       </c>
       <c r="E174" s="3" t="inlineStr">
@@ -10187,7 +10199,7 @@
       </c>
       <c r="G174" s="3" t="inlineStr">
         <is>
-          <t>Full proper-case display</t>
+          <t>Proper-case display honoring exceptions</t>
         </is>
       </c>
       <c r="H174" s="3" t="inlineStr">
@@ -10227,12 +10239,12 @@
       </c>
       <c r="C175" s="3" t="inlineStr">
         <is>
-          <t>Docs › Upload Document › Category/entity/date inputs</t>
+          <t>Reports › Custom report builder › Report name</t>
         </is>
       </c>
       <c r="D175" s="3" t="inlineStr">
         <is>
-          <t>D056: Four visible inputs 38px; date fields about 1201px wide</t>
+          <t>D054: Input measures 26.67px high and 1156.38px wide</t>
         </is>
       </c>
       <c r="E175" s="3" t="inlineStr">
@@ -10247,7 +10259,7 @@
       </c>
       <c r="G175" s="3" t="inlineStr">
         <is>
-          <t>Inputs 32px; date widths fit MM/DD/YYYY</t>
+          <t>Single-line input 32px; content-appropriate width</t>
         </is>
       </c>
       <c r="H175" s="3" t="inlineStr">
@@ -10287,12 +10299,12 @@
       </c>
       <c r="C176" s="3" t="inlineStr">
         <is>
-          <t>Users › Master-detail › User labels</t>
+          <t>Docs › All Entities › Entity names</t>
         </is>
       </c>
       <c r="D176" s="3" t="inlineStr">
         <is>
-          <t>D057: Repeated generic User labels and mixed name capitalization</t>
+          <t>D055: Mixed uppercase and proper-case driver names</t>
         </is>
       </c>
       <c r="E176" s="3" t="inlineStr">
@@ -10307,7 +10319,7 @@
       </c>
       <c r="G176" s="3" t="inlineStr">
         <is>
-          <t>Resolved full names with proper-case display</t>
+          <t>Full proper-case display</t>
         </is>
       </c>
       <c r="H176" s="3" t="inlineStr">
@@ -10347,12 +10359,12 @@
       </c>
       <c r="C177" s="3" t="inlineStr">
         <is>
-          <t>Users › Create User › Name/email/role</t>
+          <t>Docs › Upload Document › Category/entity/date inputs</t>
         </is>
       </c>
       <c r="D177" s="3" t="inlineStr">
         <is>
-          <t>D058: Three visible inputs 38px high</t>
+          <t>D056: Four visible inputs 38px; date fields about 1201px wide</t>
         </is>
       </c>
       <c r="E177" s="3" t="inlineStr">
@@ -10367,7 +10379,7 @@
       </c>
       <c r="G177" s="3" t="inlineStr">
         <is>
-          <t>Single-line inputs 32px</t>
+          <t>Inputs 32px; date widths fit MM/DD/YYYY</t>
         </is>
       </c>
       <c r="H177" s="3" t="inlineStr">
@@ -10407,12 +10419,12 @@
       </c>
       <c r="C178" s="3" t="inlineStr">
         <is>
-          <t>Program › Scenario tracker › Certification timestamp</t>
+          <t>Users › Master-detail › User labels</t>
         </is>
       </c>
       <c r="D178" s="3" t="inlineStr">
         <is>
-          <t>D059: Raw database timestamp with fractional seconds and +00 timezone</t>
+          <t>D057: Repeated generic User labels and mixed name capitalization</t>
         </is>
       </c>
       <c r="E178" s="3" t="inlineStr">
@@ -10422,17 +10434,17 @@
       </c>
       <c r="F178" s="3" t="inlineStr">
         <is>
-          <t>class D</t>
+          <t>class N</t>
         </is>
       </c>
       <c r="G178" s="3" t="inlineStr">
         <is>
-          <t>MM/DD/YYYY and readable local time</t>
+          <t>Resolved full names with proper-case display</t>
         </is>
       </c>
       <c r="H178" s="3" t="inlineStr">
         <is>
-          <t>Cursor</t>
+          <t>CC-1 / Cursor</t>
         </is>
       </c>
       <c r="I178" s="3" t="inlineStr">
@@ -10467,27 +10479,27 @@
       </c>
       <c r="C179" s="3" t="inlineStr">
         <is>
-          <t>System › Transaction Health › Generated/document dates</t>
+          <t>Users › Create User › Name/email/role</t>
         </is>
       </c>
       <c r="D179" s="3" t="inlineStr">
         <is>
-          <t>D060: Month-name timestamps instead of MM/DD/YYYY</t>
+          <t>D058: Three visible inputs 38px high</t>
         </is>
       </c>
       <c r="E179" s="3" t="inlineStr">
         <is>
-          <t>pending: DOM</t>
+          <t>pending: measured DOM</t>
         </is>
       </c>
       <c r="F179" s="3" t="inlineStr">
         <is>
-          <t>class D</t>
+          <t>class I</t>
         </is>
       </c>
       <c r="G179" s="3" t="inlineStr">
         <is>
-          <t>MM/DD/YYYY with readable CT time</t>
+          <t>Single-line inputs 32px</t>
         </is>
       </c>
       <c r="H179" s="3" t="inlineStr">
@@ -10527,12 +10539,12 @@
       </c>
       <c r="C180" s="3" t="inlineStr">
         <is>
-          <t>System › Transaction Health › Journal-entry and bill-payment labels</t>
+          <t>Program › Scenario tracker › Certification timestamp</t>
         </is>
       </c>
       <c r="D180" s="3" t="inlineStr">
         <is>
-          <t>D061: Raw UUIDs are visible display labels</t>
+          <t>D059: Raw database timestamp with fractional seconds and +00 timezone</t>
         </is>
       </c>
       <c r="E180" s="3" t="inlineStr">
@@ -10542,12 +10554,12 @@
       </c>
       <c r="F180" s="3" t="inlineStr">
         <is>
-          <t>class N</t>
+          <t>class D</t>
         </is>
       </c>
       <c r="G180" s="3" t="inlineStr">
         <is>
-          <t>Human-readable display identifiers</t>
+          <t>MM/DD/YYYY and readable local time</t>
         </is>
       </c>
       <c r="H180" s="3" t="inlineStr">
@@ -10587,12 +10599,12 @@
       </c>
       <c r="C181" s="3" t="inlineStr">
         <is>
-          <t>System › Transaction Health › Wiring preview DR/CR</t>
+          <t>System › Transaction Health › Generated/document dates</t>
         </is>
       </c>
       <c r="D181" s="3" t="inlineStr">
         <is>
-          <t>D062: Currency values lack dollar signs</t>
+          <t>D060: Month-name timestamps instead of MM/DD/YYYY</t>
         </is>
       </c>
       <c r="E181" s="3" t="inlineStr">
@@ -10602,12 +10614,12 @@
       </c>
       <c r="F181" s="3" t="inlineStr">
         <is>
-          <t>class M</t>
+          <t>class D</t>
         </is>
       </c>
       <c r="G181" s="3" t="inlineStr">
         <is>
-          <t>Currency formatted $1,234.56</t>
+          <t>MM/DD/YYYY with readable CT time</t>
         </is>
       </c>
       <c r="H181" s="3" t="inlineStr">
@@ -10647,27 +10659,27 @@
       </c>
       <c r="C182" s="3" t="inlineStr">
         <is>
-          <t>Reports › Scheduled subscriptions › Add subscription timezone</t>
+          <t>System › Transaction Health › Journal-entry and bill-payment labels</t>
         </is>
       </c>
       <c r="D182" s="3" t="inlineStr">
         <is>
-          <t>D063: Input measures 30.67px high</t>
+          <t>D061: Raw UUIDs are visible display labels</t>
         </is>
       </c>
       <c r="E182" s="3" t="inlineStr">
         <is>
-          <t>pending: measured DOM</t>
+          <t>pending: DOM</t>
         </is>
       </c>
       <c r="F182" s="3" t="inlineStr">
         <is>
-          <t>class I</t>
+          <t>class N</t>
         </is>
       </c>
       <c r="G182" s="3" t="inlineStr">
         <is>
-          <t>Single-line inputs 32px</t>
+          <t>Human-readable display identifiers</t>
         </is>
       </c>
       <c r="H182" s="3" t="inlineStr">
@@ -10707,27 +10719,27 @@
       </c>
       <c r="C183" s="3" t="inlineStr">
         <is>
-          <t>Accounting › Create Manual JE › Step 2 Lines</t>
+          <t>System › Transaction Health › Wiring preview DR/CR</t>
         </is>
       </c>
       <c r="D183" s="3" t="inlineStr">
         <is>
-          <t>D064: Header summary renders `Date: 2026-10-22`, while Step 1 correctly shows `10/22/2026`</t>
+          <t>D062: Currency values lack dollar signs</t>
         </is>
       </c>
       <c r="E183" s="3" t="inlineStr">
         <is>
-          <t>inline: Manual JE Step 2</t>
+          <t>pending: DOM</t>
         </is>
       </c>
       <c r="F183" s="3" t="inlineStr">
         <is>
-          <t>class D</t>
+          <t>class M</t>
         </is>
       </c>
       <c r="G183" s="3" t="inlineStr">
         <is>
-          <t>Display dates consistently as MM/DD/YYYY</t>
+          <t>Currency formatted $1,234.56</t>
         </is>
       </c>
       <c r="H183" s="3" t="inlineStr">
@@ -10767,27 +10779,27 @@
       </c>
       <c r="C184" s="3" t="inlineStr">
         <is>
-          <t>Accounting › Create Manual JE › Step 2 Lines</t>
+          <t>Reports › Scheduled subscriptions › Add subscription timezone</t>
         </is>
       </c>
       <c r="D184" s="3" t="inlineStr">
         <is>
-          <t>D065: Class selector overlaps the adjacent Debit field; line controls overflow the drawer horizontally</t>
+          <t>D063: Input measures 30.67px high</t>
         </is>
       </c>
       <c r="E184" s="3" t="inlineStr">
         <is>
-          <t>inline: Manual JE Step 2</t>
+          <t>pending: measured DOM</t>
         </is>
       </c>
       <c r="F184" s="3" t="inlineStr">
         <is>
-          <t>class V</t>
+          <t>class I</t>
         </is>
       </c>
       <c r="G184" s="3" t="inlineStr">
         <is>
-          <t>Distinct aligned non-overlapping fields contained in the drawer</t>
+          <t>Single-line inputs 32px</t>
         </is>
       </c>
       <c r="H184" s="3" t="inlineStr">
@@ -10827,27 +10839,27 @@
       </c>
       <c r="C185" s="3" t="inlineStr">
         <is>
-          <t>Banking › Home / Record Transfer › Drawer footer</t>
+          <t>Accounting › Create Manual JE › Step 2 Lines</t>
         </is>
       </c>
       <c r="D185" s="3" t="inlineStr">
         <is>
-          <t>D066: Persistent alert stack renders above the open transfer drawer and obscures its bottom action area</t>
+          <t>D064: Header summary renders `Date: 2026-10-22`, while Step 1 correctly shows `10/22/2026`</t>
         </is>
       </c>
       <c r="E185" s="3" t="inlineStr">
         <is>
-          <t>inline: Record Transfer drawer</t>
+          <t>inline: Manual JE Step 2</t>
         </is>
       </c>
       <c r="F185" s="3" t="inlineStr">
         <is>
-          <t>class V</t>
+          <t>class D</t>
         </is>
       </c>
       <c r="G185" s="3" t="inlineStr">
         <is>
-          <t>Alerts must not obscure drawer controls; close/cancel remains accessible</t>
+          <t>Display dates consistently as MM/DD/YYYY</t>
         </is>
       </c>
       <c r="H185" s="3" t="inlineStr">
@@ -10887,27 +10899,27 @@
       </c>
       <c r="C186" s="3" t="inlineStr">
         <is>
-          <t>Accounting › Bills / Bill detail › Payments on this bill</t>
+          <t>Accounting › Create Manual JE › Step 2 Lines</t>
         </is>
       </c>
       <c r="D186" s="3" t="inlineStr">
         <is>
-          <t>D067: Two linked payments render as `Payment — not visible` rather than distinct display identifiers</t>
+          <t>D065: Class selector overlaps the adjacent Debit field; line controls overflow the drawer horizontally</t>
         </is>
       </c>
       <c r="E186" s="3" t="inlineStr">
         <is>
-          <t>observed Chrome AX</t>
+          <t>inline: Manual JE Step 2</t>
         </is>
       </c>
       <c r="F186" s="3" t="inlineStr">
         <is>
-          <t>class N</t>
+          <t>class V</t>
         </is>
       </c>
       <c r="G186" s="3" t="inlineStr">
         <is>
-          <t>Readable distinct payment identifiers; no UUID fallback</t>
+          <t>Distinct aligned non-overlapping fields contained in the drawer</t>
         </is>
       </c>
       <c r="H186" s="3" t="inlineStr">
@@ -10947,27 +10959,27 @@
       </c>
       <c r="C187" s="3" t="inlineStr">
         <is>
-          <t>Accounting › Bill detail › Journal Entity column</t>
+          <t>Banking › Home / Record Transfer › Drawer footer</t>
         </is>
       </c>
       <c r="D187" s="3" t="inlineStr">
         <is>
-          <t>D068: Five journal rows show raw UUID entity labels</t>
+          <t>D066: Persistent alert stack renders above the open transfer drawer and obscures its bottom action area</t>
         </is>
       </c>
       <c r="E187" s="3" t="inlineStr">
         <is>
-          <t>observed Chrome AX</t>
+          <t>inline: Record Transfer drawer</t>
         </is>
       </c>
       <c r="F187" s="3" t="inlineStr">
         <is>
-          <t>class N</t>
+          <t>class V</t>
         </is>
       </c>
       <c r="G187" s="3" t="inlineStr">
         <is>
-          <t>Resolve human-readable entity names</t>
+          <t>Alerts must not obscure drawer controls; close/cancel remains accessible</t>
         </is>
       </c>
       <c r="H187" s="3" t="inlineStr">
@@ -11007,12 +11019,12 @@
       </c>
       <c r="C188" s="3" t="inlineStr">
         <is>
-          <t>Accounting › Reclassify › Account balance heading</t>
+          <t>Accounting › Bills / Bill detail › Payments on this bill</t>
         </is>
       </c>
       <c r="D188" s="3" t="inlineStr">
         <is>
-          <t>D069: Date displays `10/23/26` while date filters use `10/23/2026`</t>
+          <t>D067: Two linked payments render as `Payment — not visible` rather than distinct display identifiers</t>
         </is>
       </c>
       <c r="E188" s="3" t="inlineStr">
@@ -11022,12 +11034,12 @@
       </c>
       <c r="F188" s="3" t="inlineStr">
         <is>
-          <t>class D</t>
+          <t>class N</t>
         </is>
       </c>
       <c r="G188" s="3" t="inlineStr">
         <is>
-          <t>MM/DD/YYYY consistently</t>
+          <t>Readable distinct payment identifiers; no UUID fallback</t>
         </is>
       </c>
       <c r="H188" s="3" t="inlineStr">
@@ -11067,12 +11079,12 @@
       </c>
       <c r="C189" s="3" t="inlineStr">
         <is>
-          <t>Banking › Categorize / Match › Candidate dates</t>
+          <t>Accounting › Bill detail › Journal Entity column</t>
         </is>
       </c>
       <c r="D189" s="3" t="inlineStr">
         <is>
-          <t>D070: Loaded candidate list displays YYYY-MM-DD dates while transaction header uses MM/DD/YYYY</t>
+          <t>D068: Five journal rows show raw UUID entity labels</t>
         </is>
       </c>
       <c r="E189" s="3" t="inlineStr">
@@ -11082,12 +11094,12 @@
       </c>
       <c r="F189" s="3" t="inlineStr">
         <is>
-          <t>class D</t>
+          <t>class N</t>
         </is>
       </c>
       <c r="G189" s="3" t="inlineStr">
         <is>
-          <t>MM/DD/YYYY consistently</t>
+          <t>Resolve human-readable entity names</t>
         </is>
       </c>
       <c r="H189" s="3" t="inlineStr">
@@ -11127,12 +11139,12 @@
       </c>
       <c r="C190" s="3" t="inlineStr">
         <is>
-          <t>Banking › Categorize / Match › Candidate payee labels</t>
+          <t>Accounting › Reclassify › Account balance heading</t>
         </is>
       </c>
       <c r="D190" s="3" t="inlineStr">
         <is>
-          <t>D071: Candidate names mix ALL CAPS and proper case</t>
+          <t>D069: Date displays `10/23/26` while date filters use `10/23/2026`</t>
         </is>
       </c>
       <c r="E190" s="3" t="inlineStr">
@@ -11142,12 +11154,12 @@
       </c>
       <c r="F190" s="3" t="inlineStr">
         <is>
-          <t>class N</t>
+          <t>class D</t>
         </is>
       </c>
       <c r="G190" s="3" t="inlineStr">
         <is>
-          <t>Full names in proper case, respecting approved exceptions</t>
+          <t>MM/DD/YYYY consistently</t>
         </is>
       </c>
       <c r="H190" s="3" t="inlineStr">
@@ -11187,12 +11199,12 @@
       </c>
       <c r="C191" s="3" t="inlineStr">
         <is>
-          <t>Banking › Relay card › Wallet balance tile</t>
+          <t>Banking › Categorize / Match › Candidate dates</t>
         </is>
       </c>
       <c r="D191" s="3" t="inlineStr">
         <is>
-          <t>D072: Five-digit currency omits thousands separator</t>
+          <t>D070: Loaded candidate list displays YYYY-MM-DD dates while transaction header uses MM/DD/YYYY</t>
         </is>
       </c>
       <c r="E191" s="3" t="inlineStr">
@@ -11202,12 +11214,12 @@
       </c>
       <c r="F191" s="3" t="inlineStr">
         <is>
-          <t>class M</t>
+          <t>class D</t>
         </is>
       </c>
       <c r="G191" s="3" t="inlineStr">
         <is>
-          <t>Currency formatted $1,234.56</t>
+          <t>MM/DD/YYYY consistently</t>
         </is>
       </c>
       <c r="H191" s="3" t="inlineStr">
@@ -11247,12 +11259,12 @@
       </c>
       <c r="C192" s="3" t="inlineStr">
         <is>
-          <t>Cash Flow › Projected Auto › Expected Expenses driver labels</t>
+          <t>Banking › Categorize / Match › Candidate payee labels</t>
         </is>
       </c>
       <c r="D192" s="3" t="inlineStr">
         <is>
-          <t>D073: Driver Bill labels mix ALL CAPS and proper case</t>
+          <t>D071: Candidate names mix ALL CAPS and proper case</t>
         </is>
       </c>
       <c r="E192" s="3" t="inlineStr">
@@ -11307,32 +11319,32 @@
       </c>
       <c r="C193" s="3" t="inlineStr">
         <is>
-          <t>Dispatch › Truck Line › Initial data requests</t>
+          <t>Banking › Relay card › Wallet balance tile</t>
         </is>
       </c>
       <c r="D193" s="3" t="inlineStr">
         <is>
-          <t>D074: Network capture: truck-line 11,425 ms; units-without-load 4,810 / 8,819 ms; positions/latest 4,193 ms; detention/board 3,217 ms</t>
+          <t>D072: Five-digit currency omits thousands separator</t>
         </is>
       </c>
       <c r="E193" s="3" t="inlineStr">
         <is>
-          <t>Chrome Network timing; payloads not retained</t>
+          <t>observed Chrome AX</t>
         </is>
       </c>
       <c r="F193" s="3" t="inlineStr">
         <is>
-          <t>class P</t>
+          <t>class M</t>
         </is>
       </c>
       <c r="G193" s="3" t="inlineStr">
         <is>
-          <t>API responses within 2 seconds; responsive row rendering</t>
+          <t>Currency formatted $1,234.56</t>
         </is>
       </c>
       <c r="H193" s="3" t="inlineStr">
         <is>
-          <t>Lead assigns</t>
+          <t>Cursor</t>
         </is>
       </c>
       <c r="I193" s="3" t="inlineStr">
@@ -11340,14 +11352,14 @@
           <t>443.257-D</t>
         </is>
       </c>
-      <c r="J193" s="6" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
+      <c r="J193" s="7" t="inlineStr">
+        <is>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="K193" s="3" t="inlineStr">
         <is>
-          <t>positions 168 ms / detention 203 ms (#27252); truck-line fc0a287e unverified</t>
+          <t>not re-verified since audit</t>
         </is>
       </c>
       <c r="L193" s="3" t="inlineStr">
@@ -11367,12 +11379,12 @@
       </c>
       <c r="C194" s="3" t="inlineStr">
         <is>
-          <t>Settlements › Open Tours › PU / DEL dates</t>
+          <t>Cash Flow › Projected Auto › Expected Expenses driver labels</t>
         </is>
       </c>
       <c r="D194" s="3" t="inlineStr">
         <is>
-          <t>D075: Rendered dates use OCT-21 / OCT-23 rather than numeric month/day/four-digit year</t>
+          <t>D073: Driver Bill labels mix ALL CAPS and proper case</t>
         </is>
       </c>
       <c r="E194" s="3" t="inlineStr">
@@ -11382,12 +11394,12 @@
       </c>
       <c r="F194" s="3" t="inlineStr">
         <is>
-          <t>class D</t>
+          <t>class N</t>
         </is>
       </c>
       <c r="G194" s="3" t="inlineStr">
         <is>
-          <t>MM/DD/YYYY dates</t>
+          <t>Full names in proper case, respecting approved exceptions</t>
         </is>
       </c>
       <c r="H194" s="3" t="inlineStr">
@@ -11407,7 +11419,7 @@
       </c>
       <c r="K194" s="3" t="inlineStr">
         <is>
-          <t>still OCT-21 on open tours 10-23 5:12 PM</t>
+          <t>not re-verified since audit</t>
         </is>
       </c>
       <c r="L194" s="3" t="inlineStr">
@@ -11427,32 +11439,32 @@
       </c>
       <c r="C195" s="3" t="inlineStr">
         <is>
-          <t>Settlements › Escrow Accounts › Holder labels</t>
+          <t>Dispatch › Truck Line › Initial data requests</t>
         </is>
       </c>
       <c r="D195" s="3" t="inlineStr">
         <is>
-          <t>D076: One visible holder link says Driver — Not Visible instead of a resolved full name</t>
+          <t>D074: Network capture: truck-line 11,425 ms; units-without-load 4,810 / 8,819 ms; positions/latest 4,193 ms; detention/board 3,217 ms</t>
         </is>
       </c>
       <c r="E195" s="3" t="inlineStr">
         <is>
-          <t>observed Chrome AX; names not retained</t>
+          <t>Chrome Network timing; payloads not retained</t>
         </is>
       </c>
       <c r="F195" s="3" t="inlineStr">
         <is>
-          <t>class N</t>
+          <t>class P</t>
         </is>
       </c>
       <c r="G195" s="3" t="inlineStr">
         <is>
-          <t>Readable full holder name or explicit unavailable-record explanation</t>
+          <t>API responses within 2 seconds; responsive row rendering</t>
         </is>
       </c>
       <c r="H195" s="3" t="inlineStr">
         <is>
-          <t>Cursor</t>
+          <t>Lead assigns</t>
         </is>
       </c>
       <c r="I195" s="3" t="inlineStr">
@@ -11460,14 +11472,14 @@
           <t>443.257-D</t>
         </is>
       </c>
-      <c r="J195" s="7" t="inlineStr">
-        <is>
-          <t>OPEN</t>
+      <c r="J195" s="6" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="K195" s="3" t="inlineStr">
         <is>
-          <t>still "Driver — Not Visible" 10-23 5:14 PM</t>
+          <t>positions 168 ms / detention 203 ms (#27252); truck-line fc0a287e unverified</t>
         </is>
       </c>
       <c r="L195" s="3" t="inlineStr">
@@ -11487,12 +11499,12 @@
       </c>
       <c r="C196" s="3" t="inlineStr">
         <is>
-          <t>Settlements › Escrow Accounts › Updated dates</t>
+          <t>Settlements › Open Tours › PU / DEL dates</t>
         </is>
       </c>
       <c r="D196" s="3" t="inlineStr">
         <is>
-          <t>D077: Date portion uses unpadded month/day before time</t>
+          <t>D075: Rendered dates use OCT-21 / OCT-23 rather than numeric month/day/four-digit year</t>
         </is>
       </c>
       <c r="E196" s="3" t="inlineStr">
@@ -11507,7 +11519,7 @@
       </c>
       <c r="G196" s="3" t="inlineStr">
         <is>
-          <t>MM/DD/YYYY with consistently formatted time where needed</t>
+          <t>MM/DD/YYYY dates</t>
         </is>
       </c>
       <c r="H196" s="3" t="inlineStr">
@@ -11527,7 +11539,7 @@
       </c>
       <c r="K196" s="3" t="inlineStr">
         <is>
-          <t>still 9/28/2026 unpadded 10-23 5:14 PM</t>
+          <t>still OCT-21 on open tours 10-23 5:12 PM</t>
         </is>
       </c>
       <c r="L196" s="3" t="inlineStr">
@@ -11547,27 +11559,27 @@
       </c>
       <c r="C197" s="3" t="inlineStr">
         <is>
-          <t>Maintenance › Road Service / Create Roadside WO › Ticket # and Location inputs</t>
+          <t>Settlements › Escrow Accounts › Holder labels</t>
         </is>
       </c>
       <c r="D197" s="3" t="inlineStr">
         <is>
-          <t>D078: Two single-line dialog text inputs measure 38 CSS px high</t>
+          <t>D076: One visible holder link says Driver — Not Visible instead of a resolved full name</t>
         </is>
       </c>
       <c r="E197" s="3" t="inlineStr">
         <is>
-          <t>read-only DOM bounding rectangles; opened and cancelled</t>
+          <t>observed Chrome AX; names not retained</t>
         </is>
       </c>
       <c r="F197" s="3" t="inlineStr">
         <is>
-          <t>class I</t>
+          <t>class N</t>
         </is>
       </c>
       <c r="G197" s="3" t="inlineStr">
         <is>
-          <t>32 CSS px input height under V3 audit contract</t>
+          <t>Readable full holder name or explicit unavailable-record explanation</t>
         </is>
       </c>
       <c r="H197" s="3" t="inlineStr">
@@ -11587,7 +11599,7 @@
       </c>
       <c r="K197" s="3" t="inlineStr">
         <is>
-          <t>not re-verified since audit</t>
+          <t>still "Driver — Not Visible" 10-23 5:14 PM</t>
         </is>
       </c>
       <c r="L197" s="3" t="inlineStr">
@@ -11607,12 +11619,12 @@
       </c>
       <c r="C198" s="3" t="inlineStr">
         <is>
-          <t>Customers › Per-Customer P&amp;L › Classification labels</t>
+          <t>Settlements › Escrow Accounts › Updated dates</t>
         </is>
       </c>
       <c r="D198" s="3" t="inlineStr">
         <is>
-          <t>D079: Visible tags read high_margin and past_due</t>
+          <t>D077: Date portion uses unpadded month/day before time</t>
         </is>
       </c>
       <c r="E198" s="3" t="inlineStr">
@@ -11622,12 +11634,12 @@
       </c>
       <c r="F198" s="3" t="inlineStr">
         <is>
-          <t>class N</t>
+          <t>class D</t>
         </is>
       </c>
       <c r="G198" s="3" t="inlineStr">
         <is>
-          <t>Human-readable labels, not snake_case internal codes</t>
+          <t>MM/DD/YYYY with consistently formatted time where needed</t>
         </is>
       </c>
       <c r="H198" s="3" t="inlineStr">
@@ -11647,7 +11659,7 @@
       </c>
       <c r="K198" s="3" t="inlineStr">
         <is>
-          <t>not re-verified since audit</t>
+          <t>still 9/28/2026 unpadded 10-23 5:14 PM</t>
         </is>
       </c>
       <c r="L198" s="3" t="inlineStr">
@@ -11667,49 +11679,169 @@
       </c>
       <c r="C199" s="3" t="inlineStr">
         <is>
+          <t>Maintenance › Road Service / Create Roadside WO › Ticket # and Location inputs</t>
+        </is>
+      </c>
+      <c r="D199" s="3" t="inlineStr">
+        <is>
+          <t>D078: Two single-line dialog text inputs measure 38 CSS px high</t>
+        </is>
+      </c>
+      <c r="E199" s="3" t="inlineStr">
+        <is>
+          <t>read-only DOM bounding rectangles; opened and cancelled</t>
+        </is>
+      </c>
+      <c r="F199" s="3" t="inlineStr">
+        <is>
+          <t>class I</t>
+        </is>
+      </c>
+      <c r="G199" s="3" t="inlineStr">
+        <is>
+          <t>32 CSS px input height under V3 audit contract</t>
+        </is>
+      </c>
+      <c r="H199" s="3" t="inlineStr">
+        <is>
+          <t>Cursor</t>
+        </is>
+      </c>
+      <c r="I199" s="3" t="inlineStr">
+        <is>
+          <t>443.257-D</t>
+        </is>
+      </c>
+      <c r="J199" s="7" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="K199" s="3" t="inlineStr">
+        <is>
+          <t>not re-verified since audit</t>
+        </is>
+      </c>
+      <c r="L199" s="3" t="inlineStr">
+        <is>
+          <t>10-24 02:00 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="3" t="n">
+        <v>198</v>
+      </c>
+      <c r="B200" s="3" t="inlineStr">
+        <is>
+          <t>H · Codex live Chrome audit D001-D079 (docs/bus/AUDIT-443.257-REGISTER.md)</t>
+        </is>
+      </c>
+      <c r="C200" s="3" t="inlineStr">
+        <is>
+          <t>Customers › Per-Customer P&amp;L › Classification labels</t>
+        </is>
+      </c>
+      <c r="D200" s="3" t="inlineStr">
+        <is>
+          <t>D079: Visible tags read high_margin and past_due</t>
+        </is>
+      </c>
+      <c r="E200" s="3" t="inlineStr">
+        <is>
+          <t>observed Chrome AX</t>
+        </is>
+      </c>
+      <c r="F200" s="3" t="inlineStr">
+        <is>
+          <t>class N</t>
+        </is>
+      </c>
+      <c r="G200" s="3" t="inlineStr">
+        <is>
+          <t>Human-readable labels, not snake_case internal codes</t>
+        </is>
+      </c>
+      <c r="H200" s="3" t="inlineStr">
+        <is>
+          <t>Cursor</t>
+        </is>
+      </c>
+      <c r="I200" s="3" t="inlineStr">
+        <is>
+          <t>443.257-D</t>
+        </is>
+      </c>
+      <c r="J200" s="7" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="K200" s="3" t="inlineStr">
+        <is>
+          <t>not re-verified since audit</t>
+        </is>
+      </c>
+      <c r="L200" s="3" t="inlineStr">
+        <is>
+          <t>10-24 02:00 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="3" t="n">
+        <v>199</v>
+      </c>
+      <c r="B201" s="3" t="inlineStr">
+        <is>
+          <t>H · Codex live Chrome audit D001-D079 (docs/bus/AUDIT-443.257-REGISTER.md)</t>
+        </is>
+      </c>
+      <c r="C201" s="3" t="inlineStr">
+        <is>
           <t>Coverage</t>
         </is>
       </c>
-      <c r="D199" s="3" t="inlineStr">
+      <c r="D201" s="3" t="inlineStr">
         <is>
           <t>Codex audit coverage is partial depth — remaining tabs, drawers and record pages of every module still to audit</t>
         </is>
       </c>
-      <c r="E199" s="3" t="inlineStr">
+      <c r="E201" s="3" t="inlineStr">
         <is>
           <t>coverage ledger lists pending areas</t>
         </is>
       </c>
-      <c r="F199" s="3" t="inlineStr"/>
-      <c r="G199" s="3" t="inlineStr">
+      <c r="F201" s="3" t="inlineStr"/>
+      <c r="G201" s="3" t="inlineStr">
         <is>
           <t>finish the audit module by module, append D080+</t>
         </is>
       </c>
-      <c r="H199" s="3" t="inlineStr">
+      <c r="H201" s="3" t="inlineStr">
         <is>
           <t>CODEX</t>
         </is>
       </c>
-      <c r="I199" s="3" t="inlineStr">
+      <c r="I201" s="3" t="inlineStr">
         <is>
           <t>443.281</t>
         </is>
       </c>
-      <c r="J199" s="7" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="K199" s="3" t="inlineStr"/>
-      <c r="L199" s="3" t="inlineStr">
+      <c r="J201" s="7" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="K201" s="3" t="inlineStr"/>
+      <c r="L201" s="3" t="inlineStr">
         <is>
           <t>10-24 02:00 UTC</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:L199"/>
+  <autoFilter ref="A2:L201"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -11770,7 +11902,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C2" t="n">
         <v>15</v>
@@ -11782,7 +11914,7 @@
         <v>2</v>
       </c>
       <c r="F2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G2" t="n">
         <v>2</v>
@@ -11845,7 +11977,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C5" t="n">
         <v>1</v>
@@ -11860,7 +11992,7 @@
         <v>14</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -11882,10 +12014,10 @@
         <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -11945,7 +12077,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C9" t="n">
         <v>23</v>
@@ -11957,10 +12089,10 @@
         <v>17</v>
       </c>
       <c r="F9" t="n">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="G9" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/docs/bus/lead/LEAD-PENDING-REGISTER.xlsx
+++ b/docs/bus/lead/LEAD-PENDING-REGISTER.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Register" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Register" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Register'!$A$2:$L$201</definedName>
@@ -482,7 +482,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L201"/>
+  <dimension ref="A1:L204"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -502,7 +502,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>IH35-TMS · USMCA · LEAD PENDING REGISTER · updated 10-23-2026 6:35 PM CT · every item numbered · DONE only with live proof</t>
+          <t>IH35-TMS · USMCA · LEAD PENDING REGISTER · updated 10-23-2026 7:45 PM CT · every item numbered · DONE only with live proof</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="J89" s="9" t="inlineStr">
         <is>
-          <t>IN PROGRESS</t>
+          <t>DONE-LIVE</t>
         </is>
       </c>
       <c r="K89" s="3" t="inlineStr">
         <is>
-          <t>LEAD 443.282 758bd029: guard credits tables read through a read view (D074 cache); selftest lock</t>
+          <t>LEAD #27383 d85ade3b: guard credits view-read tables; verify-no-dead-schema exit 0 on main</t>
         </is>
       </c>
       <c r="L89" s="3" t="inlineStr">
@@ -5403,7 +5403,7 @@
       </c>
       <c r="K91" s="3" t="inlineStr">
         <is>
-          <t>LEAD 443.283: one source; Manual opens from authoritative cash when no saved opening</t>
+          <t>LEAD 443.283 ea892ec5 rebased onto #27390: Manual opens at authoritative $25,533.37; tests 3/3, fe+be tsc 0; push waits on main reds</t>
         </is>
       </c>
       <c r="L91" s="3" t="inlineStr">
@@ -5463,7 +5463,7 @@
       </c>
       <c r="K92" s="3" t="inlineStr">
         <is>
-          <t>LEAD 443.283 f03a33c4: /cash-flow/opening-cash = BofA $8,202.50 + Relay $17,330.87 = $25,533.37; tests 3/3; pushing</t>
+          <t>LEAD 443.283: bank list = operating accounts only (BofA Plaid + Relay ledger); card payables/Faro removed</t>
         </is>
       </c>
       <c r="L92" s="3" t="inlineStr">
@@ -5518,12 +5518,12 @@
       </c>
       <c r="J93" s="9" t="inlineStr">
         <is>
-          <t>IN PROGRESS</t>
+          <t>DONE-LIVE</t>
         </is>
       </c>
       <c r="K93" s="3" t="inlineStr">
         <is>
-          <t>LEAD 443.282 cc74c41e/082a09a6: actuals from operating bank (Oct $208,031.56 in / $205,270.54 out posted); pushing</t>
+          <t>LEAD #27383 d85ade3b live: AvP Oct actual income $208,031.56 / expense $205,270.54 from operating bank; 283b is_credit form (exit 0 direction guard)</t>
         </is>
       </c>
       <c r="L93" s="3" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="J94" s="9" t="inlineStr">
         <is>
-          <t>IN PROGRESS</t>
+          <t>DONE-LIVE</t>
         </is>
       </c>
       <c r="K94" s="3" t="inlineStr">
         <is>
-          <t>LEAD 443.282: pointer matched_advance_id -&gt; matched_factoring_advance_id (25 advances $202,044.98); pushing</t>
+          <t>LEAD #27383: rolling ledger factoring advances matched by bt.matched_factoring_advance_id; no double count</t>
         </is>
       </c>
       <c r="L94" s="3" t="inlineStr">
@@ -11839,6 +11839,170 @@
           <t>10-24 02:00 UTC</t>
         </is>
       </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="3" t="n">
+        <v>200</v>
+      </c>
+      <c r="B202" s="3" t="inlineStr">
+        <is>
+          <t>F · Money tie-outs</t>
+        </is>
+      </c>
+      <c r="C202" s="3" t="inlineStr">
+        <is>
+          <t>Accounting</t>
+        </is>
+      </c>
+      <c r="D202" s="3" t="inlineStr">
+        <is>
+          <t>Accounting "Open invoices" KPI $624,076.72/165 vs GL A/R 1100 $621,076.72/164</t>
+        </is>
+      </c>
+      <c r="E202" s="3" t="inlineStr">
+        <is>
+          <t>prod 7:22 PM: diff $3,000.00 = 1 proforma (169-13690)</t>
+        </is>
+      </c>
+      <c r="F202" s="3" t="inlineStr">
+        <is>
+          <t>KPI filtered only void; proforma counted</t>
+        </is>
+      </c>
+      <c r="G202" s="3" t="inlineStr">
+        <is>
+          <t>issuedInvoice predicate on all 4 KPI aggregates + guard test</t>
+        </is>
+      </c>
+      <c r="H202" s="3" t="inlineStr">
+        <is>
+          <t>LEAD</t>
+        </is>
+      </c>
+      <c r="I202" s="3" t="inlineStr">
+        <is>
+          <t>443.285</t>
+        </is>
+      </c>
+      <c r="J202" s="7" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="K202" s="3" t="inlineStr">
+        <is>
+          <t>9ef89188 test 3/3, be tsc 0; push waits on main reds</t>
+        </is>
+      </c>
+      <c r="L202" s="3" t="n"/>
+    </row>
+    <row r="203">
+      <c r="A203" s="3" t="n">
+        <v>201</v>
+      </c>
+      <c r="B203" s="3" t="inlineStr">
+        <is>
+          <t>E · Main static reds</t>
+        </is>
+      </c>
+      <c r="C203" s="3" t="inlineStr">
+        <is>
+          <t>Platform</t>
+        </is>
+      </c>
+      <c r="D203" s="3" t="inlineStr">
+        <is>
+          <t>443.284: 7 main static reds from 10-23 board merges block every push</t>
+        </is>
+      </c>
+      <c r="E203" s="3" t="inlineStr">
+        <is>
+          <t>7:40 PM measured: 2 fixed (parity footer, factoring nav), 5 red</t>
+        </is>
+      </c>
+      <c r="F203" s="3" t="inlineStr">
+        <is>
+          <t>board merges changed contracts guards pin</t>
+        </is>
+      </c>
+      <c r="G203" s="3" t="inlineStr">
+        <is>
+          <t>retarget guards to board contract with failing plants; never baseline</t>
+        </is>
+      </c>
+      <c r="H203" s="3" t="inlineStr">
+        <is>
+          <t>CC-2/CC-3</t>
+        </is>
+      </c>
+      <c r="I203" s="3" t="inlineStr">
+        <is>
+          <t>443.284</t>
+        </is>
+      </c>
+      <c r="J203" s="7" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="K203" s="3" t="inlineStr">
+        <is>
+          <t>CC-2: dashboard-connectivity, sweep-pre-list, test-provider; CC-3: partial-optional-chain, unselected-boxes</t>
+        </is>
+      </c>
+      <c r="L203" s="3" t="n"/>
+    </row>
+    <row r="204">
+      <c r="A204" s="3" t="n">
+        <v>202</v>
+      </c>
+      <c r="B204" s="3" t="inlineStr">
+        <is>
+          <t>E · Main static reds</t>
+        </is>
+      </c>
+      <c r="C204" s="3" t="inlineStr">
+        <is>
+          <t>Fuel</t>
+        </is>
+      </c>
+      <c r="D204" s="3" t="inlineStr">
+        <is>
+          <t>verify-no-internal-payload-in-notes red: dreamline-statement-import memo interpolates input.expenseId</t>
+        </is>
+      </c>
+      <c r="E204" s="3" t="inlineStr">
+        <is>
+          <t>exit 1 on main 1c118712</t>
+        </is>
+      </c>
+      <c r="F204" s="3" t="inlineStr">
+        <is>
+          <t>afd3fd334e memo template</t>
+        </is>
+      </c>
+      <c r="G204" s="3" t="inlineStr">
+        <is>
+          <t>human memo + spine link</t>
+        </is>
+      </c>
+      <c r="H204" s="3" t="inlineStr">
+        <is>
+          <t>CC-2</t>
+        </is>
+      </c>
+      <c r="I204" s="3" t="inlineStr">
+        <is>
+          <t>443.284</t>
+        </is>
+      </c>
+      <c r="J204" s="7" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="K204" s="3" t="inlineStr"/>
+      <c r="L204" s="3" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:L201"/>

--- a/docs/bus/lead/LEAD-PENDING-REGISTER.xlsx
+++ b/docs/bus/lead/LEAD-PENDING-REGISTER.xlsx
@@ -482,7 +482,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L204"/>
+  <dimension ref="A1:L209"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -502,7 +502,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>IH35-TMS · USMCA · LEAD PENDING REGISTER · updated 10-23-2026 7:45 PM CT · every item numbered · DONE only with live proof</t>
+          <t>IH35-TMS · USMCA · LEAD PENDING REGISTER · updated 10-23-2026 8:15 PM CT · every item numbered · DONE only with live proof</t>
         </is>
       </c>
     </row>
@@ -12003,6 +12003,282 @@
       </c>
       <c r="K204" s="3" t="inlineStr"/>
       <c r="L204" s="3" t="n"/>
+    </row>
+    <row r="205">
+      <c r="A205" s="3" t="n">
+        <v>203</v>
+      </c>
+      <c r="B205" s="3" t="inlineStr">
+        <is>
+          <t>F · Money tie-outs</t>
+        </is>
+      </c>
+      <c r="C205" s="3" t="inlineStr">
+        <is>
+          <t>Linkage</t>
+        </is>
+      </c>
+      <c r="D205" s="3" t="inlineStr">
+        <is>
+          <t>Linkage gate red (verify-every-load-born-posting-carries-its-load) blocks every money push</t>
+        </is>
+      </c>
+      <c r="E205" s="3" t="inlineStr">
+        <is>
+          <t>uncapped prod: 43 discount legs ($1,976.20) on old load + 12 settlement legs on 4 settlements</t>
+        </is>
+      </c>
+      <c r="F205" s="3" t="inlineStr">
+        <is>
+          <t>AUTH-453 / AUTH-454 repairs built (CC-2 #27384) but never run on prod</t>
+        </is>
+      </c>
+      <c r="G205" s="3" t="inlineStr">
+        <is>
+          <t>fork rehearsal then prod, TB 0 before/after</t>
+        </is>
+      </c>
+      <c r="H205" s="3" t="inlineStr">
+        <is>
+          <t>LEAD</t>
+        </is>
+      </c>
+      <c r="I205" s="3" t="inlineStr">
+        <is>
+          <t>443.287</t>
+        </is>
+      </c>
+      <c r="J205" s="7" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="K205" s="3" t="inlineStr">
+        <is>
+          <t>fork br-bitter-lab: AUTH-454 COMMITTED 5 settlements TB 0, postings 7091=7091; AUTH-453 running</t>
+        </is>
+      </c>
+      <c r="L205" s="3" t="n"/>
+    </row>
+    <row r="206">
+      <c r="A206" s="3" t="n">
+        <v>204</v>
+      </c>
+      <c r="B206" s="3" t="inlineStr">
+        <is>
+          <t>F · Money tie-outs</t>
+        </is>
+      </c>
+      <c r="C206" s="3" t="inlineStr">
+        <is>
+          <t>Fuel</t>
+        </is>
+      </c>
+      <c r="D206" s="3" t="inlineStr">
+        <is>
+          <t>Statement card discount / difference is a separate expense with NO link to its receipt; copies the load once, never follows a move</t>
+        </is>
+      </c>
+      <c r="E206" s="3" t="inlineStr">
+        <is>
+          <t>receipt id only in memo (also the no-internal-payload red)</t>
+        </is>
+      </c>
+      <c r="F206" s="3" t="inlineStr">
+        <is>
+          <t>child document not linked to parent; move paths select by fuel link</t>
+        </is>
+      </c>
+      <c r="G206" s="3" t="inlineStr">
+        <is>
+          <t>parent_expense_id + source link; one moveExpenseFamilyToLoad; guard child-follows-parent</t>
+        </is>
+      </c>
+      <c r="H206" s="3" t="inlineStr">
+        <is>
+          <t>CC-2</t>
+        </is>
+      </c>
+      <c r="I206" s="3" t="inlineStr">
+        <is>
+          <t>443.288-A</t>
+        </is>
+      </c>
+      <c r="J206" s="7" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="K206" s="3" t="inlineStr">
+        <is>
+          <t>owner ruling 443.288 10-23 7:59 PM</t>
+        </is>
+      </c>
+      <c r="L206" s="3" t="n"/>
+    </row>
+    <row r="207">
+      <c r="A207" s="3" t="n">
+        <v>205</v>
+      </c>
+      <c r="B207" s="3" t="inlineStr">
+        <is>
+          <t>A · Owner requests (last 24 h)</t>
+        </is>
+      </c>
+      <c r="C207" s="3" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="D207" s="3" t="inlineStr">
+        <is>
+          <t>OWNER: every expense-to-load assignment confirmed by dispatcher or closer — always</t>
+        </is>
+      </c>
+      <c r="E207" s="3" t="inlineStr">
+        <is>
+          <t>10-23 7:59 PM CT</t>
+        </is>
+      </c>
+      <c r="F207" s="3" t="inlineStr">
+        <is>
+          <t>machine writers set the load as final today</t>
+        </is>
+      </c>
+      <c r="G207" s="3" t="inlineStr">
+        <is>
+          <t>load_confirmation proposed|confirmed; confirm engine; settlement close refuses proposed</t>
+        </is>
+      </c>
+      <c r="H207" s="3" t="inlineStr">
+        <is>
+          <t>CC-2</t>
+        </is>
+      </c>
+      <c r="I207" s="3" t="inlineStr">
+        <is>
+          <t>443.288-B</t>
+        </is>
+      </c>
+      <c r="J207" s="7" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="K207" s="3" t="inlineStr">
+        <is>
+          <t>docs/bus/lead/OWNER-RULING-443.288-...md</t>
+        </is>
+      </c>
+      <c r="L207" s="3" t="n"/>
+    </row>
+    <row r="208">
+      <c r="A208" s="3" t="n">
+        <v>206</v>
+      </c>
+      <c r="B208" s="3" t="inlineStr">
+        <is>
+          <t>A · Owner requests (last 24 h)</t>
+        </is>
+      </c>
+      <c r="C208" s="3" t="inlineStr">
+        <is>
+          <t>Dispatch / Settlements</t>
+        </is>
+      </c>
+      <c r="D208" s="3" t="inlineStr">
+        <is>
+          <t>Expense load confirmations queue (Dispatch + Settlements Close), multi-select, bulk confirm</t>
+        </is>
+      </c>
+      <c r="E208" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F208" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G208" s="3" t="inlineStr">
+        <is>
+          <t>V3 board, two-way links</t>
+        </is>
+      </c>
+      <c r="H208" s="3" t="inlineStr">
+        <is>
+          <t>Cursor</t>
+        </is>
+      </c>
+      <c r="I208" s="3" t="inlineStr">
+        <is>
+          <t>443.288-C</t>
+        </is>
+      </c>
+      <c r="J208" s="7" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="K208" s="3" t="inlineStr">
+        <is>
+          <t>after 443.288-B route</t>
+        </is>
+      </c>
+      <c r="L208" s="3" t="n"/>
+    </row>
+    <row r="209">
+      <c r="A209" s="3" t="n">
+        <v>207</v>
+      </c>
+      <c r="B209" s="3" t="inlineStr">
+        <is>
+          <t>E · Main static reds</t>
+        </is>
+      </c>
+      <c r="C209" s="3" t="inlineStr">
+        <is>
+          <t>Guards</t>
+        </is>
+      </c>
+      <c r="D209" s="3" t="inlineStr">
+        <is>
+          <t>Guards for 443.288 (child follows parent, no machine-final load, close refuses proposed, family moves)</t>
+        </is>
+      </c>
+      <c r="E209" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F209" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G209" s="3" t="inlineStr">
+        <is>
+          <t>failing plants; wired with each change</t>
+        </is>
+      </c>
+      <c r="H209" s="3" t="inlineStr">
+        <is>
+          <t>Codex</t>
+        </is>
+      </c>
+      <c r="I209" s="3" t="inlineStr">
+        <is>
+          <t>443.288-D</t>
+        </is>
+      </c>
+      <c r="J209" s="7" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="K209" s="3" t="inlineStr"/>
+      <c r="L209" s="3" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:L201"/>

--- a/docs/bus/lead/LEAD-PENDING-REGISTER.xlsx
+++ b/docs/bus/lead/LEAD-PENDING-REGISTER.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Register" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Register" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Register'!$A$2:$L$201</definedName>
@@ -482,7 +482,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L201"/>
+  <dimension ref="A1:L209"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -502,7 +502,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>IH35-TMS · USMCA · LEAD PENDING REGISTER · updated 10-23-2026 6:35 PM CT · every item numbered · DONE only with live proof</t>
+          <t>IH35-TMS · USMCA · LEAD PENDING REGISTER · updated 10-23-2026 8:15 PM CT · every item numbered · DONE only with live proof</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="J89" s="9" t="inlineStr">
         <is>
-          <t>IN PROGRESS</t>
+          <t>DONE-LIVE</t>
         </is>
       </c>
       <c r="K89" s="3" t="inlineStr">
         <is>
-          <t>LEAD 443.282 758bd029: guard credits tables read through a read view (D074 cache); selftest lock</t>
+          <t>LEAD #27383 d85ade3b: guard credits view-read tables; verify-no-dead-schema exit 0 on main</t>
         </is>
       </c>
       <c r="L89" s="3" t="inlineStr">
@@ -5403,7 +5403,7 @@
       </c>
       <c r="K91" s="3" t="inlineStr">
         <is>
-          <t>LEAD 443.283: one source; Manual opens from authoritative cash when no saved opening</t>
+          <t>LEAD 443.283 ea892ec5 rebased onto #27390: Manual opens at authoritative $25,533.37; tests 3/3, fe+be tsc 0; push waits on main reds</t>
         </is>
       </c>
       <c r="L91" s="3" t="inlineStr">
@@ -5463,7 +5463,7 @@
       </c>
       <c r="K92" s="3" t="inlineStr">
         <is>
-          <t>LEAD 443.283 f03a33c4: /cash-flow/opening-cash = BofA $8,202.50 + Relay $17,330.87 = $25,533.37; tests 3/3; pushing</t>
+          <t>LEAD 443.283: bank list = operating accounts only (BofA Plaid + Relay ledger); card payables/Faro removed</t>
         </is>
       </c>
       <c r="L92" s="3" t="inlineStr">
@@ -5518,12 +5518,12 @@
       </c>
       <c r="J93" s="9" t="inlineStr">
         <is>
-          <t>IN PROGRESS</t>
+          <t>DONE-LIVE</t>
         </is>
       </c>
       <c r="K93" s="3" t="inlineStr">
         <is>
-          <t>LEAD 443.282 cc74c41e/082a09a6: actuals from operating bank (Oct $208,031.56 in / $205,270.54 out posted); pushing</t>
+          <t>LEAD #27383 d85ade3b live: AvP Oct actual income $208,031.56 / expense $205,270.54 from operating bank; 283b is_credit form (exit 0 direction guard)</t>
         </is>
       </c>
       <c r="L93" s="3" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="J94" s="9" t="inlineStr">
         <is>
-          <t>IN PROGRESS</t>
+          <t>DONE-LIVE</t>
         </is>
       </c>
       <c r="K94" s="3" t="inlineStr">
         <is>
-          <t>LEAD 443.282: pointer matched_advance_id -&gt; matched_factoring_advance_id (25 advances $202,044.98); pushing</t>
+          <t>LEAD #27383: rolling ledger factoring advances matched by bt.matched_factoring_advance_id; no double count</t>
         </is>
       </c>
       <c r="L94" s="3" t="inlineStr">
@@ -11839,6 +11839,446 @@
           <t>10-24 02:00 UTC</t>
         </is>
       </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="3" t="n">
+        <v>200</v>
+      </c>
+      <c r="B202" s="3" t="inlineStr">
+        <is>
+          <t>F · Money tie-outs</t>
+        </is>
+      </c>
+      <c r="C202" s="3" t="inlineStr">
+        <is>
+          <t>Accounting</t>
+        </is>
+      </c>
+      <c r="D202" s="3" t="inlineStr">
+        <is>
+          <t>Accounting "Open invoices" KPI $624,076.72/165 vs GL A/R 1100 $621,076.72/164</t>
+        </is>
+      </c>
+      <c r="E202" s="3" t="inlineStr">
+        <is>
+          <t>prod 7:22 PM: diff $3,000.00 = 1 proforma (169-13690)</t>
+        </is>
+      </c>
+      <c r="F202" s="3" t="inlineStr">
+        <is>
+          <t>KPI filtered only void; proforma counted</t>
+        </is>
+      </c>
+      <c r="G202" s="3" t="inlineStr">
+        <is>
+          <t>issuedInvoice predicate on all 4 KPI aggregates + guard test</t>
+        </is>
+      </c>
+      <c r="H202" s="3" t="inlineStr">
+        <is>
+          <t>LEAD</t>
+        </is>
+      </c>
+      <c r="I202" s="3" t="inlineStr">
+        <is>
+          <t>443.285</t>
+        </is>
+      </c>
+      <c r="J202" s="7" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="K202" s="3" t="inlineStr">
+        <is>
+          <t>9ef89188 test 3/3, be tsc 0; push waits on main reds</t>
+        </is>
+      </c>
+      <c r="L202" s="3" t="n"/>
+    </row>
+    <row r="203">
+      <c r="A203" s="3" t="n">
+        <v>201</v>
+      </c>
+      <c r="B203" s="3" t="inlineStr">
+        <is>
+          <t>E · Main static reds</t>
+        </is>
+      </c>
+      <c r="C203" s="3" t="inlineStr">
+        <is>
+          <t>Platform</t>
+        </is>
+      </c>
+      <c r="D203" s="3" t="inlineStr">
+        <is>
+          <t>443.284: 7 main static reds from 10-23 board merges block every push</t>
+        </is>
+      </c>
+      <c r="E203" s="3" t="inlineStr">
+        <is>
+          <t>7:40 PM measured: 2 fixed (parity footer, factoring nav), 5 red</t>
+        </is>
+      </c>
+      <c r="F203" s="3" t="inlineStr">
+        <is>
+          <t>board merges changed contracts guards pin</t>
+        </is>
+      </c>
+      <c r="G203" s="3" t="inlineStr">
+        <is>
+          <t>retarget guards to board contract with failing plants; never baseline</t>
+        </is>
+      </c>
+      <c r="H203" s="3" t="inlineStr">
+        <is>
+          <t>CC-2/CC-3</t>
+        </is>
+      </c>
+      <c r="I203" s="3" t="inlineStr">
+        <is>
+          <t>443.284</t>
+        </is>
+      </c>
+      <c r="J203" s="7" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="K203" s="3" t="inlineStr">
+        <is>
+          <t>CC-2: dashboard-connectivity, sweep-pre-list, test-provider; CC-3: partial-optional-chain, unselected-boxes</t>
+        </is>
+      </c>
+      <c r="L203" s="3" t="n"/>
+    </row>
+    <row r="204">
+      <c r="A204" s="3" t="n">
+        <v>202</v>
+      </c>
+      <c r="B204" s="3" t="inlineStr">
+        <is>
+          <t>E · Main static reds</t>
+        </is>
+      </c>
+      <c r="C204" s="3" t="inlineStr">
+        <is>
+          <t>Fuel</t>
+        </is>
+      </c>
+      <c r="D204" s="3" t="inlineStr">
+        <is>
+          <t>verify-no-internal-payload-in-notes red: dreamline-statement-import memo interpolates input.expenseId</t>
+        </is>
+      </c>
+      <c r="E204" s="3" t="inlineStr">
+        <is>
+          <t>exit 1 on main 1c118712</t>
+        </is>
+      </c>
+      <c r="F204" s="3" t="inlineStr">
+        <is>
+          <t>afd3fd334e memo template</t>
+        </is>
+      </c>
+      <c r="G204" s="3" t="inlineStr">
+        <is>
+          <t>human memo + spine link</t>
+        </is>
+      </c>
+      <c r="H204" s="3" t="inlineStr">
+        <is>
+          <t>CC-2</t>
+        </is>
+      </c>
+      <c r="I204" s="3" t="inlineStr">
+        <is>
+          <t>443.284</t>
+        </is>
+      </c>
+      <c r="J204" s="7" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="K204" s="3" t="inlineStr"/>
+      <c r="L204" s="3" t="n"/>
+    </row>
+    <row r="205">
+      <c r="A205" s="3" t="n">
+        <v>203</v>
+      </c>
+      <c r="B205" s="3" t="inlineStr">
+        <is>
+          <t>F · Money tie-outs</t>
+        </is>
+      </c>
+      <c r="C205" s="3" t="inlineStr">
+        <is>
+          <t>Linkage</t>
+        </is>
+      </c>
+      <c r="D205" s="3" t="inlineStr">
+        <is>
+          <t>Linkage gate red (verify-every-load-born-posting-carries-its-load) blocks every money push</t>
+        </is>
+      </c>
+      <c r="E205" s="3" t="inlineStr">
+        <is>
+          <t>uncapped prod: 43 discount legs ($1,976.20) on old load + 12 settlement legs on 4 settlements</t>
+        </is>
+      </c>
+      <c r="F205" s="3" t="inlineStr">
+        <is>
+          <t>AUTH-453 / AUTH-454 repairs built (CC-2 #27384) but never run on prod</t>
+        </is>
+      </c>
+      <c r="G205" s="3" t="inlineStr">
+        <is>
+          <t>fork rehearsal then prod, TB 0 before/after</t>
+        </is>
+      </c>
+      <c r="H205" s="3" t="inlineStr">
+        <is>
+          <t>LEAD</t>
+        </is>
+      </c>
+      <c r="I205" s="3" t="inlineStr">
+        <is>
+          <t>443.287</t>
+        </is>
+      </c>
+      <c r="J205" s="7" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="K205" s="3" t="inlineStr">
+        <is>
+          <t>fork br-bitter-lab: AUTH-454 COMMITTED 5 settlements TB 0, postings 7091=7091; AUTH-453 running</t>
+        </is>
+      </c>
+      <c r="L205" s="3" t="n"/>
+    </row>
+    <row r="206">
+      <c r="A206" s="3" t="n">
+        <v>204</v>
+      </c>
+      <c r="B206" s="3" t="inlineStr">
+        <is>
+          <t>F · Money tie-outs</t>
+        </is>
+      </c>
+      <c r="C206" s="3" t="inlineStr">
+        <is>
+          <t>Fuel</t>
+        </is>
+      </c>
+      <c r="D206" s="3" t="inlineStr">
+        <is>
+          <t>Statement card discount / difference is a separate expense with NO link to its receipt; copies the load once, never follows a move</t>
+        </is>
+      </c>
+      <c r="E206" s="3" t="inlineStr">
+        <is>
+          <t>receipt id only in memo (also the no-internal-payload red)</t>
+        </is>
+      </c>
+      <c r="F206" s="3" t="inlineStr">
+        <is>
+          <t>child document not linked to parent; move paths select by fuel link</t>
+        </is>
+      </c>
+      <c r="G206" s="3" t="inlineStr">
+        <is>
+          <t>parent_expense_id + source link; one moveExpenseFamilyToLoad; guard child-follows-parent</t>
+        </is>
+      </c>
+      <c r="H206" s="3" t="inlineStr">
+        <is>
+          <t>CC-2</t>
+        </is>
+      </c>
+      <c r="I206" s="3" t="inlineStr">
+        <is>
+          <t>443.288-A</t>
+        </is>
+      </c>
+      <c r="J206" s="7" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="K206" s="3" t="inlineStr">
+        <is>
+          <t>owner ruling 443.288 10-23 7:59 PM</t>
+        </is>
+      </c>
+      <c r="L206" s="3" t="n"/>
+    </row>
+    <row r="207">
+      <c r="A207" s="3" t="n">
+        <v>205</v>
+      </c>
+      <c r="B207" s="3" t="inlineStr">
+        <is>
+          <t>A · Owner requests (last 24 h)</t>
+        </is>
+      </c>
+      <c r="C207" s="3" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="D207" s="3" t="inlineStr">
+        <is>
+          <t>OWNER: every expense-to-load assignment confirmed by dispatcher or closer — always</t>
+        </is>
+      </c>
+      <c r="E207" s="3" t="inlineStr">
+        <is>
+          <t>10-23 7:59 PM CT</t>
+        </is>
+      </c>
+      <c r="F207" s="3" t="inlineStr">
+        <is>
+          <t>machine writers set the load as final today</t>
+        </is>
+      </c>
+      <c r="G207" s="3" t="inlineStr">
+        <is>
+          <t>load_confirmation proposed|confirmed; confirm engine; settlement close refuses proposed</t>
+        </is>
+      </c>
+      <c r="H207" s="3" t="inlineStr">
+        <is>
+          <t>CC-2</t>
+        </is>
+      </c>
+      <c r="I207" s="3" t="inlineStr">
+        <is>
+          <t>443.288-B</t>
+        </is>
+      </c>
+      <c r="J207" s="7" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="K207" s="3" t="inlineStr">
+        <is>
+          <t>docs/bus/lead/OWNER-RULING-443.288-...md</t>
+        </is>
+      </c>
+      <c r="L207" s="3" t="n"/>
+    </row>
+    <row r="208">
+      <c r="A208" s="3" t="n">
+        <v>206</v>
+      </c>
+      <c r="B208" s="3" t="inlineStr">
+        <is>
+          <t>A · Owner requests (last 24 h)</t>
+        </is>
+      </c>
+      <c r="C208" s="3" t="inlineStr">
+        <is>
+          <t>Dispatch / Settlements</t>
+        </is>
+      </c>
+      <c r="D208" s="3" t="inlineStr">
+        <is>
+          <t>Expense load confirmations queue (Dispatch + Settlements Close), multi-select, bulk confirm</t>
+        </is>
+      </c>
+      <c r="E208" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F208" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G208" s="3" t="inlineStr">
+        <is>
+          <t>V3 board, two-way links</t>
+        </is>
+      </c>
+      <c r="H208" s="3" t="inlineStr">
+        <is>
+          <t>Cursor</t>
+        </is>
+      </c>
+      <c r="I208" s="3" t="inlineStr">
+        <is>
+          <t>443.288-C</t>
+        </is>
+      </c>
+      <c r="J208" s="7" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="K208" s="3" t="inlineStr">
+        <is>
+          <t>after 443.288-B route</t>
+        </is>
+      </c>
+      <c r="L208" s="3" t="n"/>
+    </row>
+    <row r="209">
+      <c r="A209" s="3" t="n">
+        <v>207</v>
+      </c>
+      <c r="B209" s="3" t="inlineStr">
+        <is>
+          <t>E · Main static reds</t>
+        </is>
+      </c>
+      <c r="C209" s="3" t="inlineStr">
+        <is>
+          <t>Guards</t>
+        </is>
+      </c>
+      <c r="D209" s="3" t="inlineStr">
+        <is>
+          <t>Guards for 443.288 (child follows parent, no machine-final load, close refuses proposed, family moves)</t>
+        </is>
+      </c>
+      <c r="E209" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F209" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G209" s="3" t="inlineStr">
+        <is>
+          <t>failing plants; wired with each change</t>
+        </is>
+      </c>
+      <c r="H209" s="3" t="inlineStr">
+        <is>
+          <t>Codex</t>
+        </is>
+      </c>
+      <c r="I209" s="3" t="inlineStr">
+        <is>
+          <t>443.288-D</t>
+        </is>
+      </c>
+      <c r="J209" s="7" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="K209" s="3" t="inlineStr"/>
+      <c r="L209" s="3" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:L201"/>

--- a/docs/bus/lead/LEAD-PENDING-REGISTER.xlsx
+++ b/docs/bus/lead/LEAD-PENDING-REGISTER.xlsx
@@ -482,7 +482,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L209"/>
+  <dimension ref="A1:L223"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -502,7 +502,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>IH35-TMS · USMCA · LEAD PENDING REGISTER · updated 10-23-2026 8:15 PM CT · every item numbered · DONE only with live proof</t>
+          <t>IH35-TMS · USMCA · LEAD PENDING REGISTER · updated 10-23-2026 9:20 PM CT · every item numbered · DONE only with live proof</t>
         </is>
       </c>
     </row>
@@ -11947,7 +11947,7 @@
       </c>
       <c r="K203" s="3" t="inlineStr">
         <is>
-          <t>CC-2: dashboard-connectivity, sweep-pre-list, test-provider; CC-3: partial-optional-chain, unselected-boxes</t>
+          <t>9:00 PM main: 4 of 6 green; left verify-settlement-sweep-pre-list, verify-no-internal-payload-in-notes (CC-2)</t>
         </is>
       </c>
       <c r="L203" s="3" t="n"/>
@@ -12055,7 +12055,7 @@
       </c>
       <c r="K205" s="3" t="inlineStr">
         <is>
-          <t>fork br-bitter-lab: AUTH-454 COMMITTED 5 settlements TB 0, postings 7091=7091; AUTH-453 running</t>
+          <t>AUTH-454 COMMITTED on prod (5 headers, TB 0, 7091=7091); AUTH-453 running on prod (owner OK 8:42 PM); fork: uncapped guard exit 0</t>
         </is>
       </c>
       <c r="L205" s="3" t="n"/>
@@ -12279,6 +12279,750 @@
       </c>
       <c r="K209" s="3" t="inlineStr"/>
       <c r="L209" s="3" t="n"/>
+    </row>
+    <row r="210">
+      <c r="A210" s="3" t="n">
+        <v>208</v>
+      </c>
+      <c r="B210" s="3" t="inlineStr">
+        <is>
+          <t>E · Main static reds</t>
+        </is>
+      </c>
+      <c r="C210" s="3" t="inlineStr">
+        <is>
+          <t>Platform</t>
+        </is>
+      </c>
+      <c r="D210" s="3" t="inlineStr">
+        <is>
+          <t>Main CI red at verify:arch-design (/insurance, Fuel Planner settings + Expense mapping)</t>
+        </is>
+      </c>
+      <c r="E210" s="3" t="inlineStr">
+        <is>
+          <t>nothing removed: /insurance/* route; V3Panel titles</t>
+        </is>
+      </c>
+      <c r="F210" s="3" t="inlineStr">
+        <is>
+          <t>reader read literals + h3 only</t>
+        </is>
+      </c>
+      <c r="G210" s="3" t="inlineStr">
+        <is>
+          <t>reader credits splat bases + V3 panel titles, plants</t>
+        </is>
+      </c>
+      <c r="H210" s="3" t="inlineStr">
+        <is>
+          <t>LEAD</t>
+        </is>
+      </c>
+      <c r="I210" s="3" t="inlineStr">
+        <is>
+          <t>443.289</t>
+        </is>
+      </c>
+      <c r="J210" s="7" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="K210" s="3" t="inlineStr">
+        <is>
+          <t>#27422 b1192f1e; plants red; CI re-run pending</t>
+        </is>
+      </c>
+      <c r="L210" s="3" t="n"/>
+    </row>
+    <row r="211">
+      <c r="A211" s="3" t="n">
+        <v>209</v>
+      </c>
+      <c r="B211" s="3" t="inlineStr">
+        <is>
+          <t>E · Main static reds</t>
+        </is>
+      </c>
+      <c r="C211" s="3" t="inlineStr">
+        <is>
+          <t>Guards</t>
+        </is>
+      </c>
+      <c r="D211" s="3" t="inlineStr">
+        <is>
+          <t>107 main static reds outside baseline split by seat</t>
+        </is>
+      </c>
+      <c r="E211" s="3" t="inlineStr">
+        <is>
+          <t>full verify:static 8:35 PM</t>
+        </is>
+      </c>
+      <c r="F211" s="3" t="inlineStr">
+        <is>
+          <t>board merges + stale text guards</t>
+        </is>
+      </c>
+      <c r="G211" s="3" t="inlineStr">
+        <is>
+          <t>fix code or retarget with plants</t>
+        </is>
+      </c>
+      <c r="H211" s="3" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="I211" s="3" t="inlineStr">
+        <is>
+          <t>443.290</t>
+        </is>
+      </c>
+      <c r="J211" s="7" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="K211" s="3" t="inlineStr">
+        <is>
+          <t>#27407 list; CC-1 #27413/#27416/#27417; Lead 4 Cash Flow in 443.283c</t>
+        </is>
+      </c>
+      <c r="L211" s="3" t="n"/>
+    </row>
+    <row r="212">
+      <c r="A212" s="3" t="n">
+        <v>210</v>
+      </c>
+      <c r="B212" s="3" t="inlineStr">
+        <is>
+          <t>E · Guards</t>
+        </is>
+      </c>
+      <c r="C212" s="3" t="inlineStr">
+        <is>
+          <t>Platform</t>
+        </is>
+      </c>
+      <c r="D212" s="3" t="inlineStr">
+        <is>
+          <t>6,266 guard scripts (488 live, ~5,700 source-text, 316 slate-color copies)</t>
+        </is>
+      </c>
+      <c r="E212" s="3" t="inlineStr">
+        <is>
+          <t>census 8:50 PM</t>
+        </is>
+      </c>
+      <c r="F212" s="3" t="inlineStr">
+        <is>
+          <t>one guard per bug, never merged</t>
+        </is>
+      </c>
+      <c r="G212" s="3" t="inlineStr">
+        <is>
+          <t>consolidate: one check per family; text never guards money</t>
+        </is>
+      </c>
+      <c r="H212" s="3" t="inlineStr">
+        <is>
+          <t>Codex</t>
+        </is>
+      </c>
+      <c r="I212" s="3" t="inlineStr">
+        <is>
+          <t>443.291</t>
+        </is>
+      </c>
+      <c r="J212" s="7" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="K212" s="3" t="inlineStr">
+        <is>
+          <t>after Codex filters PR</t>
+        </is>
+      </c>
+      <c r="L212" s="3" t="n"/>
+    </row>
+    <row r="213">
+      <c r="A213" s="3" t="n">
+        <v>211</v>
+      </c>
+      <c r="B213" s="3" t="inlineStr">
+        <is>
+          <t>F · Money tie-outs</t>
+        </is>
+      </c>
+      <c r="C213" s="3" t="inlineStr">
+        <is>
+          <t>Cash Flow</t>
+        </is>
+      </c>
+      <c r="D213" s="3" t="inlineStr">
+        <is>
+          <t>Actual vs Projected + Manual reverted to pre-board code by #27390</t>
+        </is>
+      </c>
+      <c r="E213" s="3" t="inlineStr">
+        <is>
+          <t>AvP 626→380 lines; 4 KPIs + chart gone</t>
+        </is>
+      </c>
+      <c r="F213" s="3" t="inlineStr">
+        <is>
+          <t>#27390 replaced files with old versions</t>
+        </is>
+      </c>
+      <c r="G213" s="3" t="inlineStr">
+        <is>
+          <t>restore approved boards</t>
+        </is>
+      </c>
+      <c r="H213" s="3" t="inlineStr">
+        <is>
+          <t>LEAD</t>
+        </is>
+      </c>
+      <c r="I213" s="3" t="inlineStr">
+        <is>
+          <t>443.283c</t>
+        </is>
+      </c>
+      <c r="J213" s="7" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="K213" s="3" t="inlineStr">
+        <is>
+          <t>162429bd guards + 7/7 tests; push after linkage green</t>
+        </is>
+      </c>
+      <c r="L213" s="3" t="n"/>
+    </row>
+    <row r="214">
+      <c r="A214" s="3" t="n">
+        <v>212</v>
+      </c>
+      <c r="B214" s="3" t="inlineStr">
+        <is>
+          <t>A · Owner requests (last 24 h)</t>
+        </is>
+      </c>
+      <c r="C214" s="3" t="inlineStr">
+        <is>
+          <t>Settlements</t>
+        </is>
+      </c>
+      <c r="D214" s="3" t="inlineStr">
+        <is>
+          <t>Settlement number: P-number shown; real series not assigned by our system</t>
+        </is>
+      </c>
+      <c r="E214" s="3" t="inlineStr">
+        <is>
+          <t>82 numbered (max 5851), 12 not; 5 closed today without number</t>
+        </is>
+      </c>
+      <c r="F214" s="3" t="inlineStr">
+        <is>
+          <t>close engine never assigns</t>
+        </is>
+      </c>
+      <c r="G214" s="3" t="inlineStr">
+        <is>
+          <t>auto-assign at close, next in series, shown everywhere</t>
+        </is>
+      </c>
+      <c r="H214" s="3" t="inlineStr">
+        <is>
+          <t>CC-1</t>
+        </is>
+      </c>
+      <c r="I214" s="3" t="inlineStr">
+        <is>
+          <t>443.292-A</t>
+        </is>
+      </c>
+      <c r="J214" s="7" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="K214" s="3" t="inlineStr"/>
+      <c r="L214" s="3" t="n"/>
+    </row>
+    <row r="215">
+      <c r="A215" s="3" t="n">
+        <v>213</v>
+      </c>
+      <c r="B215" s="3" t="inlineStr">
+        <is>
+          <t>A · Owner requests (last 24 h)</t>
+        </is>
+      </c>
+      <c r="C215" s="3" t="inlineStr">
+        <is>
+          <t>Settlements</t>
+        </is>
+      </c>
+      <c r="D215" s="3" t="inlineStr">
+        <is>
+          <t>Tour dates wrong (P-0114 10/20→10/20; real 10/16→10/23)</t>
+        </is>
+      </c>
+      <c r="E215" s="3" t="inlineStr">
+        <is>
+          <t>open headers period = creation day; UTC midnight renders a day early</t>
+        </is>
+      </c>
+      <c r="F215" s="3" t="inlineStr">
+        <is>
+          <t>writer stamps creation date</t>
+        </is>
+      </c>
+      <c r="G215" s="3" t="inlineStr">
+        <is>
+          <t>first pickup → last delivery, DATE type, re-derive 12</t>
+        </is>
+      </c>
+      <c r="H215" s="3" t="inlineStr">
+        <is>
+          <t>CC-1</t>
+        </is>
+      </c>
+      <c r="I215" s="3" t="inlineStr">
+        <is>
+          <t>443.292-B</t>
+        </is>
+      </c>
+      <c r="J215" s="7" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="K215" s="3" t="inlineStr"/>
+      <c r="L215" s="3" t="n"/>
+    </row>
+    <row r="216">
+      <c r="A216" s="3" t="n">
+        <v>214</v>
+      </c>
+      <c r="B216" s="3" t="inlineStr">
+        <is>
+          <t>A · Owner requests (last 24 h)</t>
+        </is>
+      </c>
+      <c r="C216" s="3" t="inlineStr">
+        <is>
+          <t>Settlements</t>
+        </is>
+      </c>
+      <c r="D216" s="3" t="inlineStr">
+        <is>
+          <t>Settlements tab week list: closed show Open; duplicate empty driver rows</t>
+        </is>
+      </c>
+      <c r="E216" s="3" t="inlineStr">
+        <is>
+          <t>P-0107 closed reads Open</t>
+        </is>
+      </c>
+      <c r="F216" s="3" t="inlineStr">
+        <is>
+          <t>wrong status field</t>
+        </is>
+      </c>
+      <c r="G216" s="3" t="inlineStr">
+        <is>
+          <t>status + payment status columns</t>
+        </is>
+      </c>
+      <c r="H216" s="3" t="inlineStr">
+        <is>
+          <t>CC-1</t>
+        </is>
+      </c>
+      <c r="I216" s="3" t="inlineStr">
+        <is>
+          <t>443.292-C</t>
+        </is>
+      </c>
+      <c r="J216" s="7" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="K216" s="3" t="inlineStr"/>
+      <c r="L216" s="3" t="n"/>
+    </row>
+    <row r="217">
+      <c r="A217" s="3" t="n">
+        <v>215</v>
+      </c>
+      <c r="B217" s="3" t="inlineStr">
+        <is>
+          <t>A · Owner requests (last 24 h)</t>
+        </is>
+      </c>
+      <c r="C217" s="3" t="inlineStr">
+        <is>
+          <t>Settlements</t>
+        </is>
+      </c>
+      <c r="D217" s="3" t="inlineStr">
+        <is>
+          <t>Escrow register: all same date/source, no load numbers; escrow is per load</t>
+        </is>
+      </c>
+      <c r="E217" s="3" t="inlineStr">
+        <is>
+          <t>escrow_ledger 58 rows: load 0, settlement 2</t>
+        </is>
+      </c>
+      <c r="F217" s="3" t="inlineStr">
+        <is>
+          <t>close engine writes no load/settlement</t>
+        </is>
+      </c>
+      <c r="G217" s="3" t="inlineStr">
+        <is>
+          <t>per-load rows + backfill; Date·Settlement#·Load#</t>
+        </is>
+      </c>
+      <c r="H217" s="3" t="inlineStr">
+        <is>
+          <t>CC-1</t>
+        </is>
+      </c>
+      <c r="I217" s="3" t="inlineStr">
+        <is>
+          <t>443.292-D</t>
+        </is>
+      </c>
+      <c r="J217" s="7" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="K217" s="3" t="inlineStr"/>
+      <c r="L217" s="3" t="n"/>
+    </row>
+    <row r="218">
+      <c r="A218" s="3" t="n">
+        <v>216</v>
+      </c>
+      <c r="B218" s="3" t="inlineStr">
+        <is>
+          <t>A · Owner requests (last 24 h)</t>
+        </is>
+      </c>
+      <c r="C218" s="3" t="inlineStr">
+        <is>
+          <t>Accounting</t>
+        </is>
+      </c>
+      <c r="D218" s="3" t="inlineStr">
+        <is>
+          <t>Bill Payments shows driver escrows — not bill payments</t>
+        </is>
+      </c>
+      <c r="E218" s="3" t="inlineStr">
+        <is>
+          <t>218 rows $7,303.21 all settlement deductions; 0 cash</t>
+        </is>
+      </c>
+      <c r="F218" s="3" t="inlineStr">
+        <is>
+          <t>deduction recorded as bill_payment</t>
+        </is>
+      </c>
+      <c r="G218" s="3" t="inlineStr">
+        <is>
+          <t>deduction application kind; Bill Payments = cash only; A/P still 126,443.92</t>
+        </is>
+      </c>
+      <c r="H218" s="3" t="inlineStr">
+        <is>
+          <t>CC-1</t>
+        </is>
+      </c>
+      <c r="I218" s="3" t="inlineStr">
+        <is>
+          <t>443.292-E</t>
+        </is>
+      </c>
+      <c r="J218" s="7" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="K218" s="3" t="inlineStr"/>
+      <c r="L218" s="3" t="n"/>
+    </row>
+    <row r="219">
+      <c r="A219" s="3" t="n">
+        <v>217</v>
+      </c>
+      <c r="B219" s="3" t="inlineStr">
+        <is>
+          <t>A · Owner requests (last 24 h)</t>
+        </is>
+      </c>
+      <c r="C219" s="3" t="inlineStr">
+        <is>
+          <t>Settlements</t>
+        </is>
+      </c>
+      <c r="D219" s="3" t="inlineStr">
+        <is>
+          <t>Empty closed settlements P-0123, P-0124 ($0, 0 lines)</t>
+        </is>
+      </c>
+      <c r="E219" s="3" t="inlineStr">
+        <is>
+          <t>closed 10/23</t>
+        </is>
+      </c>
+      <c r="F219" s="3" t="inlineStr">
+        <is>
+          <t>close engine allows empty</t>
+        </is>
+      </c>
+      <c r="G219" s="3" t="inlineStr">
+        <is>
+          <t>refuse empty; void both via engine</t>
+        </is>
+      </c>
+      <c r="H219" s="3" t="inlineStr">
+        <is>
+          <t>CC-1</t>
+        </is>
+      </c>
+      <c r="I219" s="3" t="inlineStr">
+        <is>
+          <t>443.292-F</t>
+        </is>
+      </c>
+      <c r="J219" s="7" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="K219" s="3" t="inlineStr"/>
+      <c r="L219" s="3" t="n"/>
+    </row>
+    <row r="220">
+      <c r="A220" s="3" t="n">
+        <v>218</v>
+      </c>
+      <c r="B220" s="3" t="inlineStr">
+        <is>
+          <t>A · Owner requests (last 24 h)</t>
+        </is>
+      </c>
+      <c r="C220" s="3" t="inlineStr">
+        <is>
+          <t>Settlements</t>
+        </is>
+      </c>
+      <c r="D220" s="3" t="inlineStr">
+        <is>
+          <t>Statement must match the owner settlement document (5753 format): loads+stops+dates, fuel, expenses, per-load deductions, P&amp;L</t>
+        </is>
+      </c>
+      <c r="E220" s="3" t="inlineStr">
+        <is>
+          <t>P-0114 statement shows no dates, $0 deductions line, fuel —</t>
+        </is>
+      </c>
+      <c r="F220" s="3" t="inlineStr">
+        <is>
+          <t>summary page, not the document</t>
+        </is>
+      </c>
+      <c r="G220" s="3" t="inlineStr">
+        <is>
+          <t>8 sections as Company/Driver_Settlement_5753</t>
+        </is>
+      </c>
+      <c r="H220" s="3" t="inlineStr">
+        <is>
+          <t>Cursor</t>
+        </is>
+      </c>
+      <c r="I220" s="3" t="inlineStr">
+        <is>
+          <t>443.293-A</t>
+        </is>
+      </c>
+      <c r="J220" s="7" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="K220" s="3" t="inlineStr"/>
+      <c r="L220" s="3" t="n"/>
+    </row>
+    <row r="221">
+      <c r="A221" s="3" t="n">
+        <v>219</v>
+      </c>
+      <c r="B221" s="3" t="inlineStr">
+        <is>
+          <t>A · Owner requests (last 24 h)</t>
+        </is>
+      </c>
+      <c r="C221" s="3" t="inlineStr">
+        <is>
+          <t>Dispatch / Settlements</t>
+        </is>
+      </c>
+      <c r="D221" s="3" t="inlineStr">
+        <is>
+          <t>Settlement Close: what it does; should be a button in Dispatch</t>
+        </is>
+      </c>
+      <c r="E221" s="3" t="inlineStr">
+        <is>
+          <t>it is the 7-step close wizard</t>
+        </is>
+      </c>
+      <c r="F221" s="3" t="inlineStr">
+        <is>
+          <t>only reachable in Settlements</t>
+        </is>
+      </c>
+      <c r="G221" s="3" t="inlineStr">
+        <is>
+          <t>Close settlement button in Dispatch opens the same wizard; tab = closer queue</t>
+        </is>
+      </c>
+      <c r="H221" s="3" t="inlineStr">
+        <is>
+          <t>Cursor</t>
+        </is>
+      </c>
+      <c r="I221" s="3" t="inlineStr">
+        <is>
+          <t>443.293-B</t>
+        </is>
+      </c>
+      <c r="J221" s="7" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="K221" s="3" t="inlineStr"/>
+      <c r="L221" s="3" t="n"/>
+    </row>
+    <row r="222">
+      <c r="A222" s="3" t="n">
+        <v>220</v>
+      </c>
+      <c r="B222" s="3" t="inlineStr">
+        <is>
+          <t>A · Owner requests (last 24 h)</t>
+        </is>
+      </c>
+      <c r="C222" s="3" t="inlineStr">
+        <is>
+          <t>Accounting</t>
+        </is>
+      </c>
+      <c r="D222" s="3" t="inlineStr">
+        <is>
+          <t>Inspect every Accounting tab; only Bills first tab is right</t>
+        </is>
+      </c>
+      <c r="E222" s="3" t="inlineStr">
+        <is>
+          <t>owner 8:52 PM</t>
+        </is>
+      </c>
+      <c r="F222" s="3" t="inlineStr">
+        <is>
+          <t>tabs not on V3 board grammar</t>
+        </is>
+      </c>
+      <c r="G222" s="3" t="inlineStr">
+        <is>
+          <t>every tab to Bills-first-tab grammar, screenshots</t>
+        </is>
+      </c>
+      <c r="H222" s="3" t="inlineStr">
+        <is>
+          <t>Cursor</t>
+        </is>
+      </c>
+      <c r="I222" s="3" t="inlineStr">
+        <is>
+          <t>443.293-C</t>
+        </is>
+      </c>
+      <c r="J222" s="7" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="K222" s="3" t="inlineStr"/>
+      <c r="L222" s="3" t="n"/>
+    </row>
+    <row r="223">
+      <c r="A223" s="3" t="n">
+        <v>221</v>
+      </c>
+      <c r="B223" s="3" t="inlineStr">
+        <is>
+          <t>A · Owner requests (last 24 h)</t>
+        </is>
+      </c>
+      <c r="C223" s="3" t="inlineStr">
+        <is>
+          <t>All modules</t>
+        </is>
+      </c>
+      <c r="D223" s="3" t="inlineStr">
+        <is>
+          <t>Override: one reasons catalog + one button app-wide; owner/accountant confirm only; others dropdown; no typing</t>
+        </is>
+      </c>
+      <c r="E223" s="3" t="inlineStr">
+        <is>
+          <t>67 files with ad-hoc override reasons</t>
+        </is>
+      </c>
+      <c r="F223" s="3" t="inlineStr">
+        <is>
+          <t>no shared catalog/engine</t>
+        </is>
+      </c>
+      <c r="G223" s="3" t="inlineStr">
+        <is>
+          <t>catalogs.override_reasons + recordOverride + OverrideButton; replace 67</t>
+        </is>
+      </c>
+      <c r="H223" s="3" t="inlineStr">
+        <is>
+          <t>CC-3</t>
+        </is>
+      </c>
+      <c r="I223" s="3" t="inlineStr">
+        <is>
+          <t>443.294</t>
+        </is>
+      </c>
+      <c r="J223" s="7" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="K223" s="3" t="inlineStr"/>
+      <c r="L223" s="3" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:L201"/>

--- a/docs/bus/lead/LEAD-PENDING-REGISTER.xlsx
+++ b/docs/bus/lead/LEAD-PENDING-REGISTER.xlsx
@@ -482,7 +482,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L223"/>
+  <dimension ref="A1:L226"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -502,7 +502,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>IH35-TMS · USMCA · LEAD PENDING REGISTER · updated 10-23-2026 9:20 PM CT · every item numbered · DONE only with live proof</t>
+          <t>IH35-TMS · USMCA · LEAD PENDING REGISTER · updated 10-23-2026 10:15 PM CT · CODE-COMPLETE MODE (owner 9:40 PM) · deadline 10-24 10:00 AM CT</t>
         </is>
       </c>
     </row>
@@ -700,7 +700,7 @@
       <c r="G5" s="3" t="inlineStr"/>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>LEAD/CC-3</t>
+          <t>LEAD</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
@@ -868,7 +868,7 @@
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>CC-2 + CODEX</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
@@ -972,7 +972,7 @@
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>CURSOR/CC-1</t>
+          <t>Cursor</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
@@ -1028,7 +1028,7 @@
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>CURSOR</t>
+          <t>Cursor</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>CC-3/CURSOR</t>
+          <t>CC-3</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
@@ -1516,7 +1516,7 @@
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>CURSOR/CODEX/CC-3</t>
+          <t>CC-3</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
@@ -2040,7 +2040,7 @@
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>CURSOR + CC-1</t>
+          <t>Cursor</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
@@ -2092,7 +2092,7 @@
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>CODEX (guard) + CURSOR (pages)</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>CURSOR</t>
+          <t>Cursor</t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
@@ -2244,7 +2244,7 @@
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>CURSOR</t>
+          <t>Cursor</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
@@ -2296,7 +2296,7 @@
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t>CURSOR</t>
+          <t>Cursor</t>
         </is>
       </c>
       <c r="I35" s="3" t="inlineStr">
@@ -2352,7 +2352,7 @@
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>CURSOR</t>
+          <t>Cursor</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t>CURSOR</t>
+          <t>Cursor</t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
@@ -2512,7 +2512,7 @@
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t>CURSOR</t>
+          <t>Cursor</t>
         </is>
       </c>
       <c r="I39" s="3" t="inlineStr">
@@ -2564,7 +2564,7 @@
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>CURSOR</t>
+          <t>Cursor</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
@@ -2620,7 +2620,7 @@
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t>CURSOR</t>
+          <t>Cursor</t>
         </is>
       </c>
       <c r="I41" s="3" t="inlineStr">
@@ -2676,7 +2676,7 @@
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>CURSOR</t>
+          <t>CC-3</t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
@@ -2728,7 +2728,7 @@
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t>CURSOR</t>
+          <t>CC-3</t>
         </is>
       </c>
       <c r="I43" s="3" t="inlineStr">
@@ -2784,7 +2784,7 @@
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t>CURSOR</t>
+          <t>CC-3</t>
         </is>
       </c>
       <c r="I44" s="3" t="inlineStr">
@@ -2840,7 +2840,7 @@
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t>CURSOR</t>
+          <t>CC-3</t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
@@ -2896,7 +2896,7 @@
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t>CURSOR</t>
+          <t>Cursor</t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
@@ -2948,7 +2948,7 @@
       </c>
       <c r="H47" s="3" t="inlineStr">
         <is>
-          <t>CURSOR</t>
+          <t>Cursor</t>
         </is>
       </c>
       <c r="I47" s="3" t="inlineStr">
@@ -3000,7 +3000,7 @@
       </c>
       <c r="H48" s="3" t="inlineStr">
         <is>
-          <t>CURSOR</t>
+          <t>Cursor</t>
         </is>
       </c>
       <c r="I48" s="3" t="inlineStr">
@@ -3056,7 +3056,7 @@
       </c>
       <c r="H49" s="3" t="inlineStr">
         <is>
-          <t>CURSOR</t>
+          <t>Cursor</t>
         </is>
       </c>
       <c r="I49" s="3" t="inlineStr">
@@ -3116,7 +3116,7 @@
       </c>
       <c r="H50" s="3" t="inlineStr">
         <is>
-          <t>CURSOR</t>
+          <t>Cursor</t>
         </is>
       </c>
       <c r="I50" s="3" t="inlineStr">
@@ -3176,7 +3176,7 @@
       </c>
       <c r="H51" s="3" t="inlineStr">
         <is>
-          <t>CURSOR</t>
+          <t>Cursor</t>
         </is>
       </c>
       <c r="I51" s="3" t="inlineStr">
@@ -3228,7 +3228,7 @@
       </c>
       <c r="H52" s="3" t="inlineStr">
         <is>
-          <t>CURSOR</t>
+          <t>Cursor</t>
         </is>
       </c>
       <c r="I52" s="3" t="inlineStr">
@@ -3288,7 +3288,7 @@
       </c>
       <c r="H53" s="3" t="inlineStr">
         <is>
-          <t>CURSOR</t>
+          <t>Cursor</t>
         </is>
       </c>
       <c r="I53" s="3" t="inlineStr">
@@ -3348,7 +3348,7 @@
       </c>
       <c r="H54" s="3" t="inlineStr">
         <is>
-          <t>CURSOR</t>
+          <t>Cursor</t>
         </is>
       </c>
       <c r="I54" s="3" t="inlineStr">
@@ -3408,7 +3408,7 @@
       </c>
       <c r="H55" s="3" t="inlineStr">
         <is>
-          <t>CURSOR</t>
+          <t>Cursor</t>
         </is>
       </c>
       <c r="I55" s="3" t="inlineStr">
@@ -3460,7 +3460,7 @@
       </c>
       <c r="H56" s="3" t="inlineStr">
         <is>
-          <t>CURSOR</t>
+          <t>Cursor</t>
         </is>
       </c>
       <c r="I56" s="3" t="inlineStr">
@@ -3516,7 +3516,7 @@
       </c>
       <c r="H57" s="3" t="inlineStr">
         <is>
-          <t>CURSOR</t>
+          <t>Cursor</t>
         </is>
       </c>
       <c r="I57" s="3" t="inlineStr">
@@ -3572,7 +3572,7 @@
       </c>
       <c r="H58" s="3" t="inlineStr">
         <is>
-          <t>CURSOR</t>
+          <t>Cursor</t>
         </is>
       </c>
       <c r="I58" s="3" t="inlineStr">
@@ -3684,7 +3684,7 @@
       </c>
       <c r="H60" s="3" t="inlineStr">
         <is>
-          <t>CODEX</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="I60" s="3" t="inlineStr">
@@ -3740,7 +3740,7 @@
       </c>
       <c r="H61" s="3" t="inlineStr">
         <is>
-          <t>CODEX</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="I61" s="3" t="inlineStr">
@@ -3792,7 +3792,7 @@
       </c>
       <c r="H62" s="3" t="inlineStr">
         <is>
-          <t>CODEX</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="I62" s="3" t="inlineStr">
@@ -4012,7 +4012,7 @@
       </c>
       <c r="H66" s="3" t="inlineStr">
         <is>
-          <t>CURSOR</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="I66" s="3" t="inlineStr">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="H68" s="3" t="inlineStr">
         <is>
-          <t>CURSOR (UI) + CC-1 (report APIs)</t>
+          <t>CC-1</t>
         </is>
       </c>
       <c r="I68" s="3" t="inlineStr">
@@ -4168,7 +4168,7 @@
       </c>
       <c r="H69" s="3" t="inlineStr">
         <is>
-          <t>CURSOR (UI) + CC-1 (report APIs)</t>
+          <t>CC-1</t>
         </is>
       </c>
       <c r="I69" s="3" t="inlineStr">
@@ -4220,7 +4220,7 @@
       </c>
       <c r="H70" s="3" t="inlineStr">
         <is>
-          <t>CURSOR (UI) + CC-1 (report APIs)</t>
+          <t>CC-1</t>
         </is>
       </c>
       <c r="I70" s="3" t="inlineStr">
@@ -4272,7 +4272,7 @@
       </c>
       <c r="H71" s="3" t="inlineStr">
         <is>
-          <t>CURSOR (UI) + CC-1 (report APIs)</t>
+          <t>CC-1</t>
         </is>
       </c>
       <c r="I71" s="3" t="inlineStr">
@@ -4324,7 +4324,7 @@
       </c>
       <c r="H72" s="3" t="inlineStr">
         <is>
-          <t>CURSOR (UI) + CC-1 (report APIs)</t>
+          <t>CC-1</t>
         </is>
       </c>
       <c r="I72" s="3" t="inlineStr">
@@ -4376,7 +4376,7 @@
       </c>
       <c r="H73" s="3" t="inlineStr">
         <is>
-          <t>CURSOR (UI) + CC-1 (report APIs)</t>
+          <t>CC-1</t>
         </is>
       </c>
       <c r="I73" s="3" t="inlineStr">
@@ -4428,7 +4428,7 @@
       </c>
       <c r="H74" s="3" t="inlineStr">
         <is>
-          <t>CURSOR (UI) + CC-1 (report APIs)</t>
+          <t>CC-1</t>
         </is>
       </c>
       <c r="I74" s="3" t="inlineStr">
@@ -4656,7 +4656,7 @@
       </c>
       <c r="H78" s="3" t="inlineStr">
         <is>
-          <t>CC-2 + OWNER</t>
+          <t>CC-2</t>
         </is>
       </c>
       <c r="I78" s="3" t="inlineStr">
@@ -4712,7 +4712,7 @@
       </c>
       <c r="H79" s="3" t="inlineStr">
         <is>
-          <t>CC-2 + OWNER</t>
+          <t>CC-2</t>
         </is>
       </c>
       <c r="I79" s="3" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="H80" s="3" t="inlineStr">
         <is>
-          <t>CC-2 + OWNER</t>
+          <t>CC-2</t>
         </is>
       </c>
       <c r="I80" s="3" t="inlineStr">
@@ -4936,7 +4936,7 @@
       </c>
       <c r="H83" s="3" t="inlineStr">
         <is>
-          <t>CC-2</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="I83" s="3" t="inlineStr">
@@ -5908,7 +5908,7 @@
       </c>
       <c r="H100" s="3" t="inlineStr">
         <is>
-          <t>CURSOR</t>
+          <t>Cursor</t>
         </is>
       </c>
       <c r="I100" s="3" t="inlineStr">
@@ -6020,7 +6020,7 @@
       </c>
       <c r="H102" s="3" t="inlineStr">
         <is>
-          <t>CC-2</t>
+          <t>CC-3</t>
         </is>
       </c>
       <c r="I102" s="3" t="inlineStr">
@@ -6132,7 +6132,7 @@
       </c>
       <c r="H104" s="3" t="inlineStr">
         <is>
-          <t>CURSOR</t>
+          <t>Cursor</t>
         </is>
       </c>
       <c r="I104" s="3" t="inlineStr">
@@ -6188,7 +6188,7 @@
       </c>
       <c r="H105" s="3" t="inlineStr">
         <is>
-          <t>CURSOR</t>
+          <t>Cursor</t>
         </is>
       </c>
       <c r="I105" s="3" t="inlineStr">
@@ -6472,7 +6472,7 @@
       </c>
       <c r="H110" s="3" t="inlineStr">
         <is>
-          <t>CC-3</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="I110" s="3" t="inlineStr">
@@ -6584,7 +6584,7 @@
       </c>
       <c r="H112" s="3" t="inlineStr">
         <is>
-          <t>CODEX/CC-3</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="I112" s="3" t="inlineStr">
@@ -6640,7 +6640,7 @@
       </c>
       <c r="H113" s="3" t="inlineStr">
         <is>
-          <t>CURSOR</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="I113" s="3" t="inlineStr">
@@ -6696,7 +6696,7 @@
       </c>
       <c r="H114" s="3" t="inlineStr">
         <is>
-          <t>CC-2</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="I114" s="3" t="inlineStr">
@@ -6800,7 +6800,7 @@
       <c r="G116" s="3" t="inlineStr"/>
       <c r="H116" s="3" t="inlineStr">
         <is>
-          <t>CURSOR</t>
+          <t>Cursor</t>
         </is>
       </c>
       <c r="I116" s="3" t="inlineStr">
@@ -6844,7 +6844,7 @@
       <c r="G117" s="3" t="inlineStr"/>
       <c r="H117" s="3" t="inlineStr">
         <is>
-          <t>CC-2/CC-3</t>
+          <t>CC-2</t>
         </is>
       </c>
       <c r="I117" s="3" t="inlineStr">
@@ -6984,7 +6984,7 @@
       <c r="G120" s="3" t="inlineStr"/>
       <c r="H120" s="3" t="inlineStr">
         <is>
-          <t>CODEX</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="I120" s="3" t="inlineStr">
@@ -7028,7 +7028,7 @@
       <c r="G121" s="3" t="inlineStr"/>
       <c r="H121" s="3" t="inlineStr">
         <is>
-          <t>CODEX</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="I121" s="3" t="inlineStr">
@@ -7204,7 +7204,7 @@
       </c>
       <c r="H124" s="3" t="inlineStr">
         <is>
-          <t>CC-1 / Cursor</t>
+          <t>CC-1</t>
         </is>
       </c>
       <c r="I124" s="3" t="inlineStr">
@@ -7384,7 +7384,7 @@
       </c>
       <c r="H127" s="3" t="inlineStr">
         <is>
-          <t>Cursor</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="I127" s="3" t="inlineStr">
@@ -8344,7 +8344,7 @@
       </c>
       <c r="H143" s="3" t="inlineStr">
         <is>
-          <t>CC-1 / Cursor</t>
+          <t>CC-1</t>
         </is>
       </c>
       <c r="I143" s="3" t="inlineStr">
@@ -8584,7 +8584,7 @@
       </c>
       <c r="H147" s="3" t="inlineStr">
         <is>
-          <t>CC-1 / Cursor</t>
+          <t>CC-1</t>
         </is>
       </c>
       <c r="I147" s="3" t="inlineStr">
@@ -8644,7 +8644,7 @@
       </c>
       <c r="H148" s="3" t="inlineStr">
         <is>
-          <t>CC-1 / Cursor</t>
+          <t>CC-1</t>
         </is>
       </c>
       <c r="I148" s="3" t="inlineStr">
@@ -8884,7 +8884,7 @@
       </c>
       <c r="H152" s="3" t="inlineStr">
         <is>
-          <t>CC-1 / Cursor</t>
+          <t>CC-1</t>
         </is>
       </c>
       <c r="I152" s="3" t="inlineStr">
@@ -9004,7 +9004,7 @@
       </c>
       <c r="H154" s="3" t="inlineStr">
         <is>
-          <t>Cursor</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="I154" s="3" t="inlineStr">
@@ -9064,7 +9064,7 @@
       </c>
       <c r="H155" s="3" t="inlineStr">
         <is>
-          <t>Cursor</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="I155" s="3" t="inlineStr">
@@ -9124,7 +9124,7 @@
       </c>
       <c r="H156" s="3" t="inlineStr">
         <is>
-          <t>Cursor</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="I156" s="3" t="inlineStr">
@@ -9184,7 +9184,7 @@
       </c>
       <c r="H157" s="3" t="inlineStr">
         <is>
-          <t>CC-1 / Cursor</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="I157" s="3" t="inlineStr">
@@ -9244,7 +9244,7 @@
       </c>
       <c r="H158" s="3" t="inlineStr">
         <is>
-          <t>Cursor</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="I158" s="3" t="inlineStr">
@@ -9304,7 +9304,7 @@
       </c>
       <c r="H159" s="3" t="inlineStr">
         <is>
-          <t>CC-1 / Cursor</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="I159" s="3" t="inlineStr">
@@ -9364,7 +9364,7 @@
       </c>
       <c r="H160" s="3" t="inlineStr">
         <is>
-          <t>Cursor</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="I160" s="3" t="inlineStr">
@@ -9424,7 +9424,7 @@
       </c>
       <c r="H161" s="3" t="inlineStr">
         <is>
-          <t>Cursor</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="I161" s="3" t="inlineStr">
@@ -9484,7 +9484,7 @@
       </c>
       <c r="H162" s="3" t="inlineStr">
         <is>
-          <t>Cursor</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="I162" s="3" t="inlineStr">
@@ -9664,7 +9664,7 @@
       </c>
       <c r="H165" s="3" t="inlineStr">
         <is>
-          <t>CC-1 / Cursor</t>
+          <t>CC-1</t>
         </is>
       </c>
       <c r="I165" s="3" t="inlineStr">
@@ -9784,7 +9784,7 @@
       </c>
       <c r="H167" s="3" t="inlineStr">
         <is>
-          <t>CC-1 / Cursor</t>
+          <t>CC-1</t>
         </is>
       </c>
       <c r="I167" s="3" t="inlineStr">
@@ -9844,7 +9844,7 @@
       </c>
       <c r="H168" s="3" t="inlineStr">
         <is>
-          <t>CC-1 / Cursor</t>
+          <t>CC-1</t>
         </is>
       </c>
       <c r="I168" s="3" t="inlineStr">
@@ -9904,7 +9904,7 @@
       </c>
       <c r="H169" s="3" t="inlineStr">
         <is>
-          <t>Cursor</t>
+          <t>CC-3</t>
         </is>
       </c>
       <c r="I169" s="3" t="inlineStr">
@@ -9964,7 +9964,7 @@
       </c>
       <c r="H170" s="3" t="inlineStr">
         <is>
-          <t>CC-1 / Cursor</t>
+          <t>CC-1</t>
         </is>
       </c>
       <c r="I170" s="3" t="inlineStr">
@@ -10204,7 +10204,7 @@
       </c>
       <c r="H174" s="3" t="inlineStr">
         <is>
-          <t>CC-1 / Cursor</t>
+          <t>CC-1</t>
         </is>
       </c>
       <c r="I174" s="3" t="inlineStr">
@@ -10264,7 +10264,7 @@
       </c>
       <c r="H175" s="3" t="inlineStr">
         <is>
-          <t>Cursor</t>
+          <t>CC-3</t>
         </is>
       </c>
       <c r="I175" s="3" t="inlineStr">
@@ -10324,7 +10324,7 @@
       </c>
       <c r="H176" s="3" t="inlineStr">
         <is>
-          <t>CC-1 / Cursor</t>
+          <t>CC-1</t>
         </is>
       </c>
       <c r="I176" s="3" t="inlineStr">
@@ -10444,7 +10444,7 @@
       </c>
       <c r="H178" s="3" t="inlineStr">
         <is>
-          <t>CC-1 / Cursor</t>
+          <t>CC-1</t>
         </is>
       </c>
       <c r="I178" s="3" t="inlineStr">
@@ -10804,7 +10804,7 @@
       </c>
       <c r="H184" s="3" t="inlineStr">
         <is>
-          <t>Cursor</t>
+          <t>CC-3</t>
         </is>
       </c>
       <c r="I184" s="3" t="inlineStr">
@@ -11464,7 +11464,7 @@
       </c>
       <c r="H195" s="3" t="inlineStr">
         <is>
-          <t>Lead assigns</t>
+          <t>CC-3</t>
         </is>
       </c>
       <c r="I195" s="3" t="inlineStr">
@@ -11704,7 +11704,7 @@
       </c>
       <c r="H199" s="3" t="inlineStr">
         <is>
-          <t>Cursor</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="I199" s="3" t="inlineStr">
@@ -11764,7 +11764,7 @@
       </c>
       <c r="H200" s="3" t="inlineStr">
         <is>
-          <t>Cursor</t>
+          <t>CC-3</t>
         </is>
       </c>
       <c r="I200" s="3" t="inlineStr">
@@ -11820,7 +11820,7 @@
       </c>
       <c r="H201" s="3" t="inlineStr">
         <is>
-          <t>CODEX</t>
+          <t>Codex</t>
         </is>
       </c>
       <c r="I201" s="3" t="inlineStr">
@@ -11932,7 +11932,7 @@
       </c>
       <c r="H203" s="3" t="inlineStr">
         <is>
-          <t>CC-2/CC-3</t>
+          <t>CC-2</t>
         </is>
       </c>
       <c r="I203" s="3" t="inlineStr">
@@ -12055,7 +12055,7 @@
       </c>
       <c r="K205" s="3" t="inlineStr">
         <is>
-          <t>AUTH-454 COMMITTED on prod (5 headers, TB 0, 7091=7091); AUTH-453 running on prod (owner OK 8:42 PM); fork: uncapped guard exit 0</t>
+          <t>AUTH-454 COMMITTED prod (TB 0); AUTH-453 150/241 on prod 10:15 PM, TB 0, retry loop (lock contention)</t>
         </is>
       </c>
       <c r="L205" s="3" t="n"/>
@@ -12372,7 +12372,7 @@
       </c>
       <c r="H211" s="3" t="inlineStr">
         <is>
-          <t>ALL</t>
+          <t>Cursor</t>
         </is>
       </c>
       <c r="I211" s="3" t="inlineStr">
@@ -13023,6 +13023,170 @@
       </c>
       <c r="K223" s="3" t="inlineStr"/>
       <c r="L223" s="3" t="n"/>
+    </row>
+    <row r="224">
+      <c r="A224" s="3" t="n">
+        <v>222</v>
+      </c>
+      <c r="B224" s="3" t="inlineStr">
+        <is>
+          <t>A · Owner requests (last 24 h)</t>
+        </is>
+      </c>
+      <c r="C224" s="3" t="inlineStr">
+        <is>
+          <t>All modules</t>
+        </is>
+      </c>
+      <c r="D224" s="3" t="inlineStr">
+        <is>
+          <t>Popup standard app-wide + Fuel assignment popup redesign</t>
+        </is>
+      </c>
+      <c r="E224" s="3" t="inlineStr">
+        <is>
+          <t>Modal falls back to 85% width; 140 of 155 popup files pass no size</t>
+        </is>
+      </c>
+      <c r="F224" s="3" t="inlineStr">
+        <is>
+          <t>no width caps except xl</t>
+        </is>
+      </c>
+      <c r="G224" s="3" t="inlineStr">
+        <is>
+          <t>sm 480/md 720/lg 960/xl 1280; default md; sections; design V3-Modal-FuelAssignment</t>
+        </is>
+      </c>
+      <c r="H224" s="3" t="inlineStr">
+        <is>
+          <t>Cursor</t>
+        </is>
+      </c>
+      <c r="I224" s="3" t="inlineStr">
+        <is>
+          <t>443.295</t>
+        </is>
+      </c>
+      <c r="J224" s="7" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="K224" s="3" t="inlineStr">
+        <is>
+          <t>design PR #27439</t>
+        </is>
+      </c>
+      <c r="L224" s="3" t="n"/>
+    </row>
+    <row r="225">
+      <c r="A225" s="3" t="n">
+        <v>223</v>
+      </c>
+      <c r="B225" s="3" t="inlineStr">
+        <is>
+          <t>E · Data / engine root causes</t>
+        </is>
+      </c>
+      <c r="C225" s="3" t="inlineStr">
+        <is>
+          <t>Fuel</t>
+        </is>
+      </c>
+      <c r="D225" s="3" t="inlineStr">
+        <is>
+          <t>Fuel evidence: odometer blank, "no GPS truck" while truck parked at pump</t>
+        </is>
+      </c>
+      <c r="E225" s="3" t="inlineStr">
+        <is>
+          <t>360 of 818 fills no station coords; 713 no GPS truck; T173 parked 3:09–4:05 PM odo 438,489.5</t>
+        </is>
+      </c>
+      <c r="F225" s="3" t="inlineStr">
+        <is>
+          <t>station never geocoded; resolver needs breadcrumb at fill minute</t>
+        </is>
+      </c>
+      <c r="G225" s="3" t="inlineStr">
+        <is>
+          <t>geocode stations; parked-hold resolver; odometer at fill</t>
+        </is>
+      </c>
+      <c r="H225" s="3" t="inlineStr">
+        <is>
+          <t>CC-2</t>
+        </is>
+      </c>
+      <c r="I225" s="3" t="inlineStr">
+        <is>
+          <t>443.296</t>
+        </is>
+      </c>
+      <c r="J225" s="7" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="K225" s="3" t="inlineStr"/>
+      <c r="L225" s="3" t="n"/>
+    </row>
+    <row r="226">
+      <c r="A226" s="3" t="n">
+        <v>224</v>
+      </c>
+      <c r="B226" s="3" t="inlineStr">
+        <is>
+          <t>A · Owner requests (last 24 h)</t>
+        </is>
+      </c>
+      <c r="C226" s="3" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="D226" s="3" t="inlineStr">
+        <is>
+          <t>CODE-COMPLETE MODE: code every row, verify at the end</t>
+        </is>
+      </c>
+      <c r="E226" s="3" t="inlineStr">
+        <is>
+          <t>owner 9:40 PM</t>
+        </is>
+      </c>
+      <c r="F226" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G226" s="3" t="inlineStr">
+        <is>
+          <t>rows assigned by seat; deadline 10-24 10:00 AM CT</t>
+        </is>
+      </c>
+      <c r="H226" s="3" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="I226" s="3" t="inlineStr">
+        <is>
+          <t>443.297</t>
+        </is>
+      </c>
+      <c r="J226" s="7" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="K226" s="3" t="inlineStr">
+        <is>
+          <t>box in docs/bus/lead/boxes/2026-10-23</t>
+        </is>
+      </c>
+      <c r="L226" s="3" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:L201"/>

--- a/docs/bus/lead/LEAD-PENDING-REGISTER.xlsx
+++ b/docs/bus/lead/LEAD-PENDING-REGISTER.xlsx
@@ -502,7 +502,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>IH35-TMS · USMCA · LEAD PENDING REGISTER · updated 10-23-2026 10:15 PM CT · CODE-COMPLETE MODE (owner 9:40 PM) · deadline 10-24 10:00 AM CT</t>
+          <t>IH35-TMS · USMCA · LEAD PENDING REGISTER · updated 10-23-2026 11:10 PM CT · CODE-COMPLETE MODE · deadline 10-24 10:00 AM CT</t>
         </is>
       </c>
     </row>
@@ -2202,10 +2202,14 @@
       </c>
       <c r="J33" s="6" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
-        </is>
-      </c>
-      <c r="K33" s="3" t="inlineStr"/>
+          <t>CODED</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t>#27453 (Home unchanged = board)</t>
+        </is>
+      </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve"> 10-24 02:00 UTC</t>
@@ -2254,10 +2258,14 @@
       </c>
       <c r="J34" s="6" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
-        </is>
-      </c>
-      <c r="K34" s="3" t="inlineStr"/>
+          <t>CODED</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>#27453</t>
+        </is>
+      </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve"> 10-24 02:00 UTC</t>
@@ -2306,10 +2314,14 @@
       </c>
       <c r="J35" s="6" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
-        </is>
-      </c>
-      <c r="K35" s="3" t="inlineStr"/>
+          <t>CODED</t>
+        </is>
+      </c>
+      <c r="K35" s="3" t="inlineStr">
+        <is>
+          <t>#27453 AvP board restored</t>
+        </is>
+      </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve"> 10-24 02:00 UTC</t>
@@ -2362,10 +2374,14 @@
       </c>
       <c r="J36" s="7" t="inlineStr">
         <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="K36" s="3" t="inlineStr"/>
+          <t>CODED</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>#27453</t>
+        </is>
+      </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve"> 10-24 02:00 UTC</t>
@@ -2418,10 +2434,14 @@
       </c>
       <c r="J37" s="7" t="inlineStr">
         <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="K37" s="3" t="inlineStr"/>
+          <t>CODED</t>
+        </is>
+      </c>
+      <c r="K37" s="3" t="inlineStr">
+        <is>
+          <t>#27453 Manual board + opening cash</t>
+        </is>
+      </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve"> 10-24 02:00 UTC</t>
@@ -5918,10 +5938,14 @@
       </c>
       <c r="J100" s="7" t="inlineStr">
         <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="K100" s="3" t="inlineStr"/>
+          <t>CODED</t>
+        </is>
+      </c>
+      <c r="K100" s="3" t="inlineStr">
+        <is>
+          <t>CC-1 7349992008 formatting; True-cost denominator with CC-1</t>
+        </is>
+      </c>
       <c r="L100" s="3" t="inlineStr">
         <is>
           <t>10-24 02:00 UTC</t>
@@ -11886,12 +11910,12 @@
       </c>
       <c r="J202" s="7" t="inlineStr">
         <is>
-          <t>IN PROGRESS</t>
+          <t>CODED</t>
         </is>
       </c>
       <c r="K202" s="3" t="inlineStr">
         <is>
-          <t>9ef89188 test 3/3, be tsc 0; push waits on main reds</t>
+          <t>#27452 eef79722</t>
         </is>
       </c>
       <c r="L202" s="3" t="n"/>
@@ -12050,12 +12074,12 @@
       </c>
       <c r="J205" s="7" t="inlineStr">
         <is>
-          <t>IN PROGRESS</t>
+          <t>PAUSED</t>
         </is>
       </c>
       <c r="K205" s="3" t="inlineStr">
         <is>
-          <t>AUTH-454 COMMITTED prod (TB 0); AUTH-453 150/241 on prod 10:15 PM, TB 0, retry loop (lock contention)</t>
+          <t>AUTH-454 done; AUTH-453 198/241 on prod — owner: resume after all rows coded</t>
         </is>
       </c>
       <c r="L205" s="3" t="n"/>
@@ -12494,12 +12518,12 @@
       </c>
       <c r="J213" s="7" t="inlineStr">
         <is>
-          <t>IN PROGRESS</t>
+          <t>CODED</t>
         </is>
       </c>
       <c r="K213" s="3" t="inlineStr">
         <is>
-          <t>162429bd guards + 7/7 tests; push after linkage green</t>
+          <t>#27453 d86e35ce</t>
         </is>
       </c>
       <c r="L213" s="3" t="n"/>

--- a/docs/bus/lead/LEAD-PENDING-REGISTER.xlsx
+++ b/docs/bus/lead/LEAD-PENDING-REGISTER.xlsx
@@ -502,7 +502,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>IH35-TMS · USMCA · LEAD PENDING REGISTER · updated 10-23-2026 11:10 PM CT · CODE-COMPLETE MODE · deadline 10-24 10:00 AM CT</t>
+          <t>IH35-TMS · USMCA · LEAD PENDING REGISTER · updated 10-24-2026 07:44 AM CT · CODE-COMPLETE MODE · deadline 10-24 10:00 AM CT</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>CC-2</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
@@ -1414,10 +1414,14 @@
       </c>
       <c r="J18" s="7" t="inlineStr">
         <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="K18" s="3" t="inlineStr"/>
+          <t>CODED</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>891305b339 #27414 (CC-2)</t>
+        </is>
+      </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
           <t>10-24 02:00 UTC</t>
@@ -1990,12 +1994,12 @@
       </c>
       <c r="J29" s="8" t="inlineStr">
         <is>
-          <t>BLOCKED</t>
+          <t>CODED</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>CC-2 fork: purge cascade casts int child ids to uuid; accidents trigger refuses DELETE -&gt; CC-2 fixing (443.281-F)</t>
+          <t>0ee3451d41 #27457 (CC-2) — deployed 0ee3451 11:04 PM CT; prod purge run = Lead under AUTH-451</t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
@@ -2040,7 +2044,7 @@
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>Cursor</t>
+          <t>CC-1</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
@@ -2092,7 +2096,7 @@
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>LEAD</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
@@ -3704,7 +3708,7 @@
       </c>
       <c r="H60" s="3" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>LEAD</t>
         </is>
       </c>
       <c r="I60" s="3" t="inlineStr">
@@ -3714,10 +3718,14 @@
       </c>
       <c r="J60" s="6" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
-        </is>
-      </c>
-      <c r="K60" s="3" t="inlineStr"/>
+          <t>CODED</t>
+        </is>
+      </c>
+      <c r="K60" s="3" t="inlineStr">
+        <is>
+          <t>893cc58eba #27375 + Home board: 4 tiles, fleet health line, PM countdown/engines/alerts/in-transit/severe, Arriving soon, At risk (all design sections; legacy strips gated to Settings / non-Home); 'PM reading unavailable' = row 108 (CC-2 odometer)</t>
+        </is>
+      </c>
       <c r="L60" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve"> 10-24 02:00 UTC</t>
@@ -3760,7 +3768,7 @@
       </c>
       <c r="H61" s="3" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>LEAD</t>
         </is>
       </c>
       <c r="I61" s="3" t="inlineStr">
@@ -3812,7 +3820,7 @@
       </c>
       <c r="H62" s="3" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>LEAD</t>
         </is>
       </c>
       <c r="I62" s="3" t="inlineStr">
@@ -3822,12 +3830,12 @@
       </c>
       <c r="J62" s="6" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>CODED</t>
         </is>
       </c>
       <c r="K62" s="3" t="inlineStr">
         <is>
-          <t>#27357 80270997; live 5:38 PM same layout, ~15 s load, "No current truck assignment" while on T156</t>
+          <t>8027099748 #27357 board (4 panels) + 75f1ed41d2 443.280 board-only test; RE-INSPECT at end: owner saw old layout + ~15 s load at 5:38 PM (before 443.280); 'No current truck assignment' = row 110 (CC-2)</t>
         </is>
       </c>
       <c r="L62" s="3" t="inlineStr">
@@ -4032,7 +4040,7 @@
       </c>
       <c r="H66" s="3" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>LEAD</t>
         </is>
       </c>
       <c r="I66" s="3" t="inlineStr">
@@ -4042,10 +4050,14 @@
       </c>
       <c r="J66" s="6" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
-        </is>
-      </c>
-      <c r="K66" s="3" t="inlineStr"/>
+          <t>CODED</t>
+        </is>
+      </c>
+      <c r="K66" s="3" t="inlineStr">
+        <is>
+          <t>d7e5e14e54 #27323 board (all design sections) + 8cff827545 #27400 own module shell; Lawsuits tab kept (not on the board) — owner decides</t>
+        </is>
+      </c>
       <c r="L66" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve"> 10-24 02:00 UTC</t>
@@ -4956,7 +4968,7 @@
       </c>
       <c r="H83" s="3" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>CC-2</t>
         </is>
       </c>
       <c r="I83" s="3" t="inlineStr">
@@ -5078,10 +5090,14 @@
       </c>
       <c r="J85" s="7" t="inlineStr">
         <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="K85" s="3" t="inlineStr"/>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="K85" s="3" t="inlineStr">
+        <is>
+          <t>afd3fd334e #27384 coded; prod 198/241 done TB 0; 43 left PAUSED (AUTH-453, owner renews)</t>
+        </is>
+      </c>
       <c r="L85" s="3" t="inlineStr">
         <is>
           <t>10-24 02:00 UTC</t>
@@ -5134,10 +5150,14 @@
       </c>
       <c r="J86" s="7" t="inlineStr">
         <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="K86" s="3" t="inlineStr"/>
+          <t>CODED</t>
+        </is>
+      </c>
+      <c r="K86" s="3" t="inlineStr">
+        <is>
+          <t>afd3fd334e #27384; prod AUTH-454 run done, TB 0</t>
+        </is>
+      </c>
       <c r="L86" s="3" t="inlineStr">
         <is>
           <t>10-24 02:00 UTC</t>
@@ -5418,12 +5438,12 @@
       </c>
       <c r="J91" s="9" t="inlineStr">
         <is>
-          <t>IN PROGRESS</t>
+          <t>CODED</t>
         </is>
       </c>
       <c r="K91" s="3" t="inlineStr">
         <is>
-          <t>LEAD 443.283 ea892ec5 rebased onto #27390: Manual opens at authoritative $25,533.37; tests 3/3, fe+be tsc 0; push waits on main reds</t>
+          <t>d86e35ce75 #27453 LEAD 443.283 opening cash = operating accounts $25,533.37</t>
         </is>
       </c>
       <c r="L91" s="3" t="inlineStr">
@@ -5478,12 +5498,12 @@
       </c>
       <c r="J92" s="9" t="inlineStr">
         <is>
-          <t>IN PROGRESS</t>
+          <t>CODED</t>
         </is>
       </c>
       <c r="K92" s="3" t="inlineStr">
         <is>
-          <t>LEAD 443.283: bank list = operating accounts only (BofA Plaid + Relay ledger); card payables/Faro removed</t>
+          <t>d86e35ce75 #27453 LEAD 443.283 cards/Faro no longer counted as cash</t>
         </is>
       </c>
       <c r="L92" s="3" t="inlineStr">
@@ -5714,10 +5734,14 @@
       </c>
       <c r="J96" s="7" t="inlineStr">
         <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="K96" s="3" t="inlineStr"/>
+          <t>CODED</t>
+        </is>
+      </c>
+      <c r="K96" s="3" t="inlineStr">
+        <is>
+          <t>eef797220e #27452 LEAD 443.285 Open invoices = issued only = GL A/R $621,076.72</t>
+        </is>
+      </c>
       <c r="L96" s="3" t="inlineStr">
         <is>
           <t>10-24 02:00 UTC</t>
@@ -5938,12 +5962,12 @@
       </c>
       <c r="J100" s="7" t="inlineStr">
         <is>
-          <t>CODED</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="K100" s="3" t="inlineStr">
         <is>
-          <t>CC-1 7349992008 formatting; True-cost denominator with CC-1</t>
+          <t>main: NUMERIC fixed (7349992008); one-source True cost = Lead branch claude/lead-row98-factoring-kpi-units, pushing</t>
         </is>
       </c>
       <c r="L100" s="3" t="inlineStr">
@@ -6496,7 +6520,7 @@
       </c>
       <c r="H110" s="3" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>CC-2</t>
         </is>
       </c>
       <c r="I110" s="3" t="inlineStr">
@@ -6608,7 +6632,7 @@
       </c>
       <c r="H112" s="3" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>CC-2</t>
         </is>
       </c>
       <c r="I112" s="3" t="inlineStr">
@@ -6664,7 +6688,7 @@
       </c>
       <c r="H113" s="3" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>CC-2</t>
         </is>
       </c>
       <c r="I113" s="3" t="inlineStr">
@@ -6674,10 +6698,14 @@
       </c>
       <c r="J113" s="7" t="inlineStr">
         <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="K113" s="3" t="inlineStr"/>
+          <t>CODED</t>
+        </is>
+      </c>
+      <c r="K113" s="3" t="inlineStr">
+        <is>
+          <t>8cff827545 #27400 — already on main; CC-2 verified /insurance/* InsuranceModuleShell</t>
+        </is>
+      </c>
       <c r="L113" s="3" t="inlineStr">
         <is>
           <t>10-24 02:00 UTC</t>
@@ -6720,7 +6748,7 @@
       </c>
       <c r="H114" s="3" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>CC-2</t>
         </is>
       </c>
       <c r="I114" s="3" t="inlineStr">
@@ -7018,10 +7046,14 @@
       </c>
       <c r="J120" s="7" t="inlineStr">
         <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="K120" s="3" t="inlineStr"/>
+          <t>CODED</t>
+        </is>
+      </c>
+      <c r="K120" s="3" t="inlineStr">
+        <is>
+          <t>3409d7a383 #27379 (Codex) selftest 10/10, scan 0</t>
+        </is>
+      </c>
       <c r="L120" s="3" t="inlineStr">
         <is>
           <t>10-24 02:00 UTC</t>
@@ -7052,7 +7084,7 @@
       <c r="G121" s="3" t="inlineStr"/>
       <c r="H121" s="3" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>LEAD</t>
         </is>
       </c>
       <c r="I121" s="3" t="inlineStr">
@@ -7228,7 +7260,7 @@
       </c>
       <c r="H124" s="3" t="inlineStr">
         <is>
-          <t>CC-1</t>
+          <t>CC-3</t>
         </is>
       </c>
       <c r="I124" s="3" t="inlineStr">
@@ -7408,7 +7440,7 @@
       </c>
       <c r="H127" s="3" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>LEAD</t>
         </is>
       </c>
       <c r="I127" s="3" t="inlineStr">
@@ -7418,12 +7450,12 @@
       </c>
       <c r="J127" s="7" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CODED</t>
         </is>
       </c>
       <c r="K127" s="3" t="inlineStr">
         <is>
-          <t>not re-verified since audit</t>
+          <t>0512ef14cd 443.258-B (tab -&gt; /driver-finance/…, route mounted) + Lead guard verify-settlements-subnav-stays-in-module</t>
         </is>
       </c>
       <c r="L127" s="3" t="inlineStr">
@@ -7478,12 +7510,12 @@
       </c>
       <c r="J128" s="7" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CODED</t>
         </is>
       </c>
       <c r="K128" s="3" t="inlineStr">
         <is>
-          <t>not re-verified since audit</t>
+          <t>0512ef14cd 443.258-B (tab -&gt; /driver-finance/…, route mounted) + Lead guard verify-settlements-subnav-stays-in-module</t>
         </is>
       </c>
       <c r="L128" s="3" t="inlineStr">
@@ -7538,12 +7570,12 @@
       </c>
       <c r="J129" s="7" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CODED</t>
         </is>
       </c>
       <c r="K129" s="3" t="inlineStr">
         <is>
-          <t>not re-verified since audit</t>
+          <t>0512ef14cd 443.258-B (tab -&gt; /driver-finance/…, route mounted) + Lead guard verify-settlements-subnav-stays-in-module</t>
         </is>
       </c>
       <c r="L129" s="3" t="inlineStr">
@@ -7598,12 +7630,12 @@
       </c>
       <c r="J130" s="7" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CODED</t>
         </is>
       </c>
       <c r="K130" s="3" t="inlineStr">
         <is>
-          <t>not re-verified since audit</t>
+          <t>0512ef14cd 443.258-B (tab -&gt; /driver-finance/…, route mounted) + Lead guard verify-settlements-subnav-stays-in-module</t>
         </is>
       </c>
       <c r="L130" s="3" t="inlineStr">
@@ -7658,12 +7690,12 @@
       </c>
       <c r="J131" s="7" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CODED</t>
         </is>
       </c>
       <c r="K131" s="3" t="inlineStr">
         <is>
-          <t>not re-verified since audit</t>
+          <t>0512ef14cd 443.258-B (tab -&gt; /driver-finance/…, route mounted) + Lead guard verify-settlements-subnav-stays-in-module</t>
         </is>
       </c>
       <c r="L131" s="3" t="inlineStr">
@@ -7718,12 +7750,12 @@
       </c>
       <c r="J132" s="7" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CODED</t>
         </is>
       </c>
       <c r="K132" s="3" t="inlineStr">
         <is>
-          <t>not re-verified since audit</t>
+          <t>0512ef14cd 443.258-B (tab -&gt; /driver-finance/…, route mounted) + Lead guard verify-settlements-subnav-stays-in-module</t>
         </is>
       </c>
       <c r="L132" s="3" t="inlineStr">
@@ -7778,12 +7810,12 @@
       </c>
       <c r="J133" s="7" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CODED</t>
         </is>
       </c>
       <c r="K133" s="3" t="inlineStr">
         <is>
-          <t>not re-verified since audit</t>
+          <t>0512ef14cd 443.258-B (tab -&gt; /driver-finance/…, route mounted) + Lead guard verify-settlements-subnav-stays-in-module</t>
         </is>
       </c>
       <c r="L133" s="3" t="inlineStr">
@@ -7838,12 +7870,12 @@
       </c>
       <c r="J134" s="7" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CODED</t>
         </is>
       </c>
       <c r="K134" s="3" t="inlineStr">
         <is>
-          <t>not re-verified since audit</t>
+          <t>0512ef14cd 443.258-B (tab -&gt; /driver-finance/…, route mounted) + Lead guard verify-settlements-subnav-stays-in-module</t>
         </is>
       </c>
       <c r="L134" s="3" t="inlineStr">
@@ -7898,12 +7930,12 @@
       </c>
       <c r="J135" s="7" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CODED</t>
         </is>
       </c>
       <c r="K135" s="3" t="inlineStr">
         <is>
-          <t>not re-verified since audit</t>
+          <t>0512ef14cd 443.258-B (tab -&gt; /driver-finance/…, route mounted) + Lead guard verify-settlements-subnav-stays-in-module</t>
         </is>
       </c>
       <c r="L135" s="3" t="inlineStr">
@@ -8128,7 +8160,7 @@
       </c>
       <c r="H139" s="3" t="inlineStr">
         <is>
-          <t>Cursor</t>
+          <t>CC-3</t>
         </is>
       </c>
       <c r="I139" s="3" t="inlineStr">
@@ -8368,7 +8400,7 @@
       </c>
       <c r="H143" s="3" t="inlineStr">
         <is>
-          <t>CC-1</t>
+          <t>CC-3</t>
         </is>
       </c>
       <c r="I143" s="3" t="inlineStr">
@@ -8608,7 +8640,7 @@
       </c>
       <c r="H147" s="3" t="inlineStr">
         <is>
-          <t>CC-1</t>
+          <t>CC-3</t>
         </is>
       </c>
       <c r="I147" s="3" t="inlineStr">
@@ -8728,7 +8760,7 @@
       </c>
       <c r="H149" s="3" t="inlineStr">
         <is>
-          <t>Cursor</t>
+          <t>CC-3</t>
         </is>
       </c>
       <c r="I149" s="3" t="inlineStr">
@@ -8908,7 +8940,7 @@
       </c>
       <c r="H152" s="3" t="inlineStr">
         <is>
-          <t>CC-1</t>
+          <t>CC-3</t>
         </is>
       </c>
       <c r="I152" s="3" t="inlineStr">
@@ -8968,7 +9000,7 @@
       </c>
       <c r="H153" s="3" t="inlineStr">
         <is>
-          <t>Cursor</t>
+          <t>CC-3</t>
         </is>
       </c>
       <c r="I153" s="3" t="inlineStr">
@@ -9028,7 +9060,7 @@
       </c>
       <c r="H154" s="3" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>LEAD</t>
         </is>
       </c>
       <c r="I154" s="3" t="inlineStr">
@@ -9088,7 +9120,7 @@
       </c>
       <c r="H155" s="3" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>CC-3</t>
         </is>
       </c>
       <c r="I155" s="3" t="inlineStr">
@@ -9148,7 +9180,7 @@
       </c>
       <c r="H156" s="3" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>LEAD</t>
         </is>
       </c>
       <c r="I156" s="3" t="inlineStr">
@@ -9208,7 +9240,7 @@
       </c>
       <c r="H157" s="3" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>CC-3</t>
         </is>
       </c>
       <c r="I157" s="3" t="inlineStr">
@@ -9268,7 +9300,7 @@
       </c>
       <c r="H158" s="3" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>CC-3</t>
         </is>
       </c>
       <c r="I158" s="3" t="inlineStr">
@@ -9328,7 +9360,7 @@
       </c>
       <c r="H159" s="3" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>CC-3</t>
         </is>
       </c>
       <c r="I159" s="3" t="inlineStr">
@@ -9388,7 +9420,7 @@
       </c>
       <c r="H160" s="3" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>CC-3</t>
         </is>
       </c>
       <c r="I160" s="3" t="inlineStr">
@@ -9448,7 +9480,7 @@
       </c>
       <c r="H161" s="3" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>CC-3</t>
         </is>
       </c>
       <c r="I161" s="3" t="inlineStr">
@@ -9508,7 +9540,7 @@
       </c>
       <c r="H162" s="3" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>CC-3</t>
         </is>
       </c>
       <c r="I162" s="3" t="inlineStr">
@@ -9688,7 +9720,7 @@
       </c>
       <c r="H165" s="3" t="inlineStr">
         <is>
-          <t>CC-1</t>
+          <t>CC-3</t>
         </is>
       </c>
       <c r="I165" s="3" t="inlineStr">
@@ -9868,7 +9900,7 @@
       </c>
       <c r="H168" s="3" t="inlineStr">
         <is>
-          <t>CC-1</t>
+          <t>CC-3</t>
         </is>
       </c>
       <c r="I168" s="3" t="inlineStr">
@@ -9988,7 +10020,7 @@
       </c>
       <c r="H170" s="3" t="inlineStr">
         <is>
-          <t>CC-1</t>
+          <t>CC-3</t>
         </is>
       </c>
       <c r="I170" s="3" t="inlineStr">
@@ -10048,7 +10080,7 @@
       </c>
       <c r="H171" s="3" t="inlineStr">
         <is>
-          <t>Cursor</t>
+          <t>CC-3</t>
         </is>
       </c>
       <c r="I171" s="3" t="inlineStr">
@@ -10108,7 +10140,7 @@
       </c>
       <c r="H172" s="3" t="inlineStr">
         <is>
-          <t>Cursor</t>
+          <t>CC-3</t>
         </is>
       </c>
       <c r="I172" s="3" t="inlineStr">
@@ -10228,7 +10260,7 @@
       </c>
       <c r="H174" s="3" t="inlineStr">
         <is>
-          <t>CC-1</t>
+          <t>CC-3</t>
         </is>
       </c>
       <c r="I174" s="3" t="inlineStr">
@@ -10348,7 +10380,7 @@
       </c>
       <c r="H176" s="3" t="inlineStr">
         <is>
-          <t>CC-1</t>
+          <t>CC-3</t>
         </is>
       </c>
       <c r="I176" s="3" t="inlineStr">
@@ -10408,7 +10440,7 @@
       </c>
       <c r="H177" s="3" t="inlineStr">
         <is>
-          <t>Cursor</t>
+          <t>CC-3</t>
         </is>
       </c>
       <c r="I177" s="3" t="inlineStr">
@@ -10468,7 +10500,7 @@
       </c>
       <c r="H178" s="3" t="inlineStr">
         <is>
-          <t>CC-1</t>
+          <t>CC-3</t>
         </is>
       </c>
       <c r="I178" s="3" t="inlineStr">
@@ -10528,7 +10560,7 @@
       </c>
       <c r="H179" s="3" t="inlineStr">
         <is>
-          <t>Cursor</t>
+          <t>CC-3</t>
         </is>
       </c>
       <c r="I179" s="3" t="inlineStr">
@@ -11728,7 +11760,7 @@
       </c>
       <c r="H199" s="3" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>CC-3</t>
         </is>
       </c>
       <c r="I199" s="3" t="inlineStr">
@@ -11844,7 +11876,7 @@
       </c>
       <c r="H201" s="3" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>LEAD</t>
         </is>
       </c>
       <c r="I201" s="3" t="inlineStr">
@@ -11966,12 +11998,12 @@
       </c>
       <c r="J203" s="7" t="inlineStr">
         <is>
-          <t>IN PROGRESS</t>
+          <t>CODED</t>
         </is>
       </c>
       <c r="K203" s="3" t="inlineStr">
         <is>
-          <t>9:00 PM main: 4 of 6 green; left verify-settlement-sweep-pre-list, verify-no-internal-payload-in-notes (CC-2)</t>
+          <t>804f5f38c2 #27409 (CC-2)</t>
         </is>
       </c>
       <c r="L203" s="3" t="n"/>
@@ -12022,10 +12054,14 @@
       </c>
       <c r="J204" s="7" t="inlineStr">
         <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="K204" s="3" t="inlineStr"/>
+          <t>CODED</t>
+        </is>
+      </c>
+      <c r="K204" s="3" t="inlineStr">
+        <is>
+          <t>804f5f38c2 memo + 5892782b30 structural link (CC-2)</t>
+        </is>
+      </c>
       <c r="L204" s="3" t="n"/>
     </row>
     <row r="205">
@@ -12130,12 +12166,12 @@
       </c>
       <c r="J206" s="7" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CODED</t>
         </is>
       </c>
       <c r="K206" s="3" t="inlineStr">
         <is>
-          <t>owner ruling 443.288 10-23 7:59 PM</t>
+          <t>5892782b30 #27432 443.288-A (CC-2); AUTH-457 ready for Lead</t>
         </is>
       </c>
       <c r="L206" s="3" t="n"/>
@@ -12186,12 +12222,12 @@
       </c>
       <c r="J207" s="7" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CODED</t>
         </is>
       </c>
       <c r="K207" s="3" t="inlineStr">
         <is>
-          <t>docs/bus/lead/OWNER-RULING-443.288-...md</t>
+          <t>e2048ed4b4 #27460 443.288-B (CC-2)</t>
         </is>
       </c>
       <c r="L207" s="3" t="n"/>
@@ -12242,12 +12278,12 @@
       </c>
       <c r="J208" s="7" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CODED</t>
         </is>
       </c>
       <c r="K208" s="3" t="inlineStr">
         <is>
-          <t>after 443.288-B route</t>
+          <t>5f0c13e0af #27445 Cursor 443.288-C queue; bound to CC-2 engine e2048ed4b4 by Lead claude/lead-443-301-frontend-tsc</t>
         </is>
       </c>
       <c r="L208" s="3" t="n"/>
@@ -12288,7 +12324,7 @@
       </c>
       <c r="H209" s="3" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>CC-2</t>
         </is>
       </c>
       <c r="I209" s="3" t="inlineStr">
@@ -12452,7 +12488,7 @@
       </c>
       <c r="H212" s="3" t="inlineStr">
         <is>
-          <t>Codex</t>
+          <t>CC-2</t>
         </is>
       </c>
       <c r="I212" s="3" t="inlineStr">
@@ -12626,10 +12662,14 @@
       </c>
       <c r="J215" s="7" t="inlineStr">
         <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="K215" s="3" t="inlineStr"/>
+          <t>CODED</t>
+        </is>
+      </c>
+      <c r="K215" s="3" t="inlineStr">
+        <is>
+          <t>7349992008 443.292-B tour period dates in Central time (CC-1)</t>
+        </is>
+      </c>
       <c r="L215" s="3" t="n"/>
     </row>
     <row r="216">
@@ -12678,10 +12718,14 @@
       </c>
       <c r="J216" s="7" t="inlineStr">
         <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="K216" s="3" t="inlineStr"/>
+          <t>CODED</t>
+        </is>
+      </c>
+      <c r="K216" s="3" t="inlineStr">
+        <is>
+          <t>7349992008 443.292-C Settlement + Payment status columns (CC-1)</t>
+        </is>
+      </c>
       <c r="L216" s="3" t="n"/>
     </row>
     <row r="217">
@@ -13224,7 +13268,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:L12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -13248,22 +13292,47 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>MERGED-UNVERIFIED</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>CODED</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>other</t>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>PAUSED</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>RE-VERIFY</t>
         </is>
       </c>
     </row>
@@ -13274,23 +13343,38 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="C2" t="n">
         <v>15</v>
       </c>
       <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
         <v>4</v>
       </c>
-      <c r="E2" t="n">
-        <v>2</v>
-      </c>
       <c r="F2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G2" t="n">
         <v>2</v>
       </c>
+      <c r="H2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" t="n">
+        <v>16</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -13305,15 +13389,30 @@
         <v>4</v>
       </c>
       <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
         <v>6</v>
       </c>
-      <c r="E3" t="n">
-        <v>13</v>
-      </c>
       <c r="F3" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G3" t="n">
+        <v>7</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>10</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13336,11 +13435,26 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>7</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -13349,23 +13463,38 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
         <v>1</v>
       </c>
-      <c r="D5" t="n">
+      <c r="F5" t="n">
         <v>1</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="n">
-        <v>14</v>
       </c>
       <c r="G5" t="n">
         <v>1</v>
       </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>13</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -13377,19 +13506,34 @@
         <v>24</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="G6" t="n">
-        <v>4</v>
+        <v>2</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>16</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -13405,17 +13549,32 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
         <v>2</v>
       </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
       <c r="F7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -13430,41 +13589,191 @@
         <v>3</v>
       </c>
       <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
         <v>3</v>
       </c>
-      <c r="E8" t="n">
-        <v>1</v>
-      </c>
       <c r="F8" t="n">
-        <v>72</v>
+        <v>9</v>
       </c>
       <c r="G8" t="n">
         <v>1</v>
       </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>63</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>F · Money tie-outs</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>4</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>3</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>E · Main static reds</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>5</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>E · Guards</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>ALL</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>199</v>
-      </c>
-      <c r="C9" t="n">
-        <v>23</v>
-      </c>
-      <c r="D9" t="n">
+      <c r="B12" t="n">
+        <v>224</v>
+      </c>
+      <c r="C12" t="n">
+        <v>26</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" t="n">
         <v>16</v>
       </c>
-      <c r="E9" t="n">
-        <v>17</v>
-      </c>
-      <c r="F9" t="n">
-        <v>135</v>
-      </c>
-      <c r="G9" t="n">
-        <v>8</v>
+      <c r="F12" t="n">
+        <v>34</v>
+      </c>
+      <c r="G12" t="n">
+        <v>13</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2</v>
+      </c>
+      <c r="I12" t="n">
+        <v>129</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docs/bus/lead/LEAD-PENDING-REGISTER.xlsx
+++ b/docs/bus/lead/LEAD-PENDING-REGISTER.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H306"/>
+  <dimension ref="A1:H315"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2937,7 +2937,7 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>d7e5e14e54 #27323 board (all design sections) + 8cff827545 #27400 own module shell; Lawsuits tab kept (not on the board) — owner decides</t>
+          <t>d7e5e14e54 #27323 + 8cff827545 #27400; owner 10-24 3:47 PM: Lawsuits only in Legal — moved #27543 (443.332), Legal › Lawsuits = legal matters (443.334)</t>
         </is>
       </c>
     </row>
@@ -12208,6 +12208,350 @@
           <t>rerun 10-24 3:25 PM CT</t>
         </is>
       </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="2" t="n">
+        <v>306</v>
+      </c>
+      <c r="B307" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C307" s="2" t="inlineStr">
+        <is>
+          <t>Legal</t>
+        </is>
+      </c>
+      <c r="D307" s="2" t="inlineStr">
+        <is>
+          <t>Lawsuits only in Legal (owner 10-24 3:47 PM CT): Insurance tab removed, /insurance/lawsuits redirects</t>
+        </is>
+      </c>
+      <c r="E307" s="2" t="inlineStr">
+        <is>
+          <t>LEAD</t>
+        </is>
+      </c>
+      <c r="F307" s="2" t="inlineStr">
+        <is>
+          <t>443.332</t>
+        </is>
+      </c>
+      <c r="G307" s="2" t="inlineStr">
+        <is>
+          <t>MERGED</t>
+        </is>
+      </c>
+      <c r="H307" s="2" t="inlineStr">
+        <is>
+          <t>#27543 156ddaa1ec</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="2" t="n">
+        <v>307</v>
+      </c>
+      <c r="B308" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C308" s="2" t="inlineStr">
+        <is>
+          <t>Legal</t>
+        </is>
+      </c>
+      <c r="D308" s="2" t="inlineStr">
+        <is>
+          <t>Legal › Lawsuits = legal-matters board locked to type lawsuit (design: lawsuits are matters); lawsuit links → ?insurance_lawsuit_id=</t>
+        </is>
+      </c>
+      <c r="E308" s="2" t="inlineStr">
+        <is>
+          <t>LEAD</t>
+        </is>
+      </c>
+      <c r="F308" s="2" t="inlineStr">
+        <is>
+          <t>443.334</t>
+        </is>
+      </c>
+      <c r="G308" s="2" t="inlineStr">
+        <is>
+          <t>CODED-QUEUED</t>
+        </is>
+      </c>
+      <c r="H308" s="2" t="inlineStr">
+        <is>
+          <t>049d20f559; guard red→green, vitest 20/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="2" t="n">
+        <v>308</v>
+      </c>
+      <c r="B309" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="C309" s="2" t="inlineStr">
+        <is>
+          <t>Legal</t>
+        </is>
+      </c>
+      <c r="D309" s="2" t="inlineStr">
+        <is>
+          <t>443.333 every USMCA coder TEST record in Legal + Insurance deleted (2 lawsuits, 18 matters, 7 claims, 3 accident reports, 5 cancelled policies; 79 rows with children); 3 real policies kept; books unchanged</t>
+        </is>
+      </c>
+      <c r="E309" s="2" t="inlineStr">
+        <is>
+          <t>LEAD</t>
+        </is>
+      </c>
+      <c r="F309" s="2" t="inlineStr">
+        <is>
+          <t>443.333</t>
+        </is>
+      </c>
+      <c r="G309" s="2" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="H309" s="2" t="inlineStr">
+        <is>
+          <t>AUTH-465 COMMITTED; audit.record_deletions 79; 3585edaf83</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="2" t="n">
+        <v>309</v>
+      </c>
+      <c r="B310" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="C310" s="2" t="inlineStr">
+        <is>
+          <t>Legal</t>
+        </is>
+      </c>
+      <c r="D310" s="2" t="inlineStr">
+        <is>
+          <t>ENG-60 retire the insurance.lawsuit side table: PolicyDetail lawsuit section → legal matters by claim, claim.lawsuit_id → legal matter, LawsuitsTab + 17 guards that read it; drop table after 0 rows all entities</t>
+        </is>
+      </c>
+      <c r="E310" s="2" t="inlineStr">
+        <is>
+          <t>CC-1</t>
+        </is>
+      </c>
+      <c r="F310" s="2" t="inlineStr">
+        <is>
+          <t>ENG-60</t>
+        </is>
+      </c>
+      <c r="G310" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H310" s="2" t="inlineStr"/>
+    </row>
+    <row r="311">
+      <c r="A311" s="2" t="n">
+        <v>310</v>
+      </c>
+      <c r="B311" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="C311" s="2" t="inlineStr">
+        <is>
+          <t>Settlements</t>
+        </is>
+      </c>
+      <c r="D311" s="2" t="inlineStr">
+        <is>
+          <t>ENG-61 closeLoadBookendedSettlementForDriver (settlement ping on final-load delivery) sets closed without posting — refused by tg_settlement_close_requires_posting (ACCT-ENG-01); the close-on-final-load path must post (postLoadBookendedSettlementGlAfterClose) or leave it open</t>
+        </is>
+      </c>
+      <c r="E311" s="2" t="inlineStr">
+        <is>
+          <t>CC-1</t>
+        </is>
+      </c>
+      <c r="F311" s="2" t="inlineStr">
+        <is>
+          <t>ENG-61</t>
+        </is>
+      </c>
+      <c r="G311" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H311" s="2" t="inlineStr">
+        <is>
+          <t>seen 10-24 on 13699/13700 stamp: settlements a41008ca, 6ba08647</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="2" t="n">
+        <v>311</v>
+      </c>
+      <c r="B312" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="C312" s="2" t="inlineStr">
+        <is>
+          <t>Dispatch</t>
+        </is>
+      </c>
+      <c r="D312" s="2" t="inlineStr">
+        <is>
+          <t>ENG-62 loads booked after their trip never got stop stamps (fences minted at booking; replay stamps nothing) — engine stop-arrival-from-fence-history; 13700 + 13699 delivered from the unit's own fence visits; stop-stamp ratchet 13 → 0</t>
+        </is>
+      </c>
+      <c r="E312" s="2" t="inlineStr">
+        <is>
+          <t>LEAD</t>
+        </is>
+      </c>
+      <c r="F312" s="2" t="inlineStr">
+        <is>
+          <t>443.335</t>
+        </is>
+      </c>
+      <c r="G312" s="2" t="inlineStr">
+        <is>
+          <t>CODED-QUEUED</t>
+        </is>
+      </c>
+      <c r="H312" s="2" t="inlineStr">
+        <is>
+          <t>a74b63e99b; prod applied: 13700 dispatched→delivered_pending_docs, 13699 in_transit→delivered_pending_docs</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="2" t="n">
+        <v>312</v>
+      </c>
+      <c r="B313" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="C313" s="2" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="D313" s="2" t="inlineStr">
+        <is>
+          <t>ENG-63 verify-list-empty-settled (resolveListState no longer returns loading while pending) and verify-entity-label-rejects-uuid-shaped-name (HosTrackerSection must call entityLabel) fail on main 5a9f8303e9</t>
+        </is>
+      </c>
+      <c r="E313" s="2" t="inlineStr">
+        <is>
+          <t>CC-3</t>
+        </is>
+      </c>
+      <c r="F313" s="2" t="inlineStr">
+        <is>
+          <t>ENG-63</t>
+        </is>
+      </c>
+      <c r="G313" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H313" s="2" t="inlineStr"/>
+    </row>
+    <row r="314">
+      <c r="A314" s="2" t="n">
+        <v>313</v>
+      </c>
+      <c r="B314" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C314" s="2" t="inlineStr">
+        <is>
+          <t>Settlements</t>
+        </is>
+      </c>
+      <c r="D314" s="2" t="inlineStr">
+        <is>
+          <t>Design audit N2: Escrow register 'Opening balance (historical)' row (design) missing — running balance cannot tie</t>
+        </is>
+      </c>
+      <c r="E314" s="2" t="inlineStr">
+        <is>
+          <t>Cursor</t>
+        </is>
+      </c>
+      <c r="F314" s="2" t="inlineStr">
+        <is>
+          <t>443.326 #6</t>
+        </is>
+      </c>
+      <c r="G314" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H314" s="2" t="inlineStr"/>
+    </row>
+    <row r="315">
+      <c r="A315" s="2" t="n">
+        <v>314</v>
+      </c>
+      <c r="B315" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C315" s="2" t="inlineStr">
+        <is>
+          <t>Settlements</t>
+        </is>
+      </c>
+      <c r="D315" s="2" t="inlineStr">
+        <is>
+          <t>Design audit N3: settlement statement body has no drill links ('[n] fills →', 'BofA line →')</t>
+        </is>
+      </c>
+      <c r="E315" s="2" t="inlineStr">
+        <is>
+          <t>Cursor</t>
+        </is>
+      </c>
+      <c r="F315" s="2" t="inlineStr">
+        <is>
+          <t>443.326 #2</t>
+        </is>
+      </c>
+      <c r="G315" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H315" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/bus/lead/LEAD-PENDING-REGISTER.xlsx
+++ b/docs/bus/lead/LEAD-PENDING-REGISTER.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H235"/>
+  <dimension ref="A1:H306"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3447,7 +3447,11 @@
           <t>OPEN</t>
         </is>
       </c>
-      <c r="H79" s="2" t="inlineStr"/>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>-&gt; ENG-17 (CC-2 443.323)</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
@@ -3483,7 +3487,11 @@
           <t>OPEN</t>
         </is>
       </c>
-      <c r="H80" s="2" t="inlineStr"/>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>-&gt; ENG-17 (CC-2 443.323)</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
@@ -4388,12 +4396,12 @@
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>CODED-QUEUED</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>#27354 e8a9f02b; duplicate rows still live</t>
+          <t>443.320 25c5d51d8f: list in one query, parity 81/81, 120 s -&gt; 0.15 s</t>
         </is>
       </c>
     </row>
@@ -8816,12 +8824,12 @@
       </c>
       <c r="G216" s="2" t="inlineStr">
         <is>
-          <t>CODED</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="H216" s="2" t="inlineStr">
         <is>
-          <t>22dfcaadd7 #27472 (CC-1) escrow register per load</t>
+          <t>22dfcaadd7 #27472 coded; prod escrow_ledger 0 of 58 with load -&gt; ENG-03</t>
         </is>
       </c>
     </row>
@@ -8859,7 +8867,11 @@
           <t>OPEN</t>
         </is>
       </c>
-      <c r="H217" s="2" t="inlineStr"/>
+      <c r="H217" s="2" t="inlineStr">
+        <is>
+          <t>CC-1 #27478 blocked by ENG-01 (ledger ratchet)</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="n">
@@ -9441,7 +9453,7 @@
       </c>
       <c r="H232" s="2" t="inlineStr">
         <is>
-          <t>921aab82b4 claude/lead-443-305-loan-match; fork-proven match/unmatch/rematch (RPL-2026-0026/0027)</t>
+          <t>443.305 account-number fix 65a90b97e0, requeued</t>
         </is>
       </c>
     </row>
@@ -9562,6 +9574,2638 @@
       <c r="H235" s="2" t="inlineStr">
         <is>
           <t>claude/lead-443-308; paged 1,855 = single page</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="2" t="n">
+        <v>235</v>
+      </c>
+      <c r="B236" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="C236" s="2" t="inlineStr">
+        <is>
+          <t>Settlements</t>
+        </is>
+      </c>
+      <c r="D236" s="2" t="inlineStr">
+        <is>
+          <t>Escrow with a balance always visible (active or inactive driver); 11 orphan TEST escrow accounts deleted; DB refuses deleting a driver/vendor that still has escrow</t>
+        </is>
+      </c>
+      <c r="E236" s="2" t="inlineStr">
+        <is>
+          <t>LEAD</t>
+        </is>
+      </c>
+      <c r="F236" s="2" t="inlineStr">
+        <is>
+          <t>443.319</t>
+        </is>
+      </c>
+      <c r="G236" s="2" t="inlineStr">
+        <is>
+          <t>CODED-QUEUED</t>
+        </is>
+      </c>
+      <c r="H236" s="2" t="inlineStr">
+        <is>
+          <t>938da431f6; AUTH-462 prod COMMITTED 11 deleted; trigger refused on fork</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="2" t="n">
+        <v>236</v>
+      </c>
+      <c r="B237" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="C237" s="2" t="inlineStr">
+        <is>
+          <t>Reports</t>
+        </is>
+      </c>
+      <c r="D237" s="2" t="inlineStr">
+        <is>
+          <t>ENG-19 Company settlement report + Trip Profitability counted fuel twice (fuel fill's own expense); 61 of 81 settlements negative -&gt; 23; net -$177,024.87 -&gt; +$113,862.11; trips negative 66 of 92 -&gt; 25</t>
+        </is>
+      </c>
+      <c r="E237" s="2" t="inlineStr">
+        <is>
+          <t>LEAD</t>
+        </is>
+      </c>
+      <c r="F237" s="2" t="inlineStr">
+        <is>
+          <t>443.321</t>
+        </is>
+      </c>
+      <c r="G237" s="2" t="inlineStr">
+        <is>
+          <t>CODED-QUEUED</t>
+        </is>
+      </c>
+      <c r="H237" s="2" t="inlineStr">
+        <is>
+          <t>2a4fbbc2d3; parity 81/81 to the cent; guard red on old engines</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="2" t="n">
+        <v>237</v>
+      </c>
+      <c r="B238" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="C238" s="2" t="inlineStr">
+        <is>
+          <t>Ledger</t>
+        </is>
+      </c>
+      <c r="D238" s="2" t="inlineStr">
+        <is>
+          <t>AUTH-461 / AUTH-462 recorded in OWNER-AUTHORIZATIONS.md with owner quotes and audit counts</t>
+        </is>
+      </c>
+      <c r="E238" s="2" t="inlineStr">
+        <is>
+          <t>LEAD</t>
+        </is>
+      </c>
+      <c r="F238" s="2" t="inlineStr">
+        <is>
+          <t>AUTH ledger</t>
+        </is>
+      </c>
+      <c r="G238" s="2" t="inlineStr">
+        <is>
+          <t>CODED-QUEUED</t>
+        </is>
+      </c>
+      <c r="H238" s="2" t="inlineStr">
+        <is>
+          <t>claude/lead-auth-461-462-ledger</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="2" t="n">
+        <v>238</v>
+      </c>
+      <c r="B239" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="C239" s="2" t="inlineStr">
+        <is>
+          <t>Dispatch</t>
+        </is>
+      </c>
+      <c r="D239" s="2" t="inlineStr">
+        <is>
+          <t>Load 13699 (Copamex, in transit) delivery stop is 'Bradley, IL' with no street; verify-stops-are-geocoded RED live, blocks dispatch-touching pushes (443.301)</t>
+        </is>
+      </c>
+      <c r="E239" s="2" t="inlineStr">
+        <is>
+          <t>OWNER</t>
+        </is>
+      </c>
+      <c r="F239" s="2" t="inlineStr">
+        <is>
+          <t>ENG-21</t>
+        </is>
+      </c>
+      <c r="G239" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H239" s="2" t="inlineStr">
+        <is>
+          <t>owner gives the delivery street address; Lead enters it</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="2" t="n">
+        <v>239</v>
+      </c>
+      <c r="B240" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="C240" s="2" t="inlineStr">
+        <is>
+          <t>Settlements</t>
+        </is>
+      </c>
+      <c r="D240" s="2" t="inlineStr">
+        <is>
+          <t>ENG-01 P-0113/P-0117/P-0119 closed but never posted (posted_at NULL, 0 postings); ledger ratchet 1 -&gt; live 3; blocks #27478. DB refusal: no close without posting</t>
+        </is>
+      </c>
+      <c r="E240" s="2" t="inlineStr">
+        <is>
+          <t>CC-1</t>
+        </is>
+      </c>
+      <c r="F240" s="2" t="inlineStr">
+        <is>
+          <t>443.322</t>
+        </is>
+      </c>
+      <c r="G240" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H240" s="2" t="inlineStr"/>
+    </row>
+    <row r="241">
+      <c r="A241" s="2" t="n">
+        <v>240</v>
+      </c>
+      <c r="B241" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="C241" s="2" t="inlineStr">
+        <is>
+          <t>Driver pay</t>
+        </is>
+      </c>
+      <c r="D241" s="2" t="inlineStr">
+        <is>
+          <t>ENG-02 driver_pay_cents reads the accrued A/P bill, not driver_bills.gross (13574 $1,538.81 vs $957.55)</t>
+        </is>
+      </c>
+      <c r="E241" s="2" t="inlineStr">
+        <is>
+          <t>CC-1</t>
+        </is>
+      </c>
+      <c r="F241" s="2" t="inlineStr">
+        <is>
+          <t>443.322</t>
+        </is>
+      </c>
+      <c r="G241" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H241" s="2" t="inlineStr"/>
+    </row>
+    <row r="242">
+      <c r="A242" s="2" t="n">
+        <v>241</v>
+      </c>
+      <c r="B242" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="C242" s="2" t="inlineStr">
+        <is>
+          <t>Settlements</t>
+        </is>
+      </c>
+      <c r="D242" s="2" t="inlineStr">
+        <is>
+          <t>ENG-03 escrow_ledger 58 rows, 0 with load_id — writer stamps the load; back-fill</t>
+        </is>
+      </c>
+      <c r="E242" s="2" t="inlineStr">
+        <is>
+          <t>CC-1</t>
+        </is>
+      </c>
+      <c r="F242" s="2" t="inlineStr">
+        <is>
+          <t>443.322</t>
+        </is>
+      </c>
+      <c r="G242" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H242" s="2" t="inlineStr"/>
+    </row>
+    <row r="243">
+      <c r="A243" s="2" t="n">
+        <v>242</v>
+      </c>
+      <c r="B243" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="C243" s="2" t="inlineStr">
+        <is>
+          <t>Accounting</t>
+        </is>
+      </c>
+      <c r="D243" s="2" t="inlineStr">
+        <is>
+          <t>ENG-04 2170 Driver Net-Pay Clearing Cr $2,575.96 / 12 postings — tie to open net pay, clear through documents</t>
+        </is>
+      </c>
+      <c r="E243" s="2" t="inlineStr">
+        <is>
+          <t>CC-1</t>
+        </is>
+      </c>
+      <c r="F243" s="2" t="inlineStr">
+        <is>
+          <t>443.322</t>
+        </is>
+      </c>
+      <c r="G243" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H243" s="2" t="inlineStr"/>
+    </row>
+    <row r="244">
+      <c r="A244" s="2" t="n">
+        <v>243</v>
+      </c>
+      <c r="B244" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="C244" s="2" t="inlineStr">
+        <is>
+          <t>Engine</t>
+        </is>
+      </c>
+      <c r="D244" s="2" t="inlineStr">
+        <is>
+          <t>ENG-05 swallowed DB errors grew 122 -&gt; 125 — fix the 3 new, baseline back to 122</t>
+        </is>
+      </c>
+      <c r="E244" s="2" t="inlineStr">
+        <is>
+          <t>CC-1</t>
+        </is>
+      </c>
+      <c r="F244" s="2" t="inlineStr">
+        <is>
+          <t>443.322</t>
+        </is>
+      </c>
+      <c r="G244" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H244" s="2" t="inlineStr"/>
+    </row>
+    <row r="245">
+      <c r="A245" s="2" t="n">
+        <v>244</v>
+      </c>
+      <c r="B245" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="C245" s="2" t="inlineStr">
+        <is>
+          <t>Engine</t>
+        </is>
+      </c>
+      <c r="D245" s="2" t="inlineStr">
+        <is>
+          <t>ENG-06 two overlapping spine guards (-has-a- / -has-its-, step claimed twice) — merge</t>
+        </is>
+      </c>
+      <c r="E245" s="2" t="inlineStr">
+        <is>
+          <t>CC-1</t>
+        </is>
+      </c>
+      <c r="F245" s="2" t="inlineStr">
+        <is>
+          <t>443.322</t>
+        </is>
+      </c>
+      <c r="G245" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H245" s="2" t="inlineStr"/>
+    </row>
+    <row r="246">
+      <c r="A246" s="2" t="n">
+        <v>245</v>
+      </c>
+      <c r="B246" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="C246" s="2" t="inlineStr">
+        <is>
+          <t>Dispatch</t>
+        </is>
+      </c>
+      <c r="D246" s="2" t="inlineStr">
+        <is>
+          <t>ENG-07 G11: 8 of 410 stops without geocode precision since 10-13; Book/Edit Load must refuse a city-only stop</t>
+        </is>
+      </c>
+      <c r="E246" s="2" t="inlineStr">
+        <is>
+          <t>CC-1</t>
+        </is>
+      </c>
+      <c r="F246" s="2" t="inlineStr">
+        <is>
+          <t>443.322</t>
+        </is>
+      </c>
+      <c r="G246" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H246" s="2" t="inlineStr"/>
+    </row>
+    <row r="247">
+      <c r="A247" s="2" t="n">
+        <v>246</v>
+      </c>
+      <c r="B247" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="C247" s="2" t="inlineStr">
+        <is>
+          <t>Driver pay</t>
+        </is>
+      </c>
+      <c r="D247" s="2" t="inlineStr">
+        <is>
+          <t>ENG-08 G15: prod check every lumper advance since 0f1f83233e posts as the load's lumper expense</t>
+        </is>
+      </c>
+      <c r="E247" s="2" t="inlineStr">
+        <is>
+          <t>CC-1</t>
+        </is>
+      </c>
+      <c r="F247" s="2" t="inlineStr">
+        <is>
+          <t>443.322</t>
+        </is>
+      </c>
+      <c r="G247" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H247" s="2" t="inlineStr"/>
+    </row>
+    <row r="248">
+      <c r="A248" s="2" t="n">
+        <v>247</v>
+      </c>
+      <c r="B248" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="C248" s="2" t="inlineStr">
+        <is>
+          <t>Engine</t>
+        </is>
+      </c>
+      <c r="D248" s="2" t="inlineStr">
+        <is>
+          <t>ENG-09 THE GUARANTEE: verify-engine-register-closed-by-guard — a register row is DONE only with a wired guard + evidence; wired in step 1</t>
+        </is>
+      </c>
+      <c r="E248" s="2" t="inlineStr">
+        <is>
+          <t>CC-1</t>
+        </is>
+      </c>
+      <c r="F248" s="2" t="inlineStr">
+        <is>
+          <t>443.322</t>
+        </is>
+      </c>
+      <c r="G248" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H248" s="2" t="inlineStr">
+        <is>
+          <t>reads docs/bus/lead/ENGINE-REGISTER.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="2" t="n">
+        <v>248</v>
+      </c>
+      <c r="B249" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="C249" s="2" t="inlineStr">
+        <is>
+          <t>Fuel</t>
+        </is>
+      </c>
+      <c r="D249" s="2" t="inlineStr">
+        <is>
+          <t>ENG-10 duplicate documents regressed 11 -&gt; 36 groups (guard RED): 31 card-discount groups; 5 &gt;= $1 (Relay 10-11 $623.75, Relay 09-23 $527.58, LOVES $15.25 x3)</t>
+        </is>
+      </c>
+      <c r="E249" s="2" t="inlineStr">
+        <is>
+          <t>CC-2</t>
+        </is>
+      </c>
+      <c r="F249" s="2" t="inlineStr">
+        <is>
+          <t>443.323</t>
+        </is>
+      </c>
+      <c r="G249" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H249" s="2" t="inlineStr"/>
+    </row>
+    <row r="250">
+      <c r="A250" s="2" t="n">
+        <v>249</v>
+      </c>
+      <c r="B250" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="C250" s="2" t="inlineStr">
+        <is>
+          <t>Dispatch</t>
+        </is>
+      </c>
+      <c r="D250" s="2" t="inlineStr">
+        <is>
+          <t>ENG-11 G10: 10 loads with a stale 10-11 linehaul next to the 10-16 one — $30,170.00 revenue overstated in reports; rate change must replace, not add</t>
+        </is>
+      </c>
+      <c r="E250" s="2" t="inlineStr">
+        <is>
+          <t>CC-2</t>
+        </is>
+      </c>
+      <c r="F250" s="2" t="inlineStr">
+        <is>
+          <t>443.323</t>
+        </is>
+      </c>
+      <c r="G250" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H250" s="2" t="inlineStr"/>
+    </row>
+    <row r="251">
+      <c r="A251" s="2" t="n">
+        <v>250</v>
+      </c>
+      <c r="B251" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="C251" s="2" t="inlineStr">
+        <is>
+          <t>Settlements</t>
+        </is>
+      </c>
+      <c r="D251" s="2" t="inlineStr">
+        <is>
+          <t>ENG-12 G14: all 105 deductions typed 'other'; fine + I-94 permit posted to 7200 admin-fee account</t>
+        </is>
+      </c>
+      <c r="E251" s="2" t="inlineStr">
+        <is>
+          <t>CC-2</t>
+        </is>
+      </c>
+      <c r="F251" s="2" t="inlineStr">
+        <is>
+          <t>443.323</t>
+        </is>
+      </c>
+      <c r="G251" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H251" s="2" t="inlineStr"/>
+    </row>
+    <row r="252">
+      <c r="A252" s="2" t="n">
+        <v>251</v>
+      </c>
+      <c r="B252" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="C252" s="2" t="inlineStr">
+        <is>
+          <t>Dispatch</t>
+        </is>
+      </c>
+      <c r="D252" s="2" t="inlineStr">
+        <is>
+          <t>ENG-13 G1: 129 loads (10-11) with no trailer choice — back-fill from documents</t>
+        </is>
+      </c>
+      <c r="E252" s="2" t="inlineStr">
+        <is>
+          <t>CC-2</t>
+        </is>
+      </c>
+      <c r="F252" s="2" t="inlineStr">
+        <is>
+          <t>443.323</t>
+        </is>
+      </c>
+      <c r="G252" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H252" s="2" t="inlineStr"/>
+    </row>
+    <row r="253">
+      <c r="A253" s="2" t="n">
+        <v>252</v>
+      </c>
+      <c r="B253" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="C253" s="2" t="inlineStr">
+        <is>
+          <t>Driver pay</t>
+        </is>
+      </c>
+      <c r="D253" s="2" t="inlineStr">
+        <is>
+          <t>ENG-14 G9: 1 of 209 driver bills without a unit</t>
+        </is>
+      </c>
+      <c r="E253" s="2" t="inlineStr">
+        <is>
+          <t>CC-2</t>
+        </is>
+      </c>
+      <c r="F253" s="2" t="inlineStr">
+        <is>
+          <t>443.323</t>
+        </is>
+      </c>
+      <c r="G253" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H253" s="2" t="inlineStr"/>
+    </row>
+    <row r="254">
+      <c r="A254" s="2" t="n">
+        <v>253</v>
+      </c>
+      <c r="B254" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="C254" s="2" t="inlineStr">
+        <is>
+          <t>Accounting</t>
+        </is>
+      </c>
+      <c r="D254" s="2" t="inlineStr">
+        <is>
+          <t>ENG-15 maintenance bill writer must stamp linked_work_order_uuid + source</t>
+        </is>
+      </c>
+      <c r="E254" s="2" t="inlineStr">
+        <is>
+          <t>CC-2</t>
+        </is>
+      </c>
+      <c r="F254" s="2" t="inlineStr">
+        <is>
+          <t>443.323</t>
+        </is>
+      </c>
+      <c r="G254" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H254" s="2" t="inlineStr"/>
+    </row>
+    <row r="255">
+      <c r="A255" s="2" t="n">
+        <v>254</v>
+      </c>
+      <c r="B255" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="C255" s="2" t="inlineStr">
+        <is>
+          <t>Accounting</t>
+        </is>
+      </c>
+      <c r="D255" s="2" t="inlineStr">
+        <is>
+          <t>ENG-16 Check Creator not commissioned: check_number_registry 0 rows (starting number from owner)</t>
+        </is>
+      </c>
+      <c r="E255" s="2" t="inlineStr">
+        <is>
+          <t>CC-2</t>
+        </is>
+      </c>
+      <c r="F255" s="2" t="inlineStr">
+        <is>
+          <t>443.323</t>
+        </is>
+      </c>
+      <c r="G255" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H255" s="2" t="inlineStr"/>
+    </row>
+    <row r="256">
+      <c r="A256" s="2" t="n">
+        <v>255</v>
+      </c>
+      <c r="B256" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="C256" s="2" t="inlineStr">
+        <is>
+          <t>Accounting</t>
+        </is>
+      </c>
+      <c r="D256" s="2" t="inlineStr">
+        <is>
+          <t>ENG-17 1090 $170,210.48 / 2510 $187,894.21 residuals — tie document by document (rows 78, 79)</t>
+        </is>
+      </c>
+      <c r="E256" s="2" t="inlineStr">
+        <is>
+          <t>CC-2</t>
+        </is>
+      </c>
+      <c r="F256" s="2" t="inlineStr">
+        <is>
+          <t>443.323</t>
+        </is>
+      </c>
+      <c r="G256" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H256" s="2" t="inlineStr"/>
+    </row>
+    <row r="257">
+      <c r="A257" s="2" t="n">
+        <v>256</v>
+      </c>
+      <c r="B257" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="C257" s="2" t="inlineStr">
+        <is>
+          <t>Engine</t>
+        </is>
+      </c>
+      <c r="D257" s="2" t="inlineStr">
+        <is>
+          <t>ENG-18 prepare-commit-msg hook (amend vs new commit)</t>
+        </is>
+      </c>
+      <c r="E257" s="2" t="inlineStr">
+        <is>
+          <t>CC-2</t>
+        </is>
+      </c>
+      <c r="F257" s="2" t="inlineStr">
+        <is>
+          <t>443.323</t>
+        </is>
+      </c>
+      <c r="G257" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H257" s="2" t="inlineStr"/>
+    </row>
+    <row r="258">
+      <c r="A258" s="2" t="n">
+        <v>257</v>
+      </c>
+      <c r="B258" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="C258" s="2" t="inlineStr">
+        <is>
+          <t>Dispatch</t>
+        </is>
+      </c>
+      <c r="D258" s="2" t="inlineStr">
+        <is>
+          <t>ENG-22 G2: 195 of 198 loads on one trailer type id that does not resolve in catalogs.equipment_types — verify reefer vs dry van</t>
+        </is>
+      </c>
+      <c r="E258" s="2" t="inlineStr">
+        <is>
+          <t>CC-3</t>
+        </is>
+      </c>
+      <c r="F258" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="G258" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H258" s="2" t="inlineStr"/>
+    </row>
+    <row r="259">
+      <c r="A259" s="2" t="n">
+        <v>258</v>
+      </c>
+      <c r="B259" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="C259" s="2" t="inlineStr">
+        <is>
+          <t>Dispatch</t>
+        </is>
+      </c>
+      <c r="D259" s="2" t="inlineStr">
+        <is>
+          <t>ENG-23 G3: audit loads booked under the old oldest-customer fallback against their documents</t>
+        </is>
+      </c>
+      <c r="E259" s="2" t="inlineStr">
+        <is>
+          <t>CC-3</t>
+        </is>
+      </c>
+      <c r="F259" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="G259" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H259" s="2" t="inlineStr"/>
+    </row>
+    <row r="260">
+      <c r="A260" s="2" t="n">
+        <v>259</v>
+      </c>
+      <c r="B260" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="C260" s="2" t="inlineStr">
+        <is>
+          <t>Settlements</t>
+        </is>
+      </c>
+      <c r="D260" s="2" t="inlineStr">
+        <is>
+          <t>ENG-24 G4/G5/G13: prod checks — Creator owed bills posted + voided on Edit; 1 Creator line without a load; Creator expenses carry load links</t>
+        </is>
+      </c>
+      <c r="E260" s="2" t="inlineStr">
+        <is>
+          <t>CC-3</t>
+        </is>
+      </c>
+      <c r="F260" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="G260" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H260" s="2" t="inlineStr"/>
+    </row>
+    <row r="261">
+      <c r="A261" s="2" t="n">
+        <v>260</v>
+      </c>
+      <c r="B261" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="C261" s="2" t="inlineStr">
+        <is>
+          <t>Fuel</t>
+        </is>
+      </c>
+      <c r="D261" s="2" t="inlineStr">
+        <is>
+          <t>ENG-25 G7: confirm the fuel import path uses resolveFuelLoadAtTime (one rule)</t>
+        </is>
+      </c>
+      <c r="E261" s="2" t="inlineStr">
+        <is>
+          <t>CC-3</t>
+        </is>
+      </c>
+      <c r="F261" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="G261" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H261" s="2" t="inlineStr"/>
+    </row>
+    <row r="262">
+      <c r="A262" s="2" t="n">
+        <v>261</v>
+      </c>
+      <c r="B262" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="C262" s="2" t="inlineStr">
+        <is>
+          <t>Accounting</t>
+        </is>
+      </c>
+      <c r="D262" s="2" t="inlineStr">
+        <is>
+          <t>ENG-26 G8: 991 of 8,057 postings without a load — factoring 155, settlement 105 (rule per load), fuel 27 / expense 24 / invoice 4 documents with no load</t>
+        </is>
+      </c>
+      <c r="E262" s="2" t="inlineStr">
+        <is>
+          <t>CC-3</t>
+        </is>
+      </c>
+      <c r="F262" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="G262" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H262" s="2" t="inlineStr"/>
+    </row>
+    <row r="263">
+      <c r="A263" s="2" t="n">
+        <v>262</v>
+      </c>
+      <c r="B263" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="C263" s="2" t="inlineStr">
+        <is>
+          <t>Banking</t>
+        </is>
+      </c>
+      <c r="D263" s="2" t="inlineStr">
+        <is>
+          <t>ENG-27 G6: 458 bank-categorization postings before 10-17 without a load — back-fill or explain</t>
+        </is>
+      </c>
+      <c r="E263" s="2" t="inlineStr">
+        <is>
+          <t>CC-3</t>
+        </is>
+      </c>
+      <c r="F263" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="G263" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H263" s="2" t="inlineStr"/>
+    </row>
+    <row r="264">
+      <c r="A264" s="2" t="n">
+        <v>263</v>
+      </c>
+      <c r="B264" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="C264" s="2" t="inlineStr">
+        <is>
+          <t>Engine</t>
+        </is>
+      </c>
+      <c r="D264" s="2" t="inlineStr">
+        <is>
+          <t>ENG-28 posting single door: posting-line-writer.ts still inserts postings beside the engine — fold in or rule</t>
+        </is>
+      </c>
+      <c r="E264" s="2" t="inlineStr">
+        <is>
+          <t>CC-3</t>
+        </is>
+      </c>
+      <c r="F264" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="G264" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H264" s="2" t="inlineStr"/>
+    </row>
+    <row r="265">
+      <c r="A265" s="2" t="n">
+        <v>264</v>
+      </c>
+      <c r="B265" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="C265" s="2" t="inlineStr">
+        <is>
+          <t>Settlements</t>
+        </is>
+      </c>
+      <c r="D265" s="2" t="inlineStr">
+        <is>
+          <t>ENG-29 real driven miles: 12 of 198 loads have miles_driven_actual — fill from fence events</t>
+        </is>
+      </c>
+      <c r="E265" s="2" t="inlineStr">
+        <is>
+          <t>CC-3</t>
+        </is>
+      </c>
+      <c r="F265" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="G265" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H265" s="2" t="inlineStr"/>
+    </row>
+    <row r="266">
+      <c r="A266" s="2" t="n">
+        <v>265</v>
+      </c>
+      <c r="B266" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="C266" s="2" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="D266" s="2" t="inlineStr">
+        <is>
+          <t>ENG-30 15 raw &lt;select&gt; left (every selector multi-select law)</t>
+        </is>
+      </c>
+      <c r="E266" s="2" t="inlineStr">
+        <is>
+          <t>Cursor</t>
+        </is>
+      </c>
+      <c r="F266" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="G266" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H266" s="2" t="inlineStr"/>
+    </row>
+    <row r="267">
+      <c r="A267" s="2" t="n">
+        <v>266</v>
+      </c>
+      <c r="B267" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="C267" s="2" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="D267" s="2" t="inlineStr">
+        <is>
+          <t>ENG-31 breadcrumbs on 10 of 999 pages</t>
+        </is>
+      </c>
+      <c r="E267" s="2" t="inlineStr">
+        <is>
+          <t>Cursor</t>
+        </is>
+      </c>
+      <c r="F267" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="G267" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H267" s="2" t="inlineStr"/>
+    </row>
+    <row r="268">
+      <c r="A268" s="2" t="n">
+        <v>267</v>
+      </c>
+      <c r="B268" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="C268" s="2" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="D268" s="2" t="inlineStr">
+        <is>
+          <t>ENG-32 89 money cells do not open their transaction (re-measure + shrink)</t>
+        </is>
+      </c>
+      <c r="E268" s="2" t="inlineStr">
+        <is>
+          <t>Cursor</t>
+        </is>
+      </c>
+      <c r="F268" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="G268" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H268" s="2" t="inlineStr"/>
+    </row>
+    <row r="269">
+      <c r="A269" s="2" t="n">
+        <v>268</v>
+      </c>
+      <c r="B269" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="C269" s="2" t="inlineStr">
+        <is>
+          <t>Banking</t>
+        </is>
+      </c>
+      <c r="D269" s="2" t="inlineStr">
+        <is>
+          <t>ENG-33 stale 'orphaned MatchDrawer' comment in BankingTransactionsDesignView.tsx:4017</t>
+        </is>
+      </c>
+      <c r="E269" s="2" t="inlineStr">
+        <is>
+          <t>Cursor</t>
+        </is>
+      </c>
+      <c r="F269" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="G269" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H269" s="2" t="inlineStr"/>
+    </row>
+    <row r="270">
+      <c r="A270" s="2" t="n">
+        <v>269</v>
+      </c>
+      <c r="B270" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="C270" s="2" t="inlineStr">
+        <is>
+          <t>Engine</t>
+        </is>
+      </c>
+      <c r="D270" s="2" t="inlineStr">
+        <is>
+          <t>ENG-34 920 guard-exempt entries (CI does not run them) — wire or delete, shrink-only</t>
+        </is>
+      </c>
+      <c r="E270" s="2" t="inlineStr">
+        <is>
+          <t>CC-1</t>
+        </is>
+      </c>
+      <c r="F270" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="G270" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H270" s="2" t="inlineStr"/>
+    </row>
+    <row r="271">
+      <c r="A271" s="2" t="n">
+        <v>270</v>
+      </c>
+      <c r="B271" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="C271" s="2" t="inlineStr">
+        <is>
+          <t>Engine</t>
+        </is>
+      </c>
+      <c r="D271" s="2" t="inlineStr">
+        <is>
+          <t>ENG-35 re-run the full live engine-guard set (10-03: 119 failing) and list reds</t>
+        </is>
+      </c>
+      <c r="E271" s="2" t="inlineStr">
+        <is>
+          <t>LEAD</t>
+        </is>
+      </c>
+      <c r="F271" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="G271" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H271" s="2" t="inlineStr"/>
+    </row>
+    <row r="272">
+      <c r="A272" s="2" t="n">
+        <v>271</v>
+      </c>
+      <c r="B272" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="C272" s="2" t="inlineStr">
+        <is>
+          <t>Reports</t>
+        </is>
+      </c>
+      <c r="D272" s="2" t="inlineStr">
+        <is>
+          <t>ENG-36 23 company settlements still negative after ENG-19 — measure each</t>
+        </is>
+      </c>
+      <c r="E272" s="2" t="inlineStr">
+        <is>
+          <t>LEAD</t>
+        </is>
+      </c>
+      <c r="F272" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="G272" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H272" s="2" t="inlineStr"/>
+    </row>
+    <row r="273">
+      <c r="A273" s="2" t="n">
+        <v>272</v>
+      </c>
+      <c r="B273" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="C273" s="2" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="D273" s="2" t="inlineStr">
+        <is>
+          <t>ENG-37 natural-sign rendering: measure money columns not using naturalBalance</t>
+        </is>
+      </c>
+      <c r="E273" s="2" t="inlineStr">
+        <is>
+          <t>LEAD</t>
+        </is>
+      </c>
+      <c r="F273" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="G273" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H273" s="2" t="inlineStr"/>
+    </row>
+    <row r="274">
+      <c r="A274" s="2" t="n">
+        <v>273</v>
+      </c>
+      <c r="B274" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="C274" s="2" t="inlineStr">
+        <is>
+          <t>Accounting</t>
+        </is>
+      </c>
+      <c r="D274" s="2" t="inlineStr">
+        <is>
+          <t>ENG-38 periods: 24 USMCA periods all open — lock closed months (owner names the months)</t>
+        </is>
+      </c>
+      <c r="E274" s="2" t="inlineStr">
+        <is>
+          <t>OWNER</t>
+        </is>
+      </c>
+      <c r="F274" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="G274" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H274" s="2" t="inlineStr"/>
+    </row>
+    <row r="275">
+      <c r="A275" s="2" t="n">
+        <v>274</v>
+      </c>
+      <c r="B275" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="C275" s="2" t="inlineStr">
+        <is>
+          <t>Banking</t>
+        </is>
+      </c>
+      <c r="D275" s="2" t="inlineStr">
+        <is>
+          <t>M1 candidates scoped to the bank line's account</t>
+        </is>
+      </c>
+      <c r="E275" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F275" s="2" t="inlineStr">
+        <is>
+          <t>443.155</t>
+        </is>
+      </c>
+      <c r="G275" s="2" t="inlineStr">
+        <is>
+          <t>MERGED-UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="H275" s="2" t="inlineStr">
+        <is>
+          <t>722038f896</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="2" t="n">
+        <v>275</v>
+      </c>
+      <c r="B276" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="C276" s="2" t="inlineStr">
+        <is>
+          <t>Banking</t>
+        </is>
+      </c>
+      <c r="D276" s="2" t="inlineStr">
+        <is>
+          <t>M2 invoices + Faro purchases in the match union</t>
+        </is>
+      </c>
+      <c r="E276" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F276" s="2" t="inlineStr">
+        <is>
+          <t>443.155</t>
+        </is>
+      </c>
+      <c r="G276" s="2" t="inlineStr">
+        <is>
+          <t>MERGED-UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="H276" s="2" t="inlineStr">
+        <is>
+          <t>722038f896 add69bd031</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="2" t="n">
+        <v>276</v>
+      </c>
+      <c r="B277" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="C277" s="2" t="inlineStr">
+        <is>
+          <t>Banking</t>
+        </is>
+      </c>
+      <c r="D277" s="2" t="inlineStr">
+        <is>
+          <t>M3/M5 one matcher (MatchDrawer embedded); filters live</t>
+        </is>
+      </c>
+      <c r="E277" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F277" s="2" t="inlineStr">
+        <is>
+          <t>443.163</t>
+        </is>
+      </c>
+      <c r="G277" s="2" t="inlineStr">
+        <is>
+          <t>MERGED-UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="H277" s="2" t="inlineStr">
+        <is>
+          <t>8a58f20d9c</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="2" t="n">
+        <v>277</v>
+      </c>
+      <c r="B278" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="C278" s="2" t="inlineStr">
+        <is>
+          <t>Banking</t>
+        </is>
+      </c>
+      <c r="D278" s="2" t="inlineStr">
+        <is>
+          <t>M4 recon idempotency on transaction_source_links, not memo; 0 session-uuid memos on prod</t>
+        </is>
+      </c>
+      <c r="E278" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F278" s="2" t="inlineStr">
+        <is>
+          <t>390.3</t>
+        </is>
+      </c>
+      <c r="G278" s="2" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="H278" s="2" t="inlineStr">
+        <is>
+          <t>9147a9a055; prod 0/0</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="2" t="n">
+        <v>278</v>
+      </c>
+      <c r="B279" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="C279" s="2" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="D279" s="2" t="inlineStr">
+        <is>
+          <t>Palette: unselected boxes not pure white (0 of 1,556 files)</t>
+        </is>
+      </c>
+      <c r="E279" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F279" s="2" t="inlineStr">
+        <is>
+          <t>443.284</t>
+        </is>
+      </c>
+      <c r="G279" s="2" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="H279" s="2" t="inlineStr">
+        <is>
+          <t>75f1ed41d2; guard PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="2" t="n">
+        <v>279</v>
+      </c>
+      <c r="B280" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="C280" s="2" t="inlineStr">
+        <is>
+          <t>Dispatch</t>
+        </is>
+      </c>
+      <c r="D280" s="2" t="inlineStr">
+        <is>
+          <t>G1/G9/G11/G12/G15 code fixes merged (data remainders in ENG-07/08/13/14)</t>
+        </is>
+      </c>
+      <c r="E280" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F280" s="2" t="inlineStr">
+        <is>
+          <t>G-gaps</t>
+        </is>
+      </c>
+      <c r="G280" s="2" t="inlineStr">
+        <is>
+          <t>MERGED-UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="H280" s="2" t="inlineStr">
+        <is>
+          <t>6db7585fb6 4093026783 3b90a7f77b e136e13a58 0f1f83233e</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="2" t="n">
+        <v>280</v>
+      </c>
+      <c r="B281" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="C281" s="2" t="inlineStr">
+        <is>
+          <t>Accounting</t>
+        </is>
+      </c>
+      <c r="D281" s="2" t="inlineStr">
+        <is>
+          <t>Spine links: 0 of 8,057 postings without a spine link; TB 0</t>
+        </is>
+      </c>
+      <c r="E281" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F281" s="2" t="inlineStr">
+        <is>
+          <t>10-03</t>
+        </is>
+      </c>
+      <c r="G281" s="2" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="H281" s="2" t="inlineStr">
+        <is>
+          <t>prod measured 10-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="2" t="n">
+        <v>281</v>
+      </c>
+      <c r="B282" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="C282" s="2" t="inlineStr">
+        <is>
+          <t>Accounting</t>
+        </is>
+      </c>
+      <c r="D282" s="2" t="inlineStr">
+        <is>
+          <t>Cash-basis P&amp;L (F412), bank-line delete rule (F431), recurring worker refusal, 7-day unmatched alert, reefer off IFTA, A/P control by documents, matched-to-nothing refusal</t>
+        </is>
+      </c>
+      <c r="E282" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F282" s="2" t="inlineStr">
+        <is>
+          <t>various</t>
+        </is>
+      </c>
+      <c r="G282" s="2" t="inlineStr">
+        <is>
+          <t>MERGED-UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="H282" s="2" t="inlineStr">
+        <is>
+          <t>9b5809f1c0 3312d604a6 4693704449 202615380200 202615360600</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="2" t="n">
+        <v>282</v>
+      </c>
+      <c r="B283" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="C283" s="2" t="inlineStr">
+        <is>
+          <t>Engine</t>
+        </is>
+      </c>
+      <c r="D283" s="2" t="inlineStr">
+        <is>
+          <t>ENG-35 live sweep 10-24 3:10 PM CT: 339 live guards on a fresh prod fork — 283 PASS / 56 FAIL; split into ENG-39..53 + harness items</t>
+        </is>
+      </c>
+      <c r="E283" s="2" t="inlineStr">
+        <is>
+          <t>LEAD</t>
+        </is>
+      </c>
+      <c r="F283" s="2" t="inlineStr">
+        <is>
+          <t>ENG-35</t>
+        </is>
+      </c>
+      <c r="G283" s="2" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="H283" s="2" t="inlineStr">
+        <is>
+          <t>/tmp/live-results.txt; boxes 443.328/329/330</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="2" t="n">
+        <v>283</v>
+      </c>
+      <c r="B284" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="C284" s="2" t="inlineStr">
+        <is>
+          <t>Settlements</t>
+        </is>
+      </c>
+      <c r="D284" s="2" t="inlineStr">
+        <is>
+          <t>ENG-01c P-0119 settlement line deduction $10.00 has no driver_settlement_deductions row — writer + back-fill; ENG-01b refusal proven on fork</t>
+        </is>
+      </c>
+      <c r="E284" s="2" t="inlineStr">
+        <is>
+          <t>CC-1</t>
+        </is>
+      </c>
+      <c r="F284" s="2" t="inlineStr">
+        <is>
+          <t>443.322</t>
+        </is>
+      </c>
+      <c r="G284" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H284" s="2" t="inlineStr"/>
+    </row>
+    <row r="285">
+      <c r="A285" s="2" t="n">
+        <v>284</v>
+      </c>
+      <c r="B285" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="C285" s="2" t="inlineStr">
+        <is>
+          <t>Accounting</t>
+        </is>
+      </c>
+      <c r="D285" s="2" t="inlineStr">
+        <is>
+          <t>ENG-39 P0 vendor-balance view ≠ A/P GL by exactly the net pay of P-0113 (1,416.47) and P-0117 (329.51) — what the close owes vs what the view assumes</t>
+        </is>
+      </c>
+      <c r="E285" s="2" t="inlineStr">
+        <is>
+          <t>CC-1</t>
+        </is>
+      </c>
+      <c r="F285" s="2" t="inlineStr">
+        <is>
+          <t>443.328</t>
+        </is>
+      </c>
+      <c r="G285" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H285" s="2" t="inlineStr"/>
+    </row>
+    <row r="286">
+      <c r="A286" s="2" t="n">
+        <v>285</v>
+      </c>
+      <c r="B286" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="C286" s="2" t="inlineStr">
+        <is>
+          <t>Settlements</t>
+        </is>
+      </c>
+      <c r="D286" s="2" t="inlineStr">
+        <is>
+          <t>ENG-40 P-0067 and P-0119 closed with no company settlement</t>
+        </is>
+      </c>
+      <c r="E286" s="2" t="inlineStr">
+        <is>
+          <t>CC-1</t>
+        </is>
+      </c>
+      <c r="F286" s="2" t="inlineStr">
+        <is>
+          <t>443.328</t>
+        </is>
+      </c>
+      <c r="G286" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H286" s="2" t="inlineStr"/>
+    </row>
+    <row r="287">
+      <c r="A287" s="2" t="n">
+        <v>286</v>
+      </c>
+      <c r="B287" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="C287" s="2" t="inlineStr">
+        <is>
+          <t>Settlements</t>
+        </is>
+      </c>
+      <c r="D287" s="2" t="inlineStr">
+        <is>
+          <t>ENG-41 P-0121 cancelled but still reusable</t>
+        </is>
+      </c>
+      <c r="E287" s="2" t="inlineStr">
+        <is>
+          <t>CC-1</t>
+        </is>
+      </c>
+      <c r="F287" s="2" t="inlineStr">
+        <is>
+          <t>443.328</t>
+        </is>
+      </c>
+      <c r="G287" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H287" s="2" t="inlineStr"/>
+    </row>
+    <row r="288">
+      <c r="A288" s="2" t="n">
+        <v>287</v>
+      </c>
+      <c r="B288" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="C288" s="2" t="inlineStr">
+        <is>
+          <t>Settlements</t>
+        </is>
+      </c>
+      <c r="D288" s="2" t="inlineStr">
+        <is>
+          <t>ENG-42 89 active duplicate settlement-line groups</t>
+        </is>
+      </c>
+      <c r="E288" s="2" t="inlineStr">
+        <is>
+          <t>CC-1</t>
+        </is>
+      </c>
+      <c r="F288" s="2" t="inlineStr">
+        <is>
+          <t>443.328</t>
+        </is>
+      </c>
+      <c r="G288" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H288" s="2" t="inlineStr"/>
+    </row>
+    <row r="289">
+      <c r="A289" s="2" t="n">
+        <v>288</v>
+      </c>
+      <c r="B289" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="C289" s="2" t="inlineStr">
+        <is>
+          <t>Settlements</t>
+        </is>
+      </c>
+      <c r="D289" s="2" t="inlineStr">
+        <is>
+          <t>ENG-43 2 posted with zero load lines; P-0112/0116/0079/0114 $0 header; line ffac5c35 miles/rate NULL; closed-unposted with voided deduction</t>
+        </is>
+      </c>
+      <c r="E289" s="2" t="inlineStr">
+        <is>
+          <t>CC-1</t>
+        </is>
+      </c>
+      <c r="F289" s="2" t="inlineStr">
+        <is>
+          <t>443.328</t>
+        </is>
+      </c>
+      <c r="G289" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H289" s="2" t="inlineStr"/>
+    </row>
+    <row r="290">
+      <c r="A290" s="2" t="n">
+        <v>289</v>
+      </c>
+      <c r="B290" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="C290" s="2" t="inlineStr">
+        <is>
+          <t>Driver pay</t>
+        </is>
+      </c>
+      <c r="D290" s="2" t="inlineStr">
+        <is>
+          <t>ENG-44 bill 13697 due date; salaried stray bill not voided; presettlement autolink 13556/13563; live_load_number self-referential 13694/13695</t>
+        </is>
+      </c>
+      <c r="E290" s="2" t="inlineStr">
+        <is>
+          <t>CC-1</t>
+        </is>
+      </c>
+      <c r="F290" s="2" t="inlineStr">
+        <is>
+          <t>443.328</t>
+        </is>
+      </c>
+      <c r="G290" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H290" s="2" t="inlineStr"/>
+    </row>
+    <row r="291">
+      <c r="A291" s="2" t="n">
+        <v>290</v>
+      </c>
+      <c r="B291" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="C291" s="2" t="inlineStr">
+        <is>
+          <t>Drivers</t>
+        </is>
+      </c>
+      <c r="D291" s="2" t="inlineStr">
+        <is>
+          <t>ENG-45 2 settlement-active drivers without a Driver vendor (Carlos Mauricio Carvallo, Leonel Antonio Morales Noguez) — one profile per driver</t>
+        </is>
+      </c>
+      <c r="E291" s="2" t="inlineStr">
+        <is>
+          <t>CC-1</t>
+        </is>
+      </c>
+      <c r="F291" s="2" t="inlineStr">
+        <is>
+          <t>443.328</t>
+        </is>
+      </c>
+      <c r="G291" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H291" s="2" t="inlineStr"/>
+    </row>
+    <row r="292">
+      <c r="A292" s="2" t="n">
+        <v>291</v>
+      </c>
+      <c r="B292" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="C292" s="2" t="inlineStr">
+        <is>
+          <t>Accounting</t>
+        </is>
+      </c>
+      <c r="D292" s="2" t="inlineStr">
+        <is>
+          <t>ENG-46 bill_payment ad02cc37 no source link; escrow sub-ledger 315,000¢ vs baseline 132,500¢; 5796/P-0102 USMCA settlement for a Transportation document</t>
+        </is>
+      </c>
+      <c r="E292" s="2" t="inlineStr">
+        <is>
+          <t>CC-1</t>
+        </is>
+      </c>
+      <c r="F292" s="2" t="inlineStr">
+        <is>
+          <t>443.328</t>
+        </is>
+      </c>
+      <c r="G292" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H292" s="2" t="inlineStr"/>
+    </row>
+    <row r="293">
+      <c r="A293" s="2" t="n">
+        <v>292</v>
+      </c>
+      <c r="B293" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="C293" s="2" t="inlineStr">
+        <is>
+          <t>Engine</t>
+        </is>
+      </c>
+      <c r="D293" s="2" t="inlineStr">
+        <is>
+          <t>ENG-47 guards stale vs owner rulings: TIO PERFUMES kept; voids are design; S-13655/56; unbilled revenue migration; 'USMCA hidden'; archive tables RLS</t>
+        </is>
+      </c>
+      <c r="E293" s="2" t="inlineStr">
+        <is>
+          <t>CC-1</t>
+        </is>
+      </c>
+      <c r="F293" s="2" t="inlineStr">
+        <is>
+          <t>443.328</t>
+        </is>
+      </c>
+      <c r="G293" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H293" s="2" t="inlineStr"/>
+    </row>
+    <row r="294">
+      <c r="A294" s="2" t="n">
+        <v>293</v>
+      </c>
+      <c r="B294" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="C294" s="2" t="inlineStr">
+        <is>
+          <t>Fuel</t>
+        </is>
+      </c>
+      <c r="D294" s="2" t="inlineStr">
+        <is>
+          <t>ENG-48 fuel-expense one-to-one (13563-1 JE 0¢ + 14 loads); same-day duplicate fill pairs; traceability shrink fc461eb6; literal account '5000' in statement-card-credit-repair</t>
+        </is>
+      </c>
+      <c r="E294" s="2" t="inlineStr">
+        <is>
+          <t>CC-2</t>
+        </is>
+      </c>
+      <c r="F294" s="2" t="inlineStr">
+        <is>
+          <t>443.329</t>
+        </is>
+      </c>
+      <c r="G294" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H294" s="2" t="inlineStr"/>
+    </row>
+    <row r="295">
+      <c r="A295" s="2" t="n">
+        <v>294</v>
+      </c>
+      <c r="B295" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="C295" s="2" t="inlineStr">
+        <is>
+          <t>Settlements</t>
+        </is>
+      </c>
+      <c r="D295" s="2" t="inlineStr">
+        <is>
+          <t>ENG-49 settlement 5787 non-diesel expenses $235.01 vs signed $140.20</t>
+        </is>
+      </c>
+      <c r="E295" s="2" t="inlineStr">
+        <is>
+          <t>CC-2</t>
+        </is>
+      </c>
+      <c r="F295" s="2" t="inlineStr">
+        <is>
+          <t>443.329</t>
+        </is>
+      </c>
+      <c r="G295" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H295" s="2" t="inlineStr"/>
+    </row>
+    <row r="296">
+      <c r="A296" s="2" t="n">
+        <v>295</v>
+      </c>
+      <c r="B296" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="C296" s="2" t="inlineStr">
+        <is>
+          <t>Factoring</t>
+        </is>
+      </c>
+      <c r="D296" s="2" t="inlineStr">
+        <is>
+          <t>ENG-50 invoice amount_paid vs applications (9-13515 $525, 7 $350); book = Faro = AlwaysTrack 12 issues; factoring-advance-links-its-load selftest</t>
+        </is>
+      </c>
+      <c r="E296" s="2" t="inlineStr">
+        <is>
+          <t>CC-2</t>
+        </is>
+      </c>
+      <c r="F296" s="2" t="inlineStr">
+        <is>
+          <t>443.329</t>
+        </is>
+      </c>
+      <c r="G296" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H296" s="2" t="inlineStr"/>
+    </row>
+    <row r="297">
+      <c r="A297" s="2" t="n">
+        <v>296</v>
+      </c>
+      <c r="B297" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="C297" s="2" t="inlineStr">
+        <is>
+          <t>Banking</t>
+        </is>
+      </c>
+      <c r="D297" s="2" t="inlineStr">
+        <is>
+          <t>ENG-51 944 composite-memo rows unbackfilled; 1 Creator load miles without source</t>
+        </is>
+      </c>
+      <c r="E297" s="2" t="inlineStr">
+        <is>
+          <t>CC-2</t>
+        </is>
+      </c>
+      <c r="F297" s="2" t="inlineStr">
+        <is>
+          <t>443.329</t>
+        </is>
+      </c>
+      <c r="G297" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H297" s="2" t="inlineStr"/>
+    </row>
+    <row r="298">
+      <c r="A298" s="2" t="n">
+        <v>297</v>
+      </c>
+      <c r="B298" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="C298" s="2" t="inlineStr">
+        <is>
+          <t>Accounting</t>
+        </is>
+      </c>
+      <c r="D298" s="2" t="inlineStr">
+        <is>
+          <t>ENG-52 load-costs-board revenue not from loadCostRollupLateral (one source)</t>
+        </is>
+      </c>
+      <c r="E298" s="2" t="inlineStr">
+        <is>
+          <t>CC-2</t>
+        </is>
+      </c>
+      <c r="F298" s="2" t="inlineStr">
+        <is>
+          <t>443.329</t>
+        </is>
+      </c>
+      <c r="G298" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H298" s="2" t="inlineStr"/>
+    </row>
+    <row r="299">
+      <c r="A299" s="2" t="n">
+        <v>298</v>
+      </c>
+      <c r="B299" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="C299" s="2" t="inlineStr">
+        <is>
+          <t>Dispatch</t>
+        </is>
+      </c>
+      <c r="D299" s="2" t="inlineStr">
+        <is>
+          <t>ENG-53 13690 deadhead NULL; 16 live loads missing mileage; T174 odometer capture 49.7 h stale; 13700 no stop stamps; stops-gps-verified &gt; 120 s</t>
+        </is>
+      </c>
+      <c r="E299" s="2" t="inlineStr">
+        <is>
+          <t>CC-3</t>
+        </is>
+      </c>
+      <c r="F299" s="2" t="inlineStr">
+        <is>
+          <t>443.330</t>
+        </is>
+      </c>
+      <c r="G299" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H299" s="2" t="inlineStr"/>
+    </row>
+    <row r="300">
+      <c r="A300" s="2" t="n">
+        <v>299</v>
+      </c>
+      <c r="B300" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="C300" s="2" t="inlineStr">
+        <is>
+          <t>Fleet</t>
+        </is>
+      </c>
+      <c r="D300" s="2" t="inlineStr">
+        <is>
+          <t>ENG-54 T122, T124, T156 owned by IH 35 Transportation (leased to USMCA); rule: every real truck owned by IH 35 Trucking — waits for the owner's truck list (16 trucks)</t>
+        </is>
+      </c>
+      <c r="E300" s="2" t="inlineStr">
+        <is>
+          <t>OWNER</t>
+        </is>
+      </c>
+      <c r="F300" s="2" t="inlineStr">
+        <is>
+          <t>ENG-54</t>
+        </is>
+      </c>
+      <c r="G300" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H300" s="2" t="inlineStr"/>
+    </row>
+    <row r="301">
+      <c r="A301" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="B301" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="C301" s="2" t="inlineStr">
+        <is>
+          <t>Dispatch</t>
+        </is>
+      </c>
+      <c r="D301" s="2" t="inlineStr">
+        <is>
+          <t>ENG-55 443.327 app-wide drift alert every 30 min until fixed (reconciler I9: truck cannot make next stop, no stop date, no street address, no rate); 7 live</t>
+        </is>
+      </c>
+      <c r="E301" s="2" t="inlineStr">
+        <is>
+          <t>LEAD</t>
+        </is>
+      </c>
+      <c r="F301" s="2" t="inlineStr">
+        <is>
+          <t>443.327</t>
+        </is>
+      </c>
+      <c r="G301" s="2" t="inlineStr">
+        <is>
+          <t>CODED-QUEUED</t>
+        </is>
+      </c>
+      <c r="H301" s="2" t="inlineStr">
+        <is>
+          <t>eb338ebe94; reconciler 42/42, popup 5/5</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="2" t="n">
+        <v>301</v>
+      </c>
+      <c r="B302" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="C302" s="2" t="inlineStr">
+        <is>
+          <t>Fuel</t>
+        </is>
+      </c>
+      <c r="D302" s="2" t="inlineStr">
+        <is>
+          <t>ENG-25b owner 10-24 2:36 PM: Transportation diesel not on USMCA loads per signed docs = loan to Transportation (8000 Inter-company - IH35 Transportation) via rewriteDocumentLine</t>
+        </is>
+      </c>
+      <c r="E302" s="2" t="inlineStr">
+        <is>
+          <t>CC-3</t>
+        </is>
+      </c>
+      <c r="F302" s="2" t="inlineStr">
+        <is>
+          <t>443.324</t>
+        </is>
+      </c>
+      <c r="G302" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H302" s="2" t="inlineStr">
+        <is>
+          <t>Lead applies under AUTH-464</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="2" t="n">
+        <v>302</v>
+      </c>
+      <c r="B303" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="C303" s="2" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="D303" s="2" t="inlineStr">
+        <is>
+          <t>ENG-56 Cursor 443.326: V3 board grammar on all 23 PARTIAL/SHELL-ONLY surfaces of Cursor's own audit; one ratchet guard to 0</t>
+        </is>
+      </c>
+      <c r="E303" s="2" t="inlineStr">
+        <is>
+          <t>Cursor</t>
+        </is>
+      </c>
+      <c r="F303" s="2" t="inlineStr">
+        <is>
+          <t>443.326</t>
+        </is>
+      </c>
+      <c r="G303" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H303" s="2" t="inlineStr"/>
+    </row>
+    <row r="304">
+      <c r="A304" s="2" t="n">
+        <v>303</v>
+      </c>
+      <c r="B304" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="C304" s="2" t="inlineStr">
+        <is>
+          <t>Migrations</t>
+        </is>
+      </c>
+      <c r="D304" s="2" t="inlineStr">
+        <is>
+          <t>ENG-57 3 migrations held off prod 23 days waiting for a Lead fork validation (202614110000 source_document_ref unique; 202615210000/0100 lease-to-own ASC 842); 0000 carried a stale role list that fails on prod — fixed (dynamic append) and released; 0200 stays superseded</t>
+        </is>
+      </c>
+      <c r="E304" s="2" t="inlineStr">
+        <is>
+          <t>LEAD</t>
+        </is>
+      </c>
+      <c r="F304" s="2" t="inlineStr">
+        <is>
+          <t>443.331</t>
+        </is>
+      </c>
+      <c r="G304" s="2" t="inlineStr">
+        <is>
+          <t>CODED-QUEUED</t>
+        </is>
+      </c>
+      <c r="H304" s="2" t="inlineStr">
+        <is>
+          <t>1c1ea23b1e; real runner in prod mode on fresh fork: APPLY 3, SKIP 1,531, held untouched</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="2" t="n">
+        <v>304</v>
+      </c>
+      <c r="B305" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="C305" s="2" t="inlineStr">
+        <is>
+          <t>Engine</t>
+        </is>
+      </c>
+      <c r="D305" s="2" t="inlineStr">
+        <is>
+          <t>ENG-58 program-scoreboard.json 82 commits behind (max 80) failed every seat's step 1 — regenerated</t>
+        </is>
+      </c>
+      <c r="E305" s="2" t="inlineStr">
+        <is>
+          <t>LEAD</t>
+        </is>
+      </c>
+      <c r="F305" s="2" t="inlineStr">
+        <is>
+          <t>scoreboard</t>
+        </is>
+      </c>
+      <c r="G305" s="2" t="inlineStr">
+        <is>
+          <t>CODED-QUEUED</t>
+        </is>
+      </c>
+      <c r="H305" s="2" t="inlineStr">
+        <is>
+          <t>7de5f80937</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="2" t="n">
+        <v>305</v>
+      </c>
+      <c r="B306" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="C306" s="2" t="inlineStr">
+        <is>
+          <t>Engine</t>
+        </is>
+      </c>
+      <c r="D306" s="2" t="inlineStr">
+        <is>
+          <t>ENG-59 harness-only live failures (not data): pooler refused (list-apis, reports-neon-pv, loves-geofences), loopback-only fixture (invoice-header), CI-only file (no-sample-data), tsx import (recon-usmca), geocode key absent locally; rpt-s02 + invoice-copies PASS on rerun</t>
+        </is>
+      </c>
+      <c r="E306" s="2" t="inlineStr">
+        <is>
+          <t>LEAD</t>
+        </is>
+      </c>
+      <c r="F306" s="2" t="inlineStr">
+        <is>
+          <t>ENG-35</t>
+        </is>
+      </c>
+      <c r="G306" s="2" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="H306" s="2" t="inlineStr">
+        <is>
+          <t>rerun 10-24 3:25 PM CT</t>
         </is>
       </c>
     </row>

--- a/docs/bus/lead/LEAD-PENDING-REGISTER.xlsx
+++ b/docs/bus/lead/LEAD-PENDING-REGISTER.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H235"/>
+  <dimension ref="A1:H315"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2937,7 +2937,7 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>d7e5e14e54 #27323 board (all design sections) + 8cff827545 #27400 own module shell; Lawsuits tab kept (not on the board) — owner decides</t>
+          <t>d7e5e14e54 #27323 + 8cff827545 #27400; owner 10-24 3:47 PM: Lawsuits only in Legal — moved #27543 (443.332), Legal › Lawsuits = legal matters (443.334)</t>
         </is>
       </c>
     </row>
@@ -3447,7 +3447,11 @@
           <t>OPEN</t>
         </is>
       </c>
-      <c r="H79" s="2" t="inlineStr"/>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>-&gt; ENG-17 (CC-2 443.323)</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
@@ -3483,7 +3487,11 @@
           <t>OPEN</t>
         </is>
       </c>
-      <c r="H80" s="2" t="inlineStr"/>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>-&gt; ENG-17 (CC-2 443.323)</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
@@ -4388,12 +4396,12 @@
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>CODED-QUEUED</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>#27354 e8a9f02b; duplicate rows still live</t>
+          <t>443.320 25c5d51d8f: list in one query, parity 81/81, 120 s -&gt; 0.15 s</t>
         </is>
       </c>
     </row>
@@ -8816,12 +8824,12 @@
       </c>
       <c r="G216" s="2" t="inlineStr">
         <is>
-          <t>CODED</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="H216" s="2" t="inlineStr">
         <is>
-          <t>22dfcaadd7 #27472 (CC-1) escrow register per load</t>
+          <t>22dfcaadd7 #27472 coded; prod escrow_ledger 0 of 58 with load -&gt; ENG-03</t>
         </is>
       </c>
     </row>
@@ -8859,7 +8867,11 @@
           <t>OPEN</t>
         </is>
       </c>
-      <c r="H217" s="2" t="inlineStr"/>
+      <c r="H217" s="2" t="inlineStr">
+        <is>
+          <t>CC-1 #27478 blocked by ENG-01 (ledger ratchet)</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="n">
@@ -9441,7 +9453,7 @@
       </c>
       <c r="H232" s="2" t="inlineStr">
         <is>
-          <t>921aab82b4 claude/lead-443-305-loan-match; fork-proven match/unmatch/rematch (RPL-2026-0026/0027)</t>
+          <t>443.305 account-number fix 65a90b97e0, requeued</t>
         </is>
       </c>
     </row>
@@ -9564,6 +9576,2982 @@
           <t>claude/lead-443-308; paged 1,855 = single page</t>
         </is>
       </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="2" t="n">
+        <v>235</v>
+      </c>
+      <c r="B236" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="C236" s="2" t="inlineStr">
+        <is>
+          <t>Settlements</t>
+        </is>
+      </c>
+      <c r="D236" s="2" t="inlineStr">
+        <is>
+          <t>Escrow with a balance always visible (active or inactive driver); 11 orphan TEST escrow accounts deleted; DB refuses deleting a driver/vendor that still has escrow</t>
+        </is>
+      </c>
+      <c r="E236" s="2" t="inlineStr">
+        <is>
+          <t>LEAD</t>
+        </is>
+      </c>
+      <c r="F236" s="2" t="inlineStr">
+        <is>
+          <t>443.319</t>
+        </is>
+      </c>
+      <c r="G236" s="2" t="inlineStr">
+        <is>
+          <t>CODED-QUEUED</t>
+        </is>
+      </c>
+      <c r="H236" s="2" t="inlineStr">
+        <is>
+          <t>938da431f6; AUTH-462 prod COMMITTED 11 deleted; trigger refused on fork</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="2" t="n">
+        <v>236</v>
+      </c>
+      <c r="B237" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="C237" s="2" t="inlineStr">
+        <is>
+          <t>Reports</t>
+        </is>
+      </c>
+      <c r="D237" s="2" t="inlineStr">
+        <is>
+          <t>ENG-19 Company settlement report + Trip Profitability counted fuel twice (fuel fill's own expense); 61 of 81 settlements negative -&gt; 23; net -$177,024.87 -&gt; +$113,862.11; trips negative 66 of 92 -&gt; 25</t>
+        </is>
+      </c>
+      <c r="E237" s="2" t="inlineStr">
+        <is>
+          <t>LEAD</t>
+        </is>
+      </c>
+      <c r="F237" s="2" t="inlineStr">
+        <is>
+          <t>443.321</t>
+        </is>
+      </c>
+      <c r="G237" s="2" t="inlineStr">
+        <is>
+          <t>CODED-QUEUED</t>
+        </is>
+      </c>
+      <c r="H237" s="2" t="inlineStr">
+        <is>
+          <t>2a4fbbc2d3; parity 81/81 to the cent; guard red on old engines</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="2" t="n">
+        <v>237</v>
+      </c>
+      <c r="B238" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="C238" s="2" t="inlineStr">
+        <is>
+          <t>Ledger</t>
+        </is>
+      </c>
+      <c r="D238" s="2" t="inlineStr">
+        <is>
+          <t>AUTH-461 / AUTH-462 recorded in OWNER-AUTHORIZATIONS.md with owner quotes and audit counts</t>
+        </is>
+      </c>
+      <c r="E238" s="2" t="inlineStr">
+        <is>
+          <t>LEAD</t>
+        </is>
+      </c>
+      <c r="F238" s="2" t="inlineStr">
+        <is>
+          <t>AUTH ledger</t>
+        </is>
+      </c>
+      <c r="G238" s="2" t="inlineStr">
+        <is>
+          <t>CODED-QUEUED</t>
+        </is>
+      </c>
+      <c r="H238" s="2" t="inlineStr">
+        <is>
+          <t>claude/lead-auth-461-462-ledger</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="2" t="n">
+        <v>238</v>
+      </c>
+      <c r="B239" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="C239" s="2" t="inlineStr">
+        <is>
+          <t>Dispatch</t>
+        </is>
+      </c>
+      <c r="D239" s="2" t="inlineStr">
+        <is>
+          <t>Load 13699 (Copamex, in transit) delivery stop is 'Bradley, IL' with no street; verify-stops-are-geocoded RED live, blocks dispatch-touching pushes (443.301)</t>
+        </is>
+      </c>
+      <c r="E239" s="2" t="inlineStr">
+        <is>
+          <t>OWNER</t>
+        </is>
+      </c>
+      <c r="F239" s="2" t="inlineStr">
+        <is>
+          <t>ENG-21</t>
+        </is>
+      </c>
+      <c r="G239" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H239" s="2" t="inlineStr">
+        <is>
+          <t>owner gives the delivery street address; Lead enters it</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="2" t="n">
+        <v>239</v>
+      </c>
+      <c r="B240" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="C240" s="2" t="inlineStr">
+        <is>
+          <t>Settlements</t>
+        </is>
+      </c>
+      <c r="D240" s="2" t="inlineStr">
+        <is>
+          <t>ENG-01 P-0113/P-0117/P-0119 closed but never posted (posted_at NULL, 0 postings); ledger ratchet 1 -&gt; live 3; blocks #27478. DB refusal: no close without posting</t>
+        </is>
+      </c>
+      <c r="E240" s="2" t="inlineStr">
+        <is>
+          <t>CC-1</t>
+        </is>
+      </c>
+      <c r="F240" s="2" t="inlineStr">
+        <is>
+          <t>443.322</t>
+        </is>
+      </c>
+      <c r="G240" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H240" s="2" t="inlineStr"/>
+    </row>
+    <row r="241">
+      <c r="A241" s="2" t="n">
+        <v>240</v>
+      </c>
+      <c r="B241" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="C241" s="2" t="inlineStr">
+        <is>
+          <t>Driver pay</t>
+        </is>
+      </c>
+      <c r="D241" s="2" t="inlineStr">
+        <is>
+          <t>ENG-02 driver_pay_cents reads the accrued A/P bill, not driver_bills.gross (13574 $1,538.81 vs $957.55)</t>
+        </is>
+      </c>
+      <c r="E241" s="2" t="inlineStr">
+        <is>
+          <t>CC-1</t>
+        </is>
+      </c>
+      <c r="F241" s="2" t="inlineStr">
+        <is>
+          <t>443.322</t>
+        </is>
+      </c>
+      <c r="G241" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H241" s="2" t="inlineStr"/>
+    </row>
+    <row r="242">
+      <c r="A242" s="2" t="n">
+        <v>241</v>
+      </c>
+      <c r="B242" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="C242" s="2" t="inlineStr">
+        <is>
+          <t>Settlements</t>
+        </is>
+      </c>
+      <c r="D242" s="2" t="inlineStr">
+        <is>
+          <t>ENG-03 escrow_ledger 58 rows, 0 with load_id — writer stamps the load; back-fill</t>
+        </is>
+      </c>
+      <c r="E242" s="2" t="inlineStr">
+        <is>
+          <t>CC-1</t>
+        </is>
+      </c>
+      <c r="F242" s="2" t="inlineStr">
+        <is>
+          <t>443.322</t>
+        </is>
+      </c>
+      <c r="G242" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H242" s="2" t="inlineStr"/>
+    </row>
+    <row r="243">
+      <c r="A243" s="2" t="n">
+        <v>242</v>
+      </c>
+      <c r="B243" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="C243" s="2" t="inlineStr">
+        <is>
+          <t>Accounting</t>
+        </is>
+      </c>
+      <c r="D243" s="2" t="inlineStr">
+        <is>
+          <t>ENG-04 2170 Driver Net-Pay Clearing Cr $2,575.96 / 12 postings — tie to open net pay, clear through documents</t>
+        </is>
+      </c>
+      <c r="E243" s="2" t="inlineStr">
+        <is>
+          <t>CC-1</t>
+        </is>
+      </c>
+      <c r="F243" s="2" t="inlineStr">
+        <is>
+          <t>443.322</t>
+        </is>
+      </c>
+      <c r="G243" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H243" s="2" t="inlineStr"/>
+    </row>
+    <row r="244">
+      <c r="A244" s="2" t="n">
+        <v>243</v>
+      </c>
+      <c r="B244" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="C244" s="2" t="inlineStr">
+        <is>
+          <t>Engine</t>
+        </is>
+      </c>
+      <c r="D244" s="2" t="inlineStr">
+        <is>
+          <t>ENG-05 swallowed DB errors grew 122 -&gt; 125 — fix the 3 new, baseline back to 122</t>
+        </is>
+      </c>
+      <c r="E244" s="2" t="inlineStr">
+        <is>
+          <t>CC-1</t>
+        </is>
+      </c>
+      <c r="F244" s="2" t="inlineStr">
+        <is>
+          <t>443.322</t>
+        </is>
+      </c>
+      <c r="G244" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H244" s="2" t="inlineStr"/>
+    </row>
+    <row r="245">
+      <c r="A245" s="2" t="n">
+        <v>244</v>
+      </c>
+      <c r="B245" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="C245" s="2" t="inlineStr">
+        <is>
+          <t>Engine</t>
+        </is>
+      </c>
+      <c r="D245" s="2" t="inlineStr">
+        <is>
+          <t>ENG-06 two overlapping spine guards (-has-a- / -has-its-, step claimed twice) — merge</t>
+        </is>
+      </c>
+      <c r="E245" s="2" t="inlineStr">
+        <is>
+          <t>CC-1</t>
+        </is>
+      </c>
+      <c r="F245" s="2" t="inlineStr">
+        <is>
+          <t>443.322</t>
+        </is>
+      </c>
+      <c r="G245" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H245" s="2" t="inlineStr"/>
+    </row>
+    <row r="246">
+      <c r="A246" s="2" t="n">
+        <v>245</v>
+      </c>
+      <c r="B246" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="C246" s="2" t="inlineStr">
+        <is>
+          <t>Dispatch</t>
+        </is>
+      </c>
+      <c r="D246" s="2" t="inlineStr">
+        <is>
+          <t>ENG-07 G11: 8 of 410 stops without geocode precision since 10-13; Book/Edit Load must refuse a city-only stop</t>
+        </is>
+      </c>
+      <c r="E246" s="2" t="inlineStr">
+        <is>
+          <t>CC-1</t>
+        </is>
+      </c>
+      <c r="F246" s="2" t="inlineStr">
+        <is>
+          <t>443.322</t>
+        </is>
+      </c>
+      <c r="G246" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H246" s="2" t="inlineStr"/>
+    </row>
+    <row r="247">
+      <c r="A247" s="2" t="n">
+        <v>246</v>
+      </c>
+      <c r="B247" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="C247" s="2" t="inlineStr">
+        <is>
+          <t>Driver pay</t>
+        </is>
+      </c>
+      <c r="D247" s="2" t="inlineStr">
+        <is>
+          <t>ENG-08 G15: prod check every lumper advance since 0f1f83233e posts as the load's lumper expense</t>
+        </is>
+      </c>
+      <c r="E247" s="2" t="inlineStr">
+        <is>
+          <t>CC-1</t>
+        </is>
+      </c>
+      <c r="F247" s="2" t="inlineStr">
+        <is>
+          <t>443.322</t>
+        </is>
+      </c>
+      <c r="G247" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H247" s="2" t="inlineStr"/>
+    </row>
+    <row r="248">
+      <c r="A248" s="2" t="n">
+        <v>247</v>
+      </c>
+      <c r="B248" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="C248" s="2" t="inlineStr">
+        <is>
+          <t>Engine</t>
+        </is>
+      </c>
+      <c r="D248" s="2" t="inlineStr">
+        <is>
+          <t>ENG-09 THE GUARANTEE: verify-engine-register-closed-by-guard — a register row is DONE only with a wired guard + evidence; wired in step 1</t>
+        </is>
+      </c>
+      <c r="E248" s="2" t="inlineStr">
+        <is>
+          <t>CC-1</t>
+        </is>
+      </c>
+      <c r="F248" s="2" t="inlineStr">
+        <is>
+          <t>443.322</t>
+        </is>
+      </c>
+      <c r="G248" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H248" s="2" t="inlineStr">
+        <is>
+          <t>reads docs/bus/lead/ENGINE-REGISTER.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="2" t="n">
+        <v>248</v>
+      </c>
+      <c r="B249" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="C249" s="2" t="inlineStr">
+        <is>
+          <t>Fuel</t>
+        </is>
+      </c>
+      <c r="D249" s="2" t="inlineStr">
+        <is>
+          <t>ENG-10 duplicate documents regressed 11 -&gt; 36 groups (guard RED): 31 card-discount groups; 5 &gt;= $1 (Relay 10-11 $623.75, Relay 09-23 $527.58, LOVES $15.25 x3)</t>
+        </is>
+      </c>
+      <c r="E249" s="2" t="inlineStr">
+        <is>
+          <t>CC-2</t>
+        </is>
+      </c>
+      <c r="F249" s="2" t="inlineStr">
+        <is>
+          <t>443.323</t>
+        </is>
+      </c>
+      <c r="G249" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H249" s="2" t="inlineStr"/>
+    </row>
+    <row r="250">
+      <c r="A250" s="2" t="n">
+        <v>249</v>
+      </c>
+      <c r="B250" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="C250" s="2" t="inlineStr">
+        <is>
+          <t>Dispatch</t>
+        </is>
+      </c>
+      <c r="D250" s="2" t="inlineStr">
+        <is>
+          <t>ENG-11 G10: 10 loads with a stale 10-11 linehaul next to the 10-16 one — $30,170.00 revenue overstated in reports; rate change must replace, not add</t>
+        </is>
+      </c>
+      <c r="E250" s="2" t="inlineStr">
+        <is>
+          <t>CC-2</t>
+        </is>
+      </c>
+      <c r="F250" s="2" t="inlineStr">
+        <is>
+          <t>443.323</t>
+        </is>
+      </c>
+      <c r="G250" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H250" s="2" t="inlineStr"/>
+    </row>
+    <row r="251">
+      <c r="A251" s="2" t="n">
+        <v>250</v>
+      </c>
+      <c r="B251" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="C251" s="2" t="inlineStr">
+        <is>
+          <t>Settlements</t>
+        </is>
+      </c>
+      <c r="D251" s="2" t="inlineStr">
+        <is>
+          <t>ENG-12 G14: all 105 deductions typed 'other'; fine + I-94 permit posted to 7200 admin-fee account</t>
+        </is>
+      </c>
+      <c r="E251" s="2" t="inlineStr">
+        <is>
+          <t>CC-2</t>
+        </is>
+      </c>
+      <c r="F251" s="2" t="inlineStr">
+        <is>
+          <t>443.323</t>
+        </is>
+      </c>
+      <c r="G251" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H251" s="2" t="inlineStr"/>
+    </row>
+    <row r="252">
+      <c r="A252" s="2" t="n">
+        <v>251</v>
+      </c>
+      <c r="B252" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="C252" s="2" t="inlineStr">
+        <is>
+          <t>Dispatch</t>
+        </is>
+      </c>
+      <c r="D252" s="2" t="inlineStr">
+        <is>
+          <t>ENG-13 G1: 129 loads (10-11) with no trailer choice — back-fill from documents</t>
+        </is>
+      </c>
+      <c r="E252" s="2" t="inlineStr">
+        <is>
+          <t>CC-2</t>
+        </is>
+      </c>
+      <c r="F252" s="2" t="inlineStr">
+        <is>
+          <t>443.323</t>
+        </is>
+      </c>
+      <c r="G252" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H252" s="2" t="inlineStr"/>
+    </row>
+    <row r="253">
+      <c r="A253" s="2" t="n">
+        <v>252</v>
+      </c>
+      <c r="B253" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="C253" s="2" t="inlineStr">
+        <is>
+          <t>Driver pay</t>
+        </is>
+      </c>
+      <c r="D253" s="2" t="inlineStr">
+        <is>
+          <t>ENG-14 G9: 1 of 209 driver bills without a unit</t>
+        </is>
+      </c>
+      <c r="E253" s="2" t="inlineStr">
+        <is>
+          <t>CC-2</t>
+        </is>
+      </c>
+      <c r="F253" s="2" t="inlineStr">
+        <is>
+          <t>443.323</t>
+        </is>
+      </c>
+      <c r="G253" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H253" s="2" t="inlineStr"/>
+    </row>
+    <row r="254">
+      <c r="A254" s="2" t="n">
+        <v>253</v>
+      </c>
+      <c r="B254" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="C254" s="2" t="inlineStr">
+        <is>
+          <t>Accounting</t>
+        </is>
+      </c>
+      <c r="D254" s="2" t="inlineStr">
+        <is>
+          <t>ENG-15 maintenance bill writer must stamp linked_work_order_uuid + source</t>
+        </is>
+      </c>
+      <c r="E254" s="2" t="inlineStr">
+        <is>
+          <t>CC-2</t>
+        </is>
+      </c>
+      <c r="F254" s="2" t="inlineStr">
+        <is>
+          <t>443.323</t>
+        </is>
+      </c>
+      <c r="G254" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H254" s="2" t="inlineStr"/>
+    </row>
+    <row r="255">
+      <c r="A255" s="2" t="n">
+        <v>254</v>
+      </c>
+      <c r="B255" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="C255" s="2" t="inlineStr">
+        <is>
+          <t>Accounting</t>
+        </is>
+      </c>
+      <c r="D255" s="2" t="inlineStr">
+        <is>
+          <t>ENG-16 Check Creator not commissioned: check_number_registry 0 rows (starting number from owner)</t>
+        </is>
+      </c>
+      <c r="E255" s="2" t="inlineStr">
+        <is>
+          <t>CC-2</t>
+        </is>
+      </c>
+      <c r="F255" s="2" t="inlineStr">
+        <is>
+          <t>443.323</t>
+        </is>
+      </c>
+      <c r="G255" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H255" s="2" t="inlineStr"/>
+    </row>
+    <row r="256">
+      <c r="A256" s="2" t="n">
+        <v>255</v>
+      </c>
+      <c r="B256" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="C256" s="2" t="inlineStr">
+        <is>
+          <t>Accounting</t>
+        </is>
+      </c>
+      <c r="D256" s="2" t="inlineStr">
+        <is>
+          <t>ENG-17 1090 $170,210.48 / 2510 $187,894.21 residuals — tie document by document (rows 78, 79)</t>
+        </is>
+      </c>
+      <c r="E256" s="2" t="inlineStr">
+        <is>
+          <t>CC-2</t>
+        </is>
+      </c>
+      <c r="F256" s="2" t="inlineStr">
+        <is>
+          <t>443.323</t>
+        </is>
+      </c>
+      <c r="G256" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H256" s="2" t="inlineStr"/>
+    </row>
+    <row r="257">
+      <c r="A257" s="2" t="n">
+        <v>256</v>
+      </c>
+      <c r="B257" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="C257" s="2" t="inlineStr">
+        <is>
+          <t>Engine</t>
+        </is>
+      </c>
+      <c r="D257" s="2" t="inlineStr">
+        <is>
+          <t>ENG-18 prepare-commit-msg hook (amend vs new commit)</t>
+        </is>
+      </c>
+      <c r="E257" s="2" t="inlineStr">
+        <is>
+          <t>CC-2</t>
+        </is>
+      </c>
+      <c r="F257" s="2" t="inlineStr">
+        <is>
+          <t>443.323</t>
+        </is>
+      </c>
+      <c r="G257" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H257" s="2" t="inlineStr"/>
+    </row>
+    <row r="258">
+      <c r="A258" s="2" t="n">
+        <v>257</v>
+      </c>
+      <c r="B258" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="C258" s="2" t="inlineStr">
+        <is>
+          <t>Dispatch</t>
+        </is>
+      </c>
+      <c r="D258" s="2" t="inlineStr">
+        <is>
+          <t>ENG-22 G2: 195 of 198 loads on one trailer type id that does not resolve in catalogs.equipment_types — verify reefer vs dry van</t>
+        </is>
+      </c>
+      <c r="E258" s="2" t="inlineStr">
+        <is>
+          <t>CC-3</t>
+        </is>
+      </c>
+      <c r="F258" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="G258" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H258" s="2" t="inlineStr"/>
+    </row>
+    <row r="259">
+      <c r="A259" s="2" t="n">
+        <v>258</v>
+      </c>
+      <c r="B259" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="C259" s="2" t="inlineStr">
+        <is>
+          <t>Dispatch</t>
+        </is>
+      </c>
+      <c r="D259" s="2" t="inlineStr">
+        <is>
+          <t>ENG-23 G3: audit loads booked under the old oldest-customer fallback against their documents</t>
+        </is>
+      </c>
+      <c r="E259" s="2" t="inlineStr">
+        <is>
+          <t>CC-3</t>
+        </is>
+      </c>
+      <c r="F259" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="G259" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H259" s="2" t="inlineStr"/>
+    </row>
+    <row r="260">
+      <c r="A260" s="2" t="n">
+        <v>259</v>
+      </c>
+      <c r="B260" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="C260" s="2" t="inlineStr">
+        <is>
+          <t>Settlements</t>
+        </is>
+      </c>
+      <c r="D260" s="2" t="inlineStr">
+        <is>
+          <t>ENG-24 G4/G5/G13: prod checks — Creator owed bills posted + voided on Edit; 1 Creator line without a load; Creator expenses carry load links</t>
+        </is>
+      </c>
+      <c r="E260" s="2" t="inlineStr">
+        <is>
+          <t>CC-3</t>
+        </is>
+      </c>
+      <c r="F260" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="G260" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H260" s="2" t="inlineStr"/>
+    </row>
+    <row r="261">
+      <c r="A261" s="2" t="n">
+        <v>260</v>
+      </c>
+      <c r="B261" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="C261" s="2" t="inlineStr">
+        <is>
+          <t>Fuel</t>
+        </is>
+      </c>
+      <c r="D261" s="2" t="inlineStr">
+        <is>
+          <t>ENG-25 G7: confirm the fuel import path uses resolveFuelLoadAtTime (one rule)</t>
+        </is>
+      </c>
+      <c r="E261" s="2" t="inlineStr">
+        <is>
+          <t>CC-3</t>
+        </is>
+      </c>
+      <c r="F261" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="G261" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H261" s="2" t="inlineStr"/>
+    </row>
+    <row r="262">
+      <c r="A262" s="2" t="n">
+        <v>261</v>
+      </c>
+      <c r="B262" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="C262" s="2" t="inlineStr">
+        <is>
+          <t>Accounting</t>
+        </is>
+      </c>
+      <c r="D262" s="2" t="inlineStr">
+        <is>
+          <t>ENG-26 G8: 991 of 8,057 postings without a load — factoring 155, settlement 105 (rule per load), fuel 27 / expense 24 / invoice 4 documents with no load</t>
+        </is>
+      </c>
+      <c r="E262" s="2" t="inlineStr">
+        <is>
+          <t>CC-3</t>
+        </is>
+      </c>
+      <c r="F262" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="G262" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H262" s="2" t="inlineStr"/>
+    </row>
+    <row r="263">
+      <c r="A263" s="2" t="n">
+        <v>262</v>
+      </c>
+      <c r="B263" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="C263" s="2" t="inlineStr">
+        <is>
+          <t>Banking</t>
+        </is>
+      </c>
+      <c r="D263" s="2" t="inlineStr">
+        <is>
+          <t>ENG-27 G6: 458 bank-categorization postings before 10-17 without a load — back-fill or explain</t>
+        </is>
+      </c>
+      <c r="E263" s="2" t="inlineStr">
+        <is>
+          <t>CC-3</t>
+        </is>
+      </c>
+      <c r="F263" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="G263" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H263" s="2" t="inlineStr"/>
+    </row>
+    <row r="264">
+      <c r="A264" s="2" t="n">
+        <v>263</v>
+      </c>
+      <c r="B264" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="C264" s="2" t="inlineStr">
+        <is>
+          <t>Engine</t>
+        </is>
+      </c>
+      <c r="D264" s="2" t="inlineStr">
+        <is>
+          <t>ENG-28 posting single door: posting-line-writer.ts still inserts postings beside the engine — fold in or rule</t>
+        </is>
+      </c>
+      <c r="E264" s="2" t="inlineStr">
+        <is>
+          <t>CC-3</t>
+        </is>
+      </c>
+      <c r="F264" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="G264" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H264" s="2" t="inlineStr"/>
+    </row>
+    <row r="265">
+      <c r="A265" s="2" t="n">
+        <v>264</v>
+      </c>
+      <c r="B265" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="C265" s="2" t="inlineStr">
+        <is>
+          <t>Settlements</t>
+        </is>
+      </c>
+      <c r="D265" s="2" t="inlineStr">
+        <is>
+          <t>ENG-29 real driven miles: 12 of 198 loads have miles_driven_actual — fill from fence events</t>
+        </is>
+      </c>
+      <c r="E265" s="2" t="inlineStr">
+        <is>
+          <t>CC-3</t>
+        </is>
+      </c>
+      <c r="F265" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="G265" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H265" s="2" t="inlineStr"/>
+    </row>
+    <row r="266">
+      <c r="A266" s="2" t="n">
+        <v>265</v>
+      </c>
+      <c r="B266" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="C266" s="2" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="D266" s="2" t="inlineStr">
+        <is>
+          <t>ENG-30 15 raw &lt;select&gt; left (every selector multi-select law)</t>
+        </is>
+      </c>
+      <c r="E266" s="2" t="inlineStr">
+        <is>
+          <t>Cursor</t>
+        </is>
+      </c>
+      <c r="F266" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="G266" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H266" s="2" t="inlineStr"/>
+    </row>
+    <row r="267">
+      <c r="A267" s="2" t="n">
+        <v>266</v>
+      </c>
+      <c r="B267" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="C267" s="2" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="D267" s="2" t="inlineStr">
+        <is>
+          <t>ENG-31 breadcrumbs on 10 of 999 pages</t>
+        </is>
+      </c>
+      <c r="E267" s="2" t="inlineStr">
+        <is>
+          <t>Cursor</t>
+        </is>
+      </c>
+      <c r="F267" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="G267" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H267" s="2" t="inlineStr"/>
+    </row>
+    <row r="268">
+      <c r="A268" s="2" t="n">
+        <v>267</v>
+      </c>
+      <c r="B268" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="C268" s="2" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="D268" s="2" t="inlineStr">
+        <is>
+          <t>ENG-32 89 money cells do not open their transaction (re-measure + shrink)</t>
+        </is>
+      </c>
+      <c r="E268" s="2" t="inlineStr">
+        <is>
+          <t>Cursor</t>
+        </is>
+      </c>
+      <c r="F268" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="G268" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H268" s="2" t="inlineStr"/>
+    </row>
+    <row r="269">
+      <c r="A269" s="2" t="n">
+        <v>268</v>
+      </c>
+      <c r="B269" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="C269" s="2" t="inlineStr">
+        <is>
+          <t>Banking</t>
+        </is>
+      </c>
+      <c r="D269" s="2" t="inlineStr">
+        <is>
+          <t>ENG-33 stale 'orphaned MatchDrawer' comment in BankingTransactionsDesignView.tsx:4017</t>
+        </is>
+      </c>
+      <c r="E269" s="2" t="inlineStr">
+        <is>
+          <t>Cursor</t>
+        </is>
+      </c>
+      <c r="F269" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="G269" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H269" s="2" t="inlineStr"/>
+    </row>
+    <row r="270">
+      <c r="A270" s="2" t="n">
+        <v>269</v>
+      </c>
+      <c r="B270" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="C270" s="2" t="inlineStr">
+        <is>
+          <t>Engine</t>
+        </is>
+      </c>
+      <c r="D270" s="2" t="inlineStr">
+        <is>
+          <t>ENG-34 920 guard-exempt entries (CI does not run them) — wire or delete, shrink-only</t>
+        </is>
+      </c>
+      <c r="E270" s="2" t="inlineStr">
+        <is>
+          <t>CC-1</t>
+        </is>
+      </c>
+      <c r="F270" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="G270" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H270" s="2" t="inlineStr"/>
+    </row>
+    <row r="271">
+      <c r="A271" s="2" t="n">
+        <v>270</v>
+      </c>
+      <c r="B271" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="C271" s="2" t="inlineStr">
+        <is>
+          <t>Engine</t>
+        </is>
+      </c>
+      <c r="D271" s="2" t="inlineStr">
+        <is>
+          <t>ENG-35 re-run the full live engine-guard set (10-03: 119 failing) and list reds</t>
+        </is>
+      </c>
+      <c r="E271" s="2" t="inlineStr">
+        <is>
+          <t>LEAD</t>
+        </is>
+      </c>
+      <c r="F271" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="G271" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H271" s="2" t="inlineStr"/>
+    </row>
+    <row r="272">
+      <c r="A272" s="2" t="n">
+        <v>271</v>
+      </c>
+      <c r="B272" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="C272" s="2" t="inlineStr">
+        <is>
+          <t>Reports</t>
+        </is>
+      </c>
+      <c r="D272" s="2" t="inlineStr">
+        <is>
+          <t>ENG-36 23 company settlements still negative after ENG-19 — measure each</t>
+        </is>
+      </c>
+      <c r="E272" s="2" t="inlineStr">
+        <is>
+          <t>LEAD</t>
+        </is>
+      </c>
+      <c r="F272" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="G272" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H272" s="2" t="inlineStr"/>
+    </row>
+    <row r="273">
+      <c r="A273" s="2" t="n">
+        <v>272</v>
+      </c>
+      <c r="B273" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="C273" s="2" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="D273" s="2" t="inlineStr">
+        <is>
+          <t>ENG-37 natural-sign rendering: measure money columns not using naturalBalance</t>
+        </is>
+      </c>
+      <c r="E273" s="2" t="inlineStr">
+        <is>
+          <t>LEAD</t>
+        </is>
+      </c>
+      <c r="F273" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="G273" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H273" s="2" t="inlineStr"/>
+    </row>
+    <row r="274">
+      <c r="A274" s="2" t="n">
+        <v>273</v>
+      </c>
+      <c r="B274" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="C274" s="2" t="inlineStr">
+        <is>
+          <t>Accounting</t>
+        </is>
+      </c>
+      <c r="D274" s="2" t="inlineStr">
+        <is>
+          <t>ENG-38 periods: 24 USMCA periods all open — lock closed months (owner names the months)</t>
+        </is>
+      </c>
+      <c r="E274" s="2" t="inlineStr">
+        <is>
+          <t>OWNER</t>
+        </is>
+      </c>
+      <c r="F274" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="G274" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H274" s="2" t="inlineStr"/>
+    </row>
+    <row r="275">
+      <c r="A275" s="2" t="n">
+        <v>274</v>
+      </c>
+      <c r="B275" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="C275" s="2" t="inlineStr">
+        <is>
+          <t>Banking</t>
+        </is>
+      </c>
+      <c r="D275" s="2" t="inlineStr">
+        <is>
+          <t>M1 candidates scoped to the bank line's account</t>
+        </is>
+      </c>
+      <c r="E275" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F275" s="2" t="inlineStr">
+        <is>
+          <t>443.155</t>
+        </is>
+      </c>
+      <c r="G275" s="2" t="inlineStr">
+        <is>
+          <t>MERGED-UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="H275" s="2" t="inlineStr">
+        <is>
+          <t>722038f896</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="2" t="n">
+        <v>275</v>
+      </c>
+      <c r="B276" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="C276" s="2" t="inlineStr">
+        <is>
+          <t>Banking</t>
+        </is>
+      </c>
+      <c r="D276" s="2" t="inlineStr">
+        <is>
+          <t>M2 invoices + Faro purchases in the match union</t>
+        </is>
+      </c>
+      <c r="E276" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F276" s="2" t="inlineStr">
+        <is>
+          <t>443.155</t>
+        </is>
+      </c>
+      <c r="G276" s="2" t="inlineStr">
+        <is>
+          <t>MERGED-UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="H276" s="2" t="inlineStr">
+        <is>
+          <t>722038f896 add69bd031</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="2" t="n">
+        <v>276</v>
+      </c>
+      <c r="B277" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="C277" s="2" t="inlineStr">
+        <is>
+          <t>Banking</t>
+        </is>
+      </c>
+      <c r="D277" s="2" t="inlineStr">
+        <is>
+          <t>M3/M5 one matcher (MatchDrawer embedded); filters live</t>
+        </is>
+      </c>
+      <c r="E277" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F277" s="2" t="inlineStr">
+        <is>
+          <t>443.163</t>
+        </is>
+      </c>
+      <c r="G277" s="2" t="inlineStr">
+        <is>
+          <t>MERGED-UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="H277" s="2" t="inlineStr">
+        <is>
+          <t>8a58f20d9c</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="2" t="n">
+        <v>277</v>
+      </c>
+      <c r="B278" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="C278" s="2" t="inlineStr">
+        <is>
+          <t>Banking</t>
+        </is>
+      </c>
+      <c r="D278" s="2" t="inlineStr">
+        <is>
+          <t>M4 recon idempotency on transaction_source_links, not memo; 0 session-uuid memos on prod</t>
+        </is>
+      </c>
+      <c r="E278" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F278" s="2" t="inlineStr">
+        <is>
+          <t>390.3</t>
+        </is>
+      </c>
+      <c r="G278" s="2" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="H278" s="2" t="inlineStr">
+        <is>
+          <t>9147a9a055; prod 0/0</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="2" t="n">
+        <v>278</v>
+      </c>
+      <c r="B279" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="C279" s="2" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="D279" s="2" t="inlineStr">
+        <is>
+          <t>Palette: unselected boxes not pure white (0 of 1,556 files)</t>
+        </is>
+      </c>
+      <c r="E279" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F279" s="2" t="inlineStr">
+        <is>
+          <t>443.284</t>
+        </is>
+      </c>
+      <c r="G279" s="2" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="H279" s="2" t="inlineStr">
+        <is>
+          <t>75f1ed41d2; guard PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="2" t="n">
+        <v>279</v>
+      </c>
+      <c r="B280" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="C280" s="2" t="inlineStr">
+        <is>
+          <t>Dispatch</t>
+        </is>
+      </c>
+      <c r="D280" s="2" t="inlineStr">
+        <is>
+          <t>G1/G9/G11/G12/G15 code fixes merged (data remainders in ENG-07/08/13/14)</t>
+        </is>
+      </c>
+      <c r="E280" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F280" s="2" t="inlineStr">
+        <is>
+          <t>G-gaps</t>
+        </is>
+      </c>
+      <c r="G280" s="2" t="inlineStr">
+        <is>
+          <t>MERGED-UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="H280" s="2" t="inlineStr">
+        <is>
+          <t>6db7585fb6 4093026783 3b90a7f77b e136e13a58 0f1f83233e</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="2" t="n">
+        <v>280</v>
+      </c>
+      <c r="B281" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="C281" s="2" t="inlineStr">
+        <is>
+          <t>Accounting</t>
+        </is>
+      </c>
+      <c r="D281" s="2" t="inlineStr">
+        <is>
+          <t>Spine links: 0 of 8,057 postings without a spine link; TB 0</t>
+        </is>
+      </c>
+      <c r="E281" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F281" s="2" t="inlineStr">
+        <is>
+          <t>10-03</t>
+        </is>
+      </c>
+      <c r="G281" s="2" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="H281" s="2" t="inlineStr">
+        <is>
+          <t>prod measured 10-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="2" t="n">
+        <v>281</v>
+      </c>
+      <c r="B282" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="C282" s="2" t="inlineStr">
+        <is>
+          <t>Accounting</t>
+        </is>
+      </c>
+      <c r="D282" s="2" t="inlineStr">
+        <is>
+          <t>Cash-basis P&amp;L (F412), bank-line delete rule (F431), recurring worker refusal, 7-day unmatched alert, reefer off IFTA, A/P control by documents, matched-to-nothing refusal</t>
+        </is>
+      </c>
+      <c r="E282" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F282" s="2" t="inlineStr">
+        <is>
+          <t>various</t>
+        </is>
+      </c>
+      <c r="G282" s="2" t="inlineStr">
+        <is>
+          <t>MERGED-UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="H282" s="2" t="inlineStr">
+        <is>
+          <t>9b5809f1c0 3312d604a6 4693704449 202615380200 202615360600</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="2" t="n">
+        <v>282</v>
+      </c>
+      <c r="B283" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="C283" s="2" t="inlineStr">
+        <is>
+          <t>Engine</t>
+        </is>
+      </c>
+      <c r="D283" s="2" t="inlineStr">
+        <is>
+          <t>ENG-35 live sweep 10-24 3:10 PM CT: 339 live guards on a fresh prod fork — 283 PASS / 56 FAIL; split into ENG-39..53 + harness items</t>
+        </is>
+      </c>
+      <c r="E283" s="2" t="inlineStr">
+        <is>
+          <t>LEAD</t>
+        </is>
+      </c>
+      <c r="F283" s="2" t="inlineStr">
+        <is>
+          <t>ENG-35</t>
+        </is>
+      </c>
+      <c r="G283" s="2" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="H283" s="2" t="inlineStr">
+        <is>
+          <t>/tmp/live-results.txt; boxes 443.328/329/330</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="2" t="n">
+        <v>283</v>
+      </c>
+      <c r="B284" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="C284" s="2" t="inlineStr">
+        <is>
+          <t>Settlements</t>
+        </is>
+      </c>
+      <c r="D284" s="2" t="inlineStr">
+        <is>
+          <t>ENG-01c P-0119 settlement line deduction $10.00 has no driver_settlement_deductions row — writer + back-fill; ENG-01b refusal proven on fork</t>
+        </is>
+      </c>
+      <c r="E284" s="2" t="inlineStr">
+        <is>
+          <t>CC-1</t>
+        </is>
+      </c>
+      <c r="F284" s="2" t="inlineStr">
+        <is>
+          <t>443.322</t>
+        </is>
+      </c>
+      <c r="G284" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H284" s="2" t="inlineStr"/>
+    </row>
+    <row r="285">
+      <c r="A285" s="2" t="n">
+        <v>284</v>
+      </c>
+      <c r="B285" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="C285" s="2" t="inlineStr">
+        <is>
+          <t>Accounting</t>
+        </is>
+      </c>
+      <c r="D285" s="2" t="inlineStr">
+        <is>
+          <t>ENG-39 P0 vendor-balance view ≠ A/P GL by exactly the net pay of P-0113 (1,416.47) and P-0117 (329.51) — what the close owes vs what the view assumes</t>
+        </is>
+      </c>
+      <c r="E285" s="2" t="inlineStr">
+        <is>
+          <t>CC-1</t>
+        </is>
+      </c>
+      <c r="F285" s="2" t="inlineStr">
+        <is>
+          <t>443.328</t>
+        </is>
+      </c>
+      <c r="G285" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H285" s="2" t="inlineStr"/>
+    </row>
+    <row r="286">
+      <c r="A286" s="2" t="n">
+        <v>285</v>
+      </c>
+      <c r="B286" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="C286" s="2" t="inlineStr">
+        <is>
+          <t>Settlements</t>
+        </is>
+      </c>
+      <c r="D286" s="2" t="inlineStr">
+        <is>
+          <t>ENG-40 P-0067 and P-0119 closed with no company settlement</t>
+        </is>
+      </c>
+      <c r="E286" s="2" t="inlineStr">
+        <is>
+          <t>CC-1</t>
+        </is>
+      </c>
+      <c r="F286" s="2" t="inlineStr">
+        <is>
+          <t>443.328</t>
+        </is>
+      </c>
+      <c r="G286" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H286" s="2" t="inlineStr"/>
+    </row>
+    <row r="287">
+      <c r="A287" s="2" t="n">
+        <v>286</v>
+      </c>
+      <c r="B287" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="C287" s="2" t="inlineStr">
+        <is>
+          <t>Settlements</t>
+        </is>
+      </c>
+      <c r="D287" s="2" t="inlineStr">
+        <is>
+          <t>ENG-41 P-0121 cancelled but still reusable</t>
+        </is>
+      </c>
+      <c r="E287" s="2" t="inlineStr">
+        <is>
+          <t>CC-1</t>
+        </is>
+      </c>
+      <c r="F287" s="2" t="inlineStr">
+        <is>
+          <t>443.328</t>
+        </is>
+      </c>
+      <c r="G287" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H287" s="2" t="inlineStr"/>
+    </row>
+    <row r="288">
+      <c r="A288" s="2" t="n">
+        <v>287</v>
+      </c>
+      <c r="B288" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="C288" s="2" t="inlineStr">
+        <is>
+          <t>Settlements</t>
+        </is>
+      </c>
+      <c r="D288" s="2" t="inlineStr">
+        <is>
+          <t>ENG-42 89 active duplicate settlement-line groups</t>
+        </is>
+      </c>
+      <c r="E288" s="2" t="inlineStr">
+        <is>
+          <t>CC-1</t>
+        </is>
+      </c>
+      <c r="F288" s="2" t="inlineStr">
+        <is>
+          <t>443.328</t>
+        </is>
+      </c>
+      <c r="G288" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H288" s="2" t="inlineStr"/>
+    </row>
+    <row r="289">
+      <c r="A289" s="2" t="n">
+        <v>288</v>
+      </c>
+      <c r="B289" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="C289" s="2" t="inlineStr">
+        <is>
+          <t>Settlements</t>
+        </is>
+      </c>
+      <c r="D289" s="2" t="inlineStr">
+        <is>
+          <t>ENG-43 2 posted with zero load lines; P-0112/0116/0079/0114 $0 header; line ffac5c35 miles/rate NULL; closed-unposted with voided deduction</t>
+        </is>
+      </c>
+      <c r="E289" s="2" t="inlineStr">
+        <is>
+          <t>CC-1</t>
+        </is>
+      </c>
+      <c r="F289" s="2" t="inlineStr">
+        <is>
+          <t>443.328</t>
+        </is>
+      </c>
+      <c r="G289" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H289" s="2" t="inlineStr"/>
+    </row>
+    <row r="290">
+      <c r="A290" s="2" t="n">
+        <v>289</v>
+      </c>
+      <c r="B290" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="C290" s="2" t="inlineStr">
+        <is>
+          <t>Driver pay</t>
+        </is>
+      </c>
+      <c r="D290" s="2" t="inlineStr">
+        <is>
+          <t>ENG-44 bill 13697 due date; salaried stray bill not voided; presettlement autolink 13556/13563; live_load_number self-referential 13694/13695</t>
+        </is>
+      </c>
+      <c r="E290" s="2" t="inlineStr">
+        <is>
+          <t>CC-1</t>
+        </is>
+      </c>
+      <c r="F290" s="2" t="inlineStr">
+        <is>
+          <t>443.328</t>
+        </is>
+      </c>
+      <c r="G290" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H290" s="2" t="inlineStr"/>
+    </row>
+    <row r="291">
+      <c r="A291" s="2" t="n">
+        <v>290</v>
+      </c>
+      <c r="B291" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="C291" s="2" t="inlineStr">
+        <is>
+          <t>Drivers</t>
+        </is>
+      </c>
+      <c r="D291" s="2" t="inlineStr">
+        <is>
+          <t>ENG-45 2 settlement-active drivers without a Driver vendor (Carlos Mauricio Carvallo, Leonel Antonio Morales Noguez) — one profile per driver</t>
+        </is>
+      </c>
+      <c r="E291" s="2" t="inlineStr">
+        <is>
+          <t>CC-1</t>
+        </is>
+      </c>
+      <c r="F291" s="2" t="inlineStr">
+        <is>
+          <t>443.328</t>
+        </is>
+      </c>
+      <c r="G291" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H291" s="2" t="inlineStr"/>
+    </row>
+    <row r="292">
+      <c r="A292" s="2" t="n">
+        <v>291</v>
+      </c>
+      <c r="B292" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="C292" s="2" t="inlineStr">
+        <is>
+          <t>Accounting</t>
+        </is>
+      </c>
+      <c r="D292" s="2" t="inlineStr">
+        <is>
+          <t>ENG-46 bill_payment ad02cc37 no source link; escrow sub-ledger 315,000¢ vs baseline 132,500¢; 5796/P-0102 USMCA settlement for a Transportation document</t>
+        </is>
+      </c>
+      <c r="E292" s="2" t="inlineStr">
+        <is>
+          <t>CC-1</t>
+        </is>
+      </c>
+      <c r="F292" s="2" t="inlineStr">
+        <is>
+          <t>443.328</t>
+        </is>
+      </c>
+      <c r="G292" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H292" s="2" t="inlineStr"/>
+    </row>
+    <row r="293">
+      <c r="A293" s="2" t="n">
+        <v>292</v>
+      </c>
+      <c r="B293" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="C293" s="2" t="inlineStr">
+        <is>
+          <t>Engine</t>
+        </is>
+      </c>
+      <c r="D293" s="2" t="inlineStr">
+        <is>
+          <t>ENG-47 guards stale vs owner rulings: TIO PERFUMES kept; voids are design; S-13655/56; unbilled revenue migration; 'USMCA hidden'; archive tables RLS</t>
+        </is>
+      </c>
+      <c r="E293" s="2" t="inlineStr">
+        <is>
+          <t>CC-1</t>
+        </is>
+      </c>
+      <c r="F293" s="2" t="inlineStr">
+        <is>
+          <t>443.328</t>
+        </is>
+      </c>
+      <c r="G293" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H293" s="2" t="inlineStr"/>
+    </row>
+    <row r="294">
+      <c r="A294" s="2" t="n">
+        <v>293</v>
+      </c>
+      <c r="B294" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="C294" s="2" t="inlineStr">
+        <is>
+          <t>Fuel</t>
+        </is>
+      </c>
+      <c r="D294" s="2" t="inlineStr">
+        <is>
+          <t>ENG-48 fuel-expense one-to-one (13563-1 JE 0¢ + 14 loads); same-day duplicate fill pairs; traceability shrink fc461eb6; literal account '5000' in statement-card-credit-repair</t>
+        </is>
+      </c>
+      <c r="E294" s="2" t="inlineStr">
+        <is>
+          <t>CC-2</t>
+        </is>
+      </c>
+      <c r="F294" s="2" t="inlineStr">
+        <is>
+          <t>443.329</t>
+        </is>
+      </c>
+      <c r="G294" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H294" s="2" t="inlineStr"/>
+    </row>
+    <row r="295">
+      <c r="A295" s="2" t="n">
+        <v>294</v>
+      </c>
+      <c r="B295" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="C295" s="2" t="inlineStr">
+        <is>
+          <t>Settlements</t>
+        </is>
+      </c>
+      <c r="D295" s="2" t="inlineStr">
+        <is>
+          <t>ENG-49 settlement 5787 non-diesel expenses $235.01 vs signed $140.20</t>
+        </is>
+      </c>
+      <c r="E295" s="2" t="inlineStr">
+        <is>
+          <t>CC-2</t>
+        </is>
+      </c>
+      <c r="F295" s="2" t="inlineStr">
+        <is>
+          <t>443.329</t>
+        </is>
+      </c>
+      <c r="G295" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H295" s="2" t="inlineStr"/>
+    </row>
+    <row r="296">
+      <c r="A296" s="2" t="n">
+        <v>295</v>
+      </c>
+      <c r="B296" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="C296" s="2" t="inlineStr">
+        <is>
+          <t>Factoring</t>
+        </is>
+      </c>
+      <c r="D296" s="2" t="inlineStr">
+        <is>
+          <t>ENG-50 invoice amount_paid vs applications (9-13515 $525, 7 $350); book = Faro = AlwaysTrack 12 issues; factoring-advance-links-its-load selftest</t>
+        </is>
+      </c>
+      <c r="E296" s="2" t="inlineStr">
+        <is>
+          <t>CC-2</t>
+        </is>
+      </c>
+      <c r="F296" s="2" t="inlineStr">
+        <is>
+          <t>443.329</t>
+        </is>
+      </c>
+      <c r="G296" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H296" s="2" t="inlineStr"/>
+    </row>
+    <row r="297">
+      <c r="A297" s="2" t="n">
+        <v>296</v>
+      </c>
+      <c r="B297" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="C297" s="2" t="inlineStr">
+        <is>
+          <t>Banking</t>
+        </is>
+      </c>
+      <c r="D297" s="2" t="inlineStr">
+        <is>
+          <t>ENG-51 944 composite-memo rows unbackfilled; 1 Creator load miles without source</t>
+        </is>
+      </c>
+      <c r="E297" s="2" t="inlineStr">
+        <is>
+          <t>CC-2</t>
+        </is>
+      </c>
+      <c r="F297" s="2" t="inlineStr">
+        <is>
+          <t>443.329</t>
+        </is>
+      </c>
+      <c r="G297" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H297" s="2" t="inlineStr"/>
+    </row>
+    <row r="298">
+      <c r="A298" s="2" t="n">
+        <v>297</v>
+      </c>
+      <c r="B298" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="C298" s="2" t="inlineStr">
+        <is>
+          <t>Accounting</t>
+        </is>
+      </c>
+      <c r="D298" s="2" t="inlineStr">
+        <is>
+          <t>ENG-52 load-costs-board revenue not from loadCostRollupLateral (one source)</t>
+        </is>
+      </c>
+      <c r="E298" s="2" t="inlineStr">
+        <is>
+          <t>CC-2</t>
+        </is>
+      </c>
+      <c r="F298" s="2" t="inlineStr">
+        <is>
+          <t>443.329</t>
+        </is>
+      </c>
+      <c r="G298" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H298" s="2" t="inlineStr"/>
+    </row>
+    <row r="299">
+      <c r="A299" s="2" t="n">
+        <v>298</v>
+      </c>
+      <c r="B299" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="C299" s="2" t="inlineStr">
+        <is>
+          <t>Dispatch</t>
+        </is>
+      </c>
+      <c r="D299" s="2" t="inlineStr">
+        <is>
+          <t>ENG-53 13690 deadhead NULL; 16 live loads missing mileage; T174 odometer capture 49.7 h stale; 13700 no stop stamps; stops-gps-verified &gt; 120 s</t>
+        </is>
+      </c>
+      <c r="E299" s="2" t="inlineStr">
+        <is>
+          <t>CC-3</t>
+        </is>
+      </c>
+      <c r="F299" s="2" t="inlineStr">
+        <is>
+          <t>443.330</t>
+        </is>
+      </c>
+      <c r="G299" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H299" s="2" t="inlineStr"/>
+    </row>
+    <row r="300">
+      <c r="A300" s="2" t="n">
+        <v>299</v>
+      </c>
+      <c r="B300" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="C300" s="2" t="inlineStr">
+        <is>
+          <t>Fleet</t>
+        </is>
+      </c>
+      <c r="D300" s="2" t="inlineStr">
+        <is>
+          <t>ENG-54 T122, T124, T156 owned by IH 35 Transportation (leased to USMCA); rule: every real truck owned by IH 35 Trucking — waits for the owner's truck list (16 trucks)</t>
+        </is>
+      </c>
+      <c r="E300" s="2" t="inlineStr">
+        <is>
+          <t>OWNER</t>
+        </is>
+      </c>
+      <c r="F300" s="2" t="inlineStr">
+        <is>
+          <t>ENG-54</t>
+        </is>
+      </c>
+      <c r="G300" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H300" s="2" t="inlineStr"/>
+    </row>
+    <row r="301">
+      <c r="A301" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="B301" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="C301" s="2" t="inlineStr">
+        <is>
+          <t>Dispatch</t>
+        </is>
+      </c>
+      <c r="D301" s="2" t="inlineStr">
+        <is>
+          <t>ENG-55 443.327 app-wide drift alert every 30 min until fixed (reconciler I9: truck cannot make next stop, no stop date, no street address, no rate); 7 live</t>
+        </is>
+      </c>
+      <c r="E301" s="2" t="inlineStr">
+        <is>
+          <t>LEAD</t>
+        </is>
+      </c>
+      <c r="F301" s="2" t="inlineStr">
+        <is>
+          <t>443.327</t>
+        </is>
+      </c>
+      <c r="G301" s="2" t="inlineStr">
+        <is>
+          <t>CODED-QUEUED</t>
+        </is>
+      </c>
+      <c r="H301" s="2" t="inlineStr">
+        <is>
+          <t>eb338ebe94; reconciler 42/42, popup 5/5</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="2" t="n">
+        <v>301</v>
+      </c>
+      <c r="B302" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="C302" s="2" t="inlineStr">
+        <is>
+          <t>Fuel</t>
+        </is>
+      </c>
+      <c r="D302" s="2" t="inlineStr">
+        <is>
+          <t>ENG-25b owner 10-24 2:36 PM: Transportation diesel not on USMCA loads per signed docs = loan to Transportation (8000 Inter-company - IH35 Transportation) via rewriteDocumentLine</t>
+        </is>
+      </c>
+      <c r="E302" s="2" t="inlineStr">
+        <is>
+          <t>CC-3</t>
+        </is>
+      </c>
+      <c r="F302" s="2" t="inlineStr">
+        <is>
+          <t>443.324</t>
+        </is>
+      </c>
+      <c r="G302" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H302" s="2" t="inlineStr">
+        <is>
+          <t>Lead applies under AUTH-464</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="2" t="n">
+        <v>302</v>
+      </c>
+      <c r="B303" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="C303" s="2" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="D303" s="2" t="inlineStr">
+        <is>
+          <t>ENG-56 Cursor 443.326: V3 board grammar on all 23 PARTIAL/SHELL-ONLY surfaces of Cursor's own audit; one ratchet guard to 0</t>
+        </is>
+      </c>
+      <c r="E303" s="2" t="inlineStr">
+        <is>
+          <t>Cursor</t>
+        </is>
+      </c>
+      <c r="F303" s="2" t="inlineStr">
+        <is>
+          <t>443.326</t>
+        </is>
+      </c>
+      <c r="G303" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H303" s="2" t="inlineStr"/>
+    </row>
+    <row r="304">
+      <c r="A304" s="2" t="n">
+        <v>303</v>
+      </c>
+      <c r="B304" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="C304" s="2" t="inlineStr">
+        <is>
+          <t>Migrations</t>
+        </is>
+      </c>
+      <c r="D304" s="2" t="inlineStr">
+        <is>
+          <t>ENG-57 3 migrations held off prod 23 days waiting for a Lead fork validation (202614110000 source_document_ref unique; 202615210000/0100 lease-to-own ASC 842); 0000 carried a stale role list that fails on prod — fixed (dynamic append) and released; 0200 stays superseded</t>
+        </is>
+      </c>
+      <c r="E304" s="2" t="inlineStr">
+        <is>
+          <t>LEAD</t>
+        </is>
+      </c>
+      <c r="F304" s="2" t="inlineStr">
+        <is>
+          <t>443.331</t>
+        </is>
+      </c>
+      <c r="G304" s="2" t="inlineStr">
+        <is>
+          <t>CODED-QUEUED</t>
+        </is>
+      </c>
+      <c r="H304" s="2" t="inlineStr">
+        <is>
+          <t>1c1ea23b1e; real runner in prod mode on fresh fork: APPLY 3, SKIP 1,531, held untouched</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="2" t="n">
+        <v>304</v>
+      </c>
+      <c r="B305" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="C305" s="2" t="inlineStr">
+        <is>
+          <t>Engine</t>
+        </is>
+      </c>
+      <c r="D305" s="2" t="inlineStr">
+        <is>
+          <t>ENG-58 program-scoreboard.json 82 commits behind (max 80) failed every seat's step 1 — regenerated</t>
+        </is>
+      </c>
+      <c r="E305" s="2" t="inlineStr">
+        <is>
+          <t>LEAD</t>
+        </is>
+      </c>
+      <c r="F305" s="2" t="inlineStr">
+        <is>
+          <t>scoreboard</t>
+        </is>
+      </c>
+      <c r="G305" s="2" t="inlineStr">
+        <is>
+          <t>CODED-QUEUED</t>
+        </is>
+      </c>
+      <c r="H305" s="2" t="inlineStr">
+        <is>
+          <t>7de5f80937</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="2" t="n">
+        <v>305</v>
+      </c>
+      <c r="B306" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="C306" s="2" t="inlineStr">
+        <is>
+          <t>Engine</t>
+        </is>
+      </c>
+      <c r="D306" s="2" t="inlineStr">
+        <is>
+          <t>ENG-59 harness-only live failures (not data): pooler refused (list-apis, reports-neon-pv, loves-geofences), loopback-only fixture (invoice-header), CI-only file (no-sample-data), tsx import (recon-usmca), geocode key absent locally; rpt-s02 + invoice-copies PASS on rerun</t>
+        </is>
+      </c>
+      <c r="E306" s="2" t="inlineStr">
+        <is>
+          <t>LEAD</t>
+        </is>
+      </c>
+      <c r="F306" s="2" t="inlineStr">
+        <is>
+          <t>ENG-35</t>
+        </is>
+      </c>
+      <c r="G306" s="2" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="H306" s="2" t="inlineStr">
+        <is>
+          <t>rerun 10-24 3:25 PM CT</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="2" t="n">
+        <v>306</v>
+      </c>
+      <c r="B307" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C307" s="2" t="inlineStr">
+        <is>
+          <t>Legal</t>
+        </is>
+      </c>
+      <c r="D307" s="2" t="inlineStr">
+        <is>
+          <t>Lawsuits only in Legal (owner 10-24 3:47 PM CT): Insurance tab removed, /insurance/lawsuits redirects</t>
+        </is>
+      </c>
+      <c r="E307" s="2" t="inlineStr">
+        <is>
+          <t>LEAD</t>
+        </is>
+      </c>
+      <c r="F307" s="2" t="inlineStr">
+        <is>
+          <t>443.332</t>
+        </is>
+      </c>
+      <c r="G307" s="2" t="inlineStr">
+        <is>
+          <t>MERGED</t>
+        </is>
+      </c>
+      <c r="H307" s="2" t="inlineStr">
+        <is>
+          <t>#27543 156ddaa1ec</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="2" t="n">
+        <v>307</v>
+      </c>
+      <c r="B308" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C308" s="2" t="inlineStr">
+        <is>
+          <t>Legal</t>
+        </is>
+      </c>
+      <c r="D308" s="2" t="inlineStr">
+        <is>
+          <t>Legal › Lawsuits = legal-matters board locked to type lawsuit (design: lawsuits are matters); lawsuit links → ?insurance_lawsuit_id=</t>
+        </is>
+      </c>
+      <c r="E308" s="2" t="inlineStr">
+        <is>
+          <t>LEAD</t>
+        </is>
+      </c>
+      <c r="F308" s="2" t="inlineStr">
+        <is>
+          <t>443.334</t>
+        </is>
+      </c>
+      <c r="G308" s="2" t="inlineStr">
+        <is>
+          <t>CODED-QUEUED</t>
+        </is>
+      </c>
+      <c r="H308" s="2" t="inlineStr">
+        <is>
+          <t>049d20f559; guard red→green, vitest 20/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="2" t="n">
+        <v>308</v>
+      </c>
+      <c r="B309" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="C309" s="2" t="inlineStr">
+        <is>
+          <t>Legal</t>
+        </is>
+      </c>
+      <c r="D309" s="2" t="inlineStr">
+        <is>
+          <t>443.333 every USMCA coder TEST record in Legal + Insurance deleted (2 lawsuits, 18 matters, 7 claims, 3 accident reports, 5 cancelled policies; 79 rows with children); 3 real policies kept; books unchanged</t>
+        </is>
+      </c>
+      <c r="E309" s="2" t="inlineStr">
+        <is>
+          <t>LEAD</t>
+        </is>
+      </c>
+      <c r="F309" s="2" t="inlineStr">
+        <is>
+          <t>443.333</t>
+        </is>
+      </c>
+      <c r="G309" s="2" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="H309" s="2" t="inlineStr">
+        <is>
+          <t>AUTH-465 COMMITTED; audit.record_deletions 79; 3585edaf83</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="2" t="n">
+        <v>309</v>
+      </c>
+      <c r="B310" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="C310" s="2" t="inlineStr">
+        <is>
+          <t>Legal</t>
+        </is>
+      </c>
+      <c r="D310" s="2" t="inlineStr">
+        <is>
+          <t>ENG-60 retire the insurance.lawsuit side table: PolicyDetail lawsuit section → legal matters by claim, claim.lawsuit_id → legal matter, LawsuitsTab + 17 guards that read it; drop table after 0 rows all entities</t>
+        </is>
+      </c>
+      <c r="E310" s="2" t="inlineStr">
+        <is>
+          <t>CC-1</t>
+        </is>
+      </c>
+      <c r="F310" s="2" t="inlineStr">
+        <is>
+          <t>ENG-60</t>
+        </is>
+      </c>
+      <c r="G310" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H310" s="2" t="inlineStr"/>
+    </row>
+    <row r="311">
+      <c r="A311" s="2" t="n">
+        <v>310</v>
+      </c>
+      <c r="B311" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="C311" s="2" t="inlineStr">
+        <is>
+          <t>Settlements</t>
+        </is>
+      </c>
+      <c r="D311" s="2" t="inlineStr">
+        <is>
+          <t>ENG-61 closeLoadBookendedSettlementForDriver (settlement ping on final-load delivery) sets closed without posting — refused by tg_settlement_close_requires_posting (ACCT-ENG-01); the close-on-final-load path must post (postLoadBookendedSettlementGlAfterClose) or leave it open</t>
+        </is>
+      </c>
+      <c r="E311" s="2" t="inlineStr">
+        <is>
+          <t>CC-1</t>
+        </is>
+      </c>
+      <c r="F311" s="2" t="inlineStr">
+        <is>
+          <t>ENG-61</t>
+        </is>
+      </c>
+      <c r="G311" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H311" s="2" t="inlineStr">
+        <is>
+          <t>seen 10-24 on 13699/13700 stamp: settlements a41008ca, 6ba08647</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="2" t="n">
+        <v>311</v>
+      </c>
+      <c r="B312" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="C312" s="2" t="inlineStr">
+        <is>
+          <t>Dispatch</t>
+        </is>
+      </c>
+      <c r="D312" s="2" t="inlineStr">
+        <is>
+          <t>ENG-62 loads booked after their trip never got stop stamps (fences minted at booking; replay stamps nothing) — engine stop-arrival-from-fence-history; 13700 + 13699 delivered from the unit's own fence visits; stop-stamp ratchet 13 → 0</t>
+        </is>
+      </c>
+      <c r="E312" s="2" t="inlineStr">
+        <is>
+          <t>LEAD</t>
+        </is>
+      </c>
+      <c r="F312" s="2" t="inlineStr">
+        <is>
+          <t>443.335</t>
+        </is>
+      </c>
+      <c r="G312" s="2" t="inlineStr">
+        <is>
+          <t>CODED-QUEUED</t>
+        </is>
+      </c>
+      <c r="H312" s="2" t="inlineStr">
+        <is>
+          <t>a74b63e99b; prod applied: 13700 dispatched→delivered_pending_docs, 13699 in_transit→delivered_pending_docs</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="2" t="n">
+        <v>312</v>
+      </c>
+      <c r="B313" s="2" t="inlineStr">
+        <is>
+          <t>ENG</t>
+        </is>
+      </c>
+      <c r="C313" s="2" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="D313" s="2" t="inlineStr">
+        <is>
+          <t>ENG-63 verify-list-empty-settled (resolveListState no longer returns loading while pending) and verify-entity-label-rejects-uuid-shaped-name (HosTrackerSection must call entityLabel) fail on main 5a9f8303e9</t>
+        </is>
+      </c>
+      <c r="E313" s="2" t="inlineStr">
+        <is>
+          <t>CC-3</t>
+        </is>
+      </c>
+      <c r="F313" s="2" t="inlineStr">
+        <is>
+          <t>ENG-63</t>
+        </is>
+      </c>
+      <c r="G313" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H313" s="2" t="inlineStr"/>
+    </row>
+    <row r="314">
+      <c r="A314" s="2" t="n">
+        <v>313</v>
+      </c>
+      <c r="B314" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C314" s="2" t="inlineStr">
+        <is>
+          <t>Settlements</t>
+        </is>
+      </c>
+      <c r="D314" s="2" t="inlineStr">
+        <is>
+          <t>Design audit N2: Escrow register 'Opening balance (historical)' row (design) missing — running balance cannot tie</t>
+        </is>
+      </c>
+      <c r="E314" s="2" t="inlineStr">
+        <is>
+          <t>Cursor</t>
+        </is>
+      </c>
+      <c r="F314" s="2" t="inlineStr">
+        <is>
+          <t>443.326 #6</t>
+        </is>
+      </c>
+      <c r="G314" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H314" s="2" t="inlineStr"/>
+    </row>
+    <row r="315">
+      <c r="A315" s="2" t="n">
+        <v>314</v>
+      </c>
+      <c r="B315" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C315" s="2" t="inlineStr">
+        <is>
+          <t>Settlements</t>
+        </is>
+      </c>
+      <c r="D315" s="2" t="inlineStr">
+        <is>
+          <t>Design audit N3: settlement statement body has no drill links ('[n] fills →', 'BofA line →')</t>
+        </is>
+      </c>
+      <c r="E315" s="2" t="inlineStr">
+        <is>
+          <t>Cursor</t>
+        </is>
+      </c>
+      <c r="F315" s="2" t="inlineStr">
+        <is>
+          <t>443.326 #2</t>
+        </is>
+      </c>
+      <c r="G315" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H315" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
